--- a/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
+++ b/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
@@ -2790,7 +2790,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>713.26</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K7" s="0">
         <x:v>5</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K8" s="0">
         <x:v>5</x:v>
@@ -2842,7 +2842,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K9" s="0">
         <x:v>5</x:v>
@@ -2868,7 +2868,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>319.35</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K10" s="0">
         <x:v>5</x:v>
@@ -2894,7 +2894,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K11" s="0">
         <x:v>5</x:v>
@@ -2920,7 +2920,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K12" s="0">
         <x:v>5</x:v>
@@ -2946,7 +2946,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>30.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K13" s="0">
         <x:v>5</x:v>
@@ -2972,7 +2972,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>157.19</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K14" s="0">
         <x:v>5</x:v>
@@ -2998,7 +2998,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>534.96</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K15" s="0">
         <x:v>5</x:v>
@@ -3024,7 +3024,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>440</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K16" s="0">
         <x:v>5</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K17" s="0">
         <x:v>5</x:v>
@@ -3076,7 +3076,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>15.52</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K18" s="0">
         <x:v>5</x:v>
@@ -3102,7 +3102,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>19.14</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K19" s="0">
         <x:v>5</x:v>
@@ -3128,7 +3128,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.05</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K20" s="0">
         <x:v>5</x:v>
@@ -3154,7 +3154,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K21" s="0">
         <x:v>5</x:v>
@@ -3180,7 +3180,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K22" s="0">
         <x:v>5</x:v>
@@ -3206,7 +3206,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>54.17</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K23" s="0">
         <x:v>5</x:v>
@@ -3232,7 +3232,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>22.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K24" s="0">
         <x:v>5</x:v>
@@ -3258,7 +3258,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>39.26</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K25" s="0">
         <x:v>5</x:v>
@@ -3284,7 +3284,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K26" s="0">
         <x:v>5</x:v>
@@ -3310,7 +3310,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K27" s="0">
         <x:v>5</x:v>
@@ -3336,7 +3336,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K28" s="0">
         <x:v>5</x:v>
@@ -3362,7 +3362,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>2.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K29" s="0">
         <x:v>5</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K30" s="0">
         <x:v>5</x:v>
@@ -3414,7 +3414,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>33.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K31" s="0">
         <x:v>5</x:v>
@@ -3440,7 +3440,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K32" s="0">
         <x:v>5</x:v>
@@ -3466,7 +3466,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K33" s="0">
         <x:v>5</x:v>
@@ -3492,7 +3492,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K34" s="0">
         <x:v>5</x:v>
@@ -3518,7 +3518,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>2.63</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K35" s="0">
         <x:v>5</x:v>
@@ -3544,7 +3544,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K36" s="0">
         <x:v>5</x:v>
@@ -3570,7 +3570,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K37" s="0">
         <x:v>5</x:v>
@@ -3596,7 +3596,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K38" s="0">
         <x:v>5</x:v>
@@ -3622,7 +3622,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.71</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K39" s="0">
         <x:v>5</x:v>
@@ -3674,7 +3674,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>869.6</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K41" s="0">
         <x:v>5</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K42" s="0">
         <x:v>5</x:v>
@@ -3726,7 +3726,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K43" s="0">
         <x:v>5</x:v>
@@ -3752,7 +3752,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>285.7</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K44" s="0">
         <x:v>5</x:v>
@@ -3778,7 +3778,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K45" s="0">
         <x:v>5</x:v>
@@ -3804,7 +3804,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K46" s="0">
         <x:v>5</x:v>
@@ -3830,7 +3830,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>30.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K47" s="0">
         <x:v>5</x:v>
@@ -3856,7 +3856,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>126.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K48" s="0">
         <x:v>5</x:v>
@@ -3882,7 +3882,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>1069.92</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K49" s="0">
         <x:v>5</x:v>
@@ -3908,7 +3908,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>440</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K50" s="0">
         <x:v>5</x:v>
@@ -3934,7 +3934,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K51" s="0">
         <x:v>5</x:v>
@@ -3960,7 +3960,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>15.52</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K52" s="0">
         <x:v>5</x:v>
@@ -3986,7 +3986,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>19.14</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K53" s="0">
         <x:v>5</x:v>
@@ -4012,7 +4012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.05</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K54" s="0">
         <x:v>5</x:v>
@@ -4038,7 +4038,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K55" s="0">
         <x:v>5</x:v>
@@ -4064,7 +4064,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K56" s="0">
         <x:v>5</x:v>
@@ -4090,7 +4090,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>53.61</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K57" s="0">
         <x:v>5</x:v>
@@ -4116,7 +4116,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>22.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K58" s="0">
         <x:v>5</x:v>
@@ -4142,7 +4142,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>39.26</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K59" s="0">
         <x:v>5</x:v>
@@ -4168,7 +4168,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K60" s="0">
         <x:v>5</x:v>
@@ -4194,7 +4194,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K61" s="0">
         <x:v>5</x:v>
@@ -4220,7 +4220,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K62" s="0">
         <x:v>5</x:v>
@@ -4246,7 +4246,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K63" s="0">
         <x:v>5</x:v>
@@ -4272,7 +4272,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K64" s="0">
         <x:v>5</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>33.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K65" s="0">
         <x:v>5</x:v>
@@ -4324,7 +4324,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K66" s="0">
         <x:v>5</x:v>
@@ -4350,7 +4350,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K67" s="0">
         <x:v>5</x:v>
@@ -4376,7 +4376,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K68" s="0">
         <x:v>5</x:v>
@@ -4402,7 +4402,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>2.63</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K69" s="0">
         <x:v>5</x:v>
@@ -4428,7 +4428,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K70" s="0">
         <x:v>5</x:v>
@@ -4454,7 +4454,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K71" s="0">
         <x:v>5</x:v>
@@ -4480,7 +4480,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K72" s="0">
         <x:v>5</x:v>
@@ -4506,7 +4506,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.71</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K73" s="0">
         <x:v>5</x:v>
@@ -4558,7 +4558,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>604.35</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K75" s="0">
         <x:v>5</x:v>
@@ -4584,7 +4584,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K76" s="0">
         <x:v>5</x:v>
@@ -4610,7 +4610,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K77" s="0">
         <x:v>5</x:v>
@@ -4636,7 +4636,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>271.59</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K78" s="0">
         <x:v>5</x:v>
@@ -4662,7 +4662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K79" s="0">
         <x:v>5</x:v>
@@ -4688,7 +4688,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K80" s="0">
         <x:v>5</x:v>
@@ -4714,7 +4714,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>30.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K81" s="0">
         <x:v>5</x:v>
@@ -4740,7 +4740,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>154</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K82" s="0">
         <x:v>5</x:v>
@@ -4766,7 +4766,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>534.96</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K83" s="0">
         <x:v>5</x:v>
@@ -4792,7 +4792,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>440</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K84" s="0">
         <x:v>5</x:v>
@@ -4818,7 +4818,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>10.13</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K85" s="0">
         <x:v>5</x:v>
@@ -4844,7 +4844,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>15.72</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K86" s="0">
         <x:v>5</x:v>
@@ -4870,7 +4870,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.08</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K87" s="0">
         <x:v>5</x:v>
@@ -4896,7 +4896,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K88" s="0">
         <x:v>5</x:v>
@@ -4922,7 +4922,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K89" s="0">
         <x:v>5</x:v>
@@ -4948,7 +4948,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K90" s="0">
         <x:v>5</x:v>
@@ -4974,7 +4974,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>54.72</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K91" s="0">
         <x:v>5</x:v>
@@ -5000,7 +5000,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>39.12</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K92" s="0">
         <x:v>5</x:v>
@@ -5026,7 +5026,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>34.22</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K93" s="0">
         <x:v>5</x:v>
@@ -5052,7 +5052,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K94" s="0">
         <x:v>5</x:v>
@@ -5078,7 +5078,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K95" s="0">
         <x:v>5</x:v>
@@ -5104,7 +5104,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K96" s="0">
         <x:v>5</x:v>
@@ -5130,7 +5130,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>2.09</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K97" s="0">
         <x:v>5</x:v>
@@ -5156,7 +5156,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K98" s="0">
         <x:v>5</x:v>
@@ -5182,7 +5182,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>33.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K99" s="0">
         <x:v>5</x:v>
@@ -5208,7 +5208,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K100" s="0">
         <x:v>5</x:v>
@@ -5234,7 +5234,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K101" s="0">
         <x:v>5</x:v>
@@ -5260,7 +5260,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K102" s="0">
         <x:v>5</x:v>
@@ -5286,7 +5286,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>2.63</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K103" s="0">
         <x:v>5</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K104" s="0">
         <x:v>5</x:v>
@@ -5338,7 +5338,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K105" s="0">
         <x:v>5</x:v>
@@ -5364,7 +5364,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.71</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K106" s="0">
         <x:v>5</x:v>
@@ -5390,7 +5390,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>133.28</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K107" s="0">
         <x:v>5</x:v>
@@ -5442,7 +5442,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>649.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K109" s="0">
         <x:v>5</x:v>
@@ -5468,7 +5468,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.58</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K110" s="0">
         <x:v>5</x:v>
@@ -5494,7 +5494,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K111" s="0">
         <x:v>5</x:v>
@@ -5520,7 +5520,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>173.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K112" s="0">
         <x:v>5</x:v>
@@ -5546,7 +5546,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K113" s="0">
         <x:v>5</x:v>
@@ -5572,7 +5572,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K114" s="0">
         <x:v>5</x:v>
@@ -5598,7 +5598,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>22.62</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K115" s="0">
         <x:v>5</x:v>
@@ -5624,7 +5624,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>144.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K116" s="0">
         <x:v>5</x:v>
@@ -5650,7 +5650,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>927.99</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K117" s="0">
         <x:v>5</x:v>
@@ -5676,7 +5676,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>319</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K118" s="0">
         <x:v>5</x:v>
@@ -5702,7 +5702,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>8.87</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K119" s="0">
         <x:v>5</x:v>
@@ -5728,7 +5728,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K120" s="0">
         <x:v>5</x:v>
@@ -5754,7 +5754,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>16.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K121" s="0">
         <x:v>5</x:v>
@@ -5780,7 +5780,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K122" s="0">
         <x:v>5</x:v>
@@ -5806,7 +5806,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K123" s="0">
         <x:v>5</x:v>
@@ -5832,7 +5832,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K124" s="0">
         <x:v>5</x:v>
@@ -5858,7 +5858,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>28.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K125" s="0">
         <x:v>5</x:v>
@@ -5884,7 +5884,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>11.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K126" s="0">
         <x:v>5</x:v>
@@ -5910,7 +5910,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>28.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K127" s="0">
         <x:v>5</x:v>
@@ -5936,7 +5936,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K128" s="0">
         <x:v>5</x:v>
@@ -5962,7 +5962,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>3.18</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K129" s="0">
         <x:v>5</x:v>
@@ -5988,7 +5988,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K130" s="0">
         <x:v>5</x:v>
@@ -6014,7 +6014,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>2.16</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K131" s="0">
         <x:v>5</x:v>
@@ -6040,7 +6040,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K132" s="0">
         <x:v>5</x:v>
@@ -6066,7 +6066,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>45.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K133" s="0">
         <x:v>5</x:v>
@@ -6092,7 +6092,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K134" s="0">
         <x:v>5</x:v>
@@ -6118,7 +6118,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K135" s="0">
         <x:v>5</x:v>
@@ -6144,7 +6144,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K136" s="0">
         <x:v>5</x:v>
@@ -6170,7 +6170,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>3.06</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K137" s="0">
         <x:v>5</x:v>
@@ -6196,7 +6196,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K138" s="0">
         <x:v>5</x:v>
@@ -6222,7 +6222,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.77</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K139" s="0">
         <x:v>5</x:v>
@@ -6248,7 +6248,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>96.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K140" s="0">
         <x:v>5</x:v>
@@ -6300,7 +6300,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>769.84</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K142" s="0">
         <x:v>5</x:v>
@@ -6326,7 +6326,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K143" s="0">
         <x:v>5</x:v>
@@ -6352,7 +6352,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K144" s="0">
         <x:v>5</x:v>
@@ -6378,7 +6378,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>258.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K145" s="0">
         <x:v>5</x:v>
@@ -6404,7 +6404,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K146" s="0">
         <x:v>5</x:v>
@@ -6430,7 +6430,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K147" s="0">
         <x:v>5</x:v>
@@ -6456,7 +6456,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>30.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K148" s="0">
         <x:v>5</x:v>
@@ -6482,7 +6482,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>123.79</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K149" s="0">
         <x:v>5</x:v>
@@ -6508,7 +6508,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>1069.92</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K150" s="0">
         <x:v>5</x:v>
@@ -6534,7 +6534,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>440</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K151" s="0">
         <x:v>5</x:v>
@@ -6560,7 +6560,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>10.13</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K152" s="0">
         <x:v>5</x:v>
@@ -6586,7 +6586,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>15.72</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K153" s="0">
         <x:v>5</x:v>
@@ -6612,7 +6612,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>17.08</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K154" s="0">
         <x:v>5</x:v>
@@ -6638,7 +6638,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K155" s="0">
         <x:v>5</x:v>
@@ -6664,7 +6664,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K156" s="0">
         <x:v>5</x:v>
@@ -6690,7 +6690,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K157" s="0">
         <x:v>5</x:v>
@@ -6716,7 +6716,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>49.69</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K158" s="0">
         <x:v>5</x:v>
@@ -6742,7 +6742,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>39.12</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K159" s="0">
         <x:v>5</x:v>
@@ -6768,7 +6768,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>34.22</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K160" s="0">
         <x:v>5</x:v>
@@ -6794,7 +6794,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K161" s="0">
         <x:v>5</x:v>
@@ -6820,7 +6820,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K162" s="0">
         <x:v>5</x:v>
@@ -6846,7 +6846,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K163" s="0">
         <x:v>5</x:v>
@@ -6872,7 +6872,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>2.09</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K164" s="0">
         <x:v>5</x:v>
@@ -6898,7 +6898,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K165" s="0">
         <x:v>5</x:v>
@@ -6924,7 +6924,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>33.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K166" s="0">
         <x:v>5</x:v>
@@ -6950,7 +6950,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K167" s="0">
         <x:v>5</x:v>
@@ -6976,7 +6976,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K168" s="0">
         <x:v>5</x:v>
@@ -7002,7 +7002,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K169" s="0">
         <x:v>5</x:v>
@@ -7028,7 +7028,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>2.63</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K170" s="0">
         <x:v>5</x:v>
@@ -7054,7 +7054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K171" s="0">
         <x:v>5</x:v>
@@ -7080,7 +7080,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K172" s="0">
         <x:v>5</x:v>
@@ -7106,7 +7106,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.71</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K173" s="0">
         <x:v>5</x:v>
@@ -7132,7 +7132,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>90.21</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K174" s="0">
         <x:v>5</x:v>
@@ -7184,7 +7184,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>510.39</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K176" s="0">
         <x:v>5</x:v>
@@ -7210,7 +7210,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.58</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K177" s="0">
         <x:v>5</x:v>
@@ -7236,7 +7236,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K178" s="0">
         <x:v>5</x:v>
@@ -7262,7 +7262,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>173.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K179" s="0">
         <x:v>5</x:v>
@@ -7288,7 +7288,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K180" s="0">
         <x:v>5</x:v>
@@ -7314,7 +7314,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K181" s="0">
         <x:v>5</x:v>
@@ -7340,7 +7340,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>22.62</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K182" s="0">
         <x:v>5</x:v>
@@ -7366,7 +7366,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>144.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K183" s="0">
         <x:v>5</x:v>
@@ -7392,7 +7392,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>464</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K184" s="0">
         <x:v>5</x:v>
@@ -7418,7 +7418,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>255.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K185" s="0">
         <x:v>5</x:v>
@@ -7444,7 +7444,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>8.87</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K186" s="0">
         <x:v>5</x:v>
@@ -7470,7 +7470,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K187" s="0">
         <x:v>5</x:v>
@@ -7496,7 +7496,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>16.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K188" s="0">
         <x:v>5</x:v>
@@ -7522,7 +7522,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K189" s="0">
         <x:v>5</x:v>
@@ -7548,7 +7548,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K190" s="0">
         <x:v>5</x:v>
@@ -7574,7 +7574,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K191" s="0">
         <x:v>5</x:v>
@@ -7600,7 +7600,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>28.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K192" s="0">
         <x:v>5</x:v>
@@ -7626,7 +7626,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>11.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K193" s="0">
         <x:v>5</x:v>
@@ -7652,7 +7652,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>28.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K194" s="0">
         <x:v>5</x:v>
@@ -7678,7 +7678,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K195" s="0">
         <x:v>5</x:v>
@@ -7704,7 +7704,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I196" s="0">
-        <x:v>3.18</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K196" s="0">
         <x:v>5</x:v>
@@ -7730,7 +7730,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I197" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K197" s="0">
         <x:v>5</x:v>
@@ -7756,7 +7756,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I198" s="0">
-        <x:v>2.16</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K198" s="0">
         <x:v>5</x:v>
@@ -7782,7 +7782,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I199" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K199" s="0">
         <x:v>5</x:v>
@@ -7808,7 +7808,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I200" s="0">
-        <x:v>45.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K200" s="0">
         <x:v>5</x:v>
@@ -7834,7 +7834,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I201" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K201" s="0">
         <x:v>5</x:v>
@@ -7860,7 +7860,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I202" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K202" s="0">
         <x:v>5</x:v>
@@ -7886,7 +7886,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I203" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K203" s="0">
         <x:v>5</x:v>
@@ -7912,7 +7912,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I204" s="0">
-        <x:v>3.06</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K204" s="0">
         <x:v>5</x:v>
@@ -7938,7 +7938,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I205" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K205" s="0">
         <x:v>5</x:v>
@@ -7964,7 +7964,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I206" s="0">
-        <x:v>0.77</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K206" s="0">
         <x:v>5</x:v>
@@ -7990,7 +7990,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I207" s="0">
-        <x:v>96.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K207" s="0">
         <x:v>5</x:v>
@@ -8042,7 +8042,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I209" s="0">
-        <x:v>526.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K209" s="0">
         <x:v>5</x:v>
@@ -8068,7 +8068,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I210" s="0">
-        <x:v>0.6</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K210" s="0">
         <x:v>5</x:v>
@@ -8094,7 +8094,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I211" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K211" s="0">
         <x:v>5</x:v>
@@ -8120,7 +8120,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I212" s="0">
-        <x:v>178.73</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K212" s="0">
         <x:v>5</x:v>
@@ -8146,7 +8146,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I213" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K213" s="0">
         <x:v>5</x:v>
@@ -8172,7 +8172,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I214" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K214" s="0">
         <x:v>5</x:v>
@@ -8198,7 +8198,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I215" s="0">
-        <x:v>23.31</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K215" s="0">
         <x:v>5</x:v>
@@ -8224,7 +8224,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I216" s="0">
-        <x:v>148.84</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K216" s="0">
         <x:v>5</x:v>
@@ -8250,7 +8250,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I217" s="0">
-        <x:v>478.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K217" s="0">
         <x:v>5</x:v>
@@ -8276,7 +8276,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I218" s="0">
-        <x:v>263.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K218" s="0">
         <x:v>5</x:v>
@@ -8302,7 +8302,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I219" s="0">
-        <x:v>9.14</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K219" s="0">
         <x:v>5</x:v>
@@ -8328,7 +8328,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I220" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K220" s="0">
         <x:v>5</x:v>
@@ -8354,7 +8354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I221" s="0">
-        <x:v>17.33</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K221" s="0">
         <x:v>5</x:v>
@@ -8380,7 +8380,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I222" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K222" s="0">
         <x:v>5</x:v>
@@ -8406,7 +8406,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I223" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K223" s="0">
         <x:v>5</x:v>
@@ -8432,7 +8432,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I224" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K224" s="0">
         <x:v>5</x:v>
@@ -8458,7 +8458,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I225" s="0">
-        <x:v>29.29</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K225" s="0">
         <x:v>5</x:v>
@@ -8484,7 +8484,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I226" s="0">
-        <x:v>11.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K226" s="0">
         <x:v>5</x:v>
@@ -8510,7 +8510,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I227" s="0">
-        <x:v>29.29</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K227" s="0">
         <x:v>5</x:v>
@@ -8536,7 +8536,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I228" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K228" s="0">
         <x:v>5</x:v>
@@ -8562,7 +8562,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I229" s="0">
-        <x:v>3.28</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K229" s="0">
         <x:v>5</x:v>
@@ -8588,7 +8588,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I230" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K230" s="0">
         <x:v>5</x:v>
@@ -8614,7 +8614,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I231" s="0">
-        <x:v>2.23</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K231" s="0">
         <x:v>5</x:v>
@@ -8640,7 +8640,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I232" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K232" s="0">
         <x:v>5</x:v>
@@ -8666,7 +8666,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I233" s="0">
-        <x:v>47.22</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K233" s="0">
         <x:v>5</x:v>
@@ -8692,7 +8692,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I234" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K234" s="0">
         <x:v>5</x:v>
@@ -8718,7 +8718,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I235" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K235" s="0">
         <x:v>5</x:v>
@@ -8744,7 +8744,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I236" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K236" s="0">
         <x:v>5</x:v>
@@ -8770,7 +8770,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I237" s="0">
-        <x:v>3.15</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K237" s="0">
         <x:v>5</x:v>
@@ -8796,7 +8796,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I238" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K238" s="0">
         <x:v>5</x:v>
@@ -8822,7 +8822,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I239" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K239" s="0">
         <x:v>5</x:v>
@@ -8848,7 +8848,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I240" s="0">
-        <x:v>98.94</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K240" s="0">
         <x:v>5</x:v>
@@ -8900,7 +8900,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I242" s="0">
-        <x:v>827.92</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K242" s="0">
         <x:v>5</x:v>
@@ -8926,7 +8926,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I243" s="0">
-        <x:v>0.48</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K243" s="0">
         <x:v>5</x:v>
@@ -8952,7 +8952,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I244" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K244" s="0">
         <x:v>5</x:v>
@@ -8978,7 +8978,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I245" s="0">
-        <x:v>277.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K245" s="0">
         <x:v>5</x:v>
@@ -9004,7 +9004,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I246" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K246" s="0">
         <x:v>5</x:v>
@@ -9030,7 +9030,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I247" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K247" s="0">
         <x:v>5</x:v>
@@ -9056,7 +9056,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I248" s="0">
-        <x:v>26.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K248" s="0">
         <x:v>5</x:v>
@@ -9082,7 +9082,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I249" s="0">
-        <x:v>132.97</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K249" s="0">
         <x:v>5</x:v>
@@ -9108,7 +9108,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I250" s="0">
-        <x:v>765.68</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K250" s="0">
         <x:v>5</x:v>
@@ -9134,7 +9134,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I251" s="0">
-        <x:v>263.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K251" s="0">
         <x:v>5</x:v>
@@ -9160,7 +9160,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I252" s="0">
-        <x:v>8.94</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K252" s="0">
         <x:v>5</x:v>
@@ -9186,7 +9186,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I253" s="0">
-        <x:v>13.58</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K253" s="0">
         <x:v>5</x:v>
@@ -9212,7 +9212,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I254" s="0">
-        <x:v>14.74</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K254" s="0">
         <x:v>5</x:v>
@@ -9238,7 +9238,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I255" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K255" s="0">
         <x:v>5</x:v>
@@ -9264,7 +9264,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I256" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K256" s="0">
         <x:v>5</x:v>
@@ -9290,7 +9290,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I257" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K257" s="0">
         <x:v>5</x:v>
@@ -9316,7 +9316,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I258" s="0">
-        <x:v>58.35</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K258" s="0">
         <x:v>5</x:v>
@@ -9342,7 +9342,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I259" s="0">
-        <x:v>31.44</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K259" s="0">
         <x:v>5</x:v>
@@ -9368,7 +9368,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I260" s="0">
-        <x:v>29.54</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K260" s="0">
         <x:v>5</x:v>
@@ -9394,7 +9394,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I261" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K261" s="0">
         <x:v>5</x:v>
@@ -9420,7 +9420,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I262" s="0">
-        <x:v>3.75</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K262" s="0">
         <x:v>5</x:v>
@@ -9446,7 +9446,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I263" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K263" s="0">
         <x:v>5</x:v>
@@ -9472,7 +9472,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I264" s="0">
-        <x:v>1.91</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K264" s="0">
         <x:v>5</x:v>
@@ -9498,7 +9498,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I265" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K265" s="0">
         <x:v>5</x:v>
@@ -9524,7 +9524,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I266" s="0">
-        <x:v>32.74</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K266" s="0">
         <x:v>5</x:v>
@@ -9550,7 +9550,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I267" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K267" s="0">
         <x:v>5</x:v>
@@ -9576,7 +9576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I268" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K268" s="0">
         <x:v>5</x:v>
@@ -9602,7 +9602,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I269" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K269" s="0">
         <x:v>5</x:v>
@@ -9628,7 +9628,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I270" s="0">
-        <x:v>2.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K270" s="0">
         <x:v>5</x:v>
@@ -9654,7 +9654,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I271" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K271" s="0">
         <x:v>5</x:v>
@@ -9680,7 +9680,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I272" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K272" s="0">
         <x:v>5</x:v>
@@ -9706,7 +9706,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I273" s="0">
-        <x:v>0.64</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K273" s="0">
         <x:v>5</x:v>
@@ -9732,7 +9732,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I274" s="0">
-        <x:v>79.21</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K274" s="0">
         <x:v>5</x:v>
@@ -9784,7 +9784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I276" s="0">
-        <x:v>648.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K276" s="0">
         <x:v>5</x:v>
@@ -9810,7 +9810,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I277" s="0">
-        <x:v>0.58</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K277" s="0">
         <x:v>5</x:v>
@@ -9836,7 +9836,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I278" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K278" s="0">
         <x:v>5</x:v>
@@ -9862,7 +9862,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I279" s="0">
-        <x:v>173.15</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K279" s="0">
         <x:v>5</x:v>
@@ -9888,7 +9888,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I280" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K280" s="0">
         <x:v>5</x:v>
@@ -9914,7 +9914,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I281" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K281" s="0">
         <x:v>5</x:v>
@@ -9940,7 +9940,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I282" s="0">
-        <x:v>22.58</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K282" s="0">
         <x:v>5</x:v>
@@ -9966,7 +9966,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I283" s="0">
-        <x:v>144.19</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K283" s="0">
         <x:v>5</x:v>
@@ -9992,7 +9992,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I284" s="0">
-        <x:v>926.55</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K284" s="0">
         <x:v>5</x:v>
@@ -10018,7 +10018,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I285" s="0">
-        <x:v>318.5</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K285" s="0">
         <x:v>5</x:v>
@@ -10044,7 +10044,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I286" s="0">
-        <x:v>8.85</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K286" s="0">
         <x:v>5</x:v>
@@ -10070,7 +10070,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I287" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K287" s="0">
         <x:v>5</x:v>
@@ -10096,7 +10096,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I288" s="0">
-        <x:v>16.79</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K288" s="0">
         <x:v>5</x:v>
@@ -10122,7 +10122,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I289" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K289" s="0">
         <x:v>5</x:v>
@@ -10148,7 +10148,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I290" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K290" s="0">
         <x:v>5</x:v>
@@ -10174,7 +10174,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I291" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K291" s="0">
         <x:v>5</x:v>
@@ -10200,7 +10200,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I292" s="0">
-        <x:v>28.38</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K292" s="0">
         <x:v>5</x:v>
@@ -10226,7 +10226,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I293" s="0">
-        <x:v>11</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K293" s="0">
         <x:v>5</x:v>
@@ -10252,7 +10252,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I294" s="0">
-        <x:v>28.38</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K294" s="0">
         <x:v>5</x:v>
@@ -10278,7 +10278,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I295" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K295" s="0">
         <x:v>5</x:v>
@@ -10304,7 +10304,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I296" s="0">
-        <x:v>3.18</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K296" s="0">
         <x:v>5</x:v>
@@ -10330,7 +10330,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I297" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K297" s="0">
         <x:v>5</x:v>
@@ -10356,7 +10356,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I298" s="0">
-        <x:v>2.16</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K298" s="0">
         <x:v>5</x:v>
@@ -10382,7 +10382,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I299" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K299" s="0">
         <x:v>5</x:v>
@@ -10408,7 +10408,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I300" s="0">
-        <x:v>45.75</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K300" s="0">
         <x:v>5</x:v>
@@ -10434,7 +10434,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I301" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K301" s="0">
         <x:v>5</x:v>
@@ -10460,7 +10460,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I302" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K302" s="0">
         <x:v>5</x:v>
@@ -10486,7 +10486,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I303" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K303" s="0">
         <x:v>5</x:v>
@@ -10512,7 +10512,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I304" s="0">
-        <x:v>3.05</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K304" s="0">
         <x:v>5</x:v>
@@ -10538,7 +10538,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I305" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K305" s="0">
         <x:v>5</x:v>
@@ -10564,7 +10564,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I306" s="0">
-        <x:v>0.77</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K306" s="0">
         <x:v>5</x:v>
@@ -10590,7 +10590,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I307" s="0">
-        <x:v>95.86</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K307" s="0">
         <x:v>5</x:v>
@@ -10642,7 +10642,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I309" s="0">
-        <x:v>637.48</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K309" s="0">
         <x:v>5</x:v>
@@ -10668,7 +10668,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I310" s="0">
-        <x:v>0.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K310" s="0">
         <x:v>5</x:v>
@@ -10694,7 +10694,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I311" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K311" s="0">
         <x:v>5</x:v>
@@ -10720,7 +10720,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I312" s="0">
-        <x:v>271.91</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K312" s="0">
         <x:v>5</x:v>
@@ -10746,7 +10746,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I313" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K313" s="0">
         <x:v>5</x:v>
@@ -10772,7 +10772,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I314" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K314" s="0">
         <x:v>5</x:v>
@@ -10798,7 +10798,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I315" s="0">
-        <x:v>25.59</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K315" s="0">
         <x:v>5</x:v>
@@ -10824,7 +10824,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I316" s="0">
-        <x:v>130.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K316" s="0">
         <x:v>5</x:v>
@@ -10850,7 +10850,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I317" s="0">
-        <x:v>375.32</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K317" s="0">
         <x:v>5</x:v>
@@ -10876,7 +10876,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I318" s="0">
-        <x:v>258.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K318" s="0">
         <x:v>5</x:v>
@@ -10902,7 +10902,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I319" s="0">
-        <x:v>8.77</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K319" s="0">
         <x:v>5</x:v>
@@ -10928,7 +10928,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I320" s="0">
-        <x:v>13.31</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K320" s="0">
         <x:v>5</x:v>
@@ -10954,7 +10954,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I321" s="0">
-        <x:v>14.45</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K321" s="0">
         <x:v>5</x:v>
@@ -10980,7 +10980,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I322" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K322" s="0">
         <x:v>5</x:v>
@@ -11006,7 +11006,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I323" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K323" s="0">
         <x:v>5</x:v>
@@ -11032,7 +11032,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I324" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K324" s="0">
         <x:v>5</x:v>
@@ -11058,7 +11058,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I325" s="0">
-        <x:v>57.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K325" s="0">
         <x:v>5</x:v>
@@ -11084,7 +11084,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I326" s="0">
-        <x:v>30.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K326" s="0">
         <x:v>5</x:v>
@@ -11110,7 +11110,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I327" s="0">
-        <x:v>28.96</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K327" s="0">
         <x:v>5</x:v>
@@ -11136,7 +11136,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I328" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K328" s="0">
         <x:v>5</x:v>
@@ -11162,7 +11162,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I329" s="0">
-        <x:v>3.68</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K329" s="0">
         <x:v>5</x:v>
@@ -11188,7 +11188,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I330" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K330" s="0">
         <x:v>5</x:v>
@@ -11214,7 +11214,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I331" s="0">
-        <x:v>1.88</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K331" s="0">
         <x:v>5</x:v>
@@ -11240,7 +11240,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I332" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K332" s="0">
         <x:v>5</x:v>
@@ -11266,7 +11266,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I333" s="0">
-        <x:v>32.09</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K333" s="0">
         <x:v>5</x:v>
@@ -11292,7 +11292,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I334" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K334" s="0">
         <x:v>5</x:v>
@@ -11318,7 +11318,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I335" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K335" s="0">
         <x:v>5</x:v>
@@ -11344,7 +11344,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I336" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K336" s="0">
         <x:v>5</x:v>
@@ -11370,7 +11370,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I337" s="0">
-        <x:v>2.22</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K337" s="0">
         <x:v>5</x:v>
@@ -11396,7 +11396,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I338" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K338" s="0">
         <x:v>5</x:v>
@@ -11422,7 +11422,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I339" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K339" s="0">
         <x:v>5</x:v>
@@ -11448,7 +11448,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I340" s="0">
-        <x:v>0.62</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K340" s="0">
         <x:v>5</x:v>
@@ -11474,7 +11474,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I341" s="0">
-        <x:v>77.66</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K341" s="0">
         <x:v>5</x:v>
@@ -11526,7 +11526,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I343" s="0">
-        <x:v>924.1</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K343" s="0">
         <x:v>5</x:v>
@@ -11552,7 +11552,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I344" s="0">
-        <x:v>0.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K344" s="0">
         <x:v>5</x:v>
@@ -11578,7 +11578,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I345" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K345" s="0">
         <x:v>5</x:v>
@@ -11604,7 +11604,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I346" s="0">
-        <x:v>303.8</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K346" s="0">
         <x:v>5</x:v>
@@ -11630,7 +11630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I347" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K347" s="0">
         <x:v>5</x:v>
@@ -11656,7 +11656,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I348" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K348" s="0">
         <x:v>5</x:v>
@@ -11682,7 +11682,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I349" s="0">
-        <x:v>25.84</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K349" s="0">
         <x:v>5</x:v>
@@ -11708,7 +11708,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I350" s="0">
-        <x:v>134.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K350" s="0">
         <x:v>5</x:v>
@@ -11734,7 +11734,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I351" s="0">
-        <x:v>757.97</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K351" s="0">
         <x:v>5</x:v>
@@ -11760,7 +11760,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I352" s="0">
-        <x:v>260.55</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K352" s="0">
         <x:v>5</x:v>
@@ -11786,7 +11786,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I353" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K353" s="0">
         <x:v>5</x:v>
@@ -11812,7 +11812,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I354" s="0">
-        <x:v>13.51</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K354" s="0">
         <x:v>5</x:v>
@@ -11838,7 +11838,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I355" s="0">
-        <x:v>16.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K355" s="0">
         <x:v>5</x:v>
@@ -11864,7 +11864,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I356" s="0">
-        <x:v>0.05</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K356" s="0">
         <x:v>5</x:v>
@@ -11890,7 +11890,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I357" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K357" s="0">
         <x:v>5</x:v>
@@ -11916,7 +11916,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I358" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K358" s="0">
         <x:v>5</x:v>
@@ -11942,7 +11942,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I359" s="0">
-        <x:v>53.01</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K359" s="0">
         <x:v>5</x:v>
@@ -11968,7 +11968,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I360" s="0">
-        <x:v>13.97</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K360" s="0">
         <x:v>5</x:v>
@@ -11994,7 +11994,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I361" s="0">
-        <x:v>33.56</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K361" s="0">
         <x:v>5</x:v>
@@ -12020,7 +12020,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I362" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K362" s="0">
         <x:v>5</x:v>
@@ -12046,7 +12046,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I363" s="0">
-        <x:v>3.76</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K363" s="0">
         <x:v>5</x:v>
@@ -12072,7 +12072,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I364" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K364" s="0">
         <x:v>5</x:v>
@@ -12098,7 +12098,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I365" s="0">
-        <x:v>1.77</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K365" s="0">
         <x:v>5</x:v>
@@ -12124,7 +12124,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I366" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K366" s="0">
         <x:v>5</x:v>
@@ -12150,7 +12150,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I367" s="0">
-        <x:v>32.41</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K367" s="0">
         <x:v>5</x:v>
@@ -12176,7 +12176,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I368" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K368" s="0">
         <x:v>5</x:v>
@@ -12202,7 +12202,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I369" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K369" s="0">
         <x:v>5</x:v>
@@ -12228,7 +12228,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I370" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K370" s="0">
         <x:v>5</x:v>
@@ -12254,7 +12254,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I371" s="0">
-        <x:v>2.25</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K371" s="0">
         <x:v>5</x:v>
@@ -12280,7 +12280,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I372" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K372" s="0">
         <x:v>5</x:v>
@@ -12306,7 +12306,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I373" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K373" s="0">
         <x:v>5</x:v>
@@ -12332,7 +12332,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I374" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K374" s="0">
         <x:v>5</x:v>
@@ -12358,7 +12358,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I375" s="0">
-        <x:v>0.63</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K375" s="0">
         <x:v>5</x:v>
@@ -12384,7 +12384,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I376" s="0">
-        <x:v>97.98</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K376" s="0">
         <x:v>5</x:v>
@@ -12436,7 +12436,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I378" s="0">
-        <x:v>742.59</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K378" s="0">
         <x:v>5</x:v>
@@ -12462,7 +12462,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I379" s="0">
-        <x:v>0.46</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K379" s="0">
         <x:v>5</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I380" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K380" s="0">
         <x:v>5</x:v>
@@ -12514,7 +12514,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I381" s="0">
-        <x:v>269</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K381" s="0">
         <x:v>5</x:v>
@@ -12540,7 +12540,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I382" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K382" s="0">
         <x:v>5</x:v>
@@ -12566,7 +12566,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I383" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K383" s="0">
         <x:v>5</x:v>
@@ -12592,7 +12592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I384" s="0">
-        <x:v>25.32</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K384" s="0">
         <x:v>5</x:v>
@@ -12618,7 +12618,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I385" s="0">
-        <x:v>131.64</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K385" s="0">
         <x:v>5</x:v>
@@ -12644,7 +12644,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I386" s="0">
-        <x:v>371.3</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K386" s="0">
         <x:v>5</x:v>
@@ -12670,7 +12670,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I387" s="0">
-        <x:v>255.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K387" s="0">
         <x:v>5</x:v>
@@ -12696,7 +12696,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I388" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K388" s="0">
         <x:v>5</x:v>
@@ -12722,7 +12722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I389" s="0">
-        <x:v>13.24</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K389" s="0">
         <x:v>5</x:v>
@@ -12748,7 +12748,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I390" s="0">
-        <x:v>16.03</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K390" s="0">
         <x:v>5</x:v>
@@ -12774,7 +12774,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I391" s="0">
-        <x:v>0.05</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K391" s="0">
         <x:v>5</x:v>
@@ -12800,7 +12800,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I392" s="0">
-        <x:v>1.44</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K392" s="0">
         <x:v>5</x:v>
@@ -12826,7 +12826,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I393" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K393" s="0">
         <x:v>5</x:v>
@@ -12852,7 +12852,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I394" s="0">
-        <x:v>51.93</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K394" s="0">
         <x:v>5</x:v>
@@ -12878,7 +12878,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I395" s="0">
-        <x:v>13.69</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K395" s="0">
         <x:v>5</x:v>
@@ -12904,7 +12904,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I396" s="0">
-        <x:v>32.88</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K396" s="0">
         <x:v>5</x:v>
@@ -12930,7 +12930,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I397" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K397" s="0">
         <x:v>5</x:v>
@@ -12956,7 +12956,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I398" s="0">
-        <x:v>3.69</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K398" s="0">
         <x:v>5</x:v>
@@ -12982,7 +12982,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I399" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K399" s="0">
         <x:v>5</x:v>
@@ -13008,7 +13008,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I400" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K400" s="0">
         <x:v>5</x:v>
@@ -13034,7 +13034,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I401" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K401" s="0">
         <x:v>5</x:v>
@@ -13060,7 +13060,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I402" s="0">
-        <x:v>31.75</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K402" s="0">
         <x:v>5</x:v>
@@ -13086,7 +13086,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I403" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K403" s="0">
         <x:v>5</x:v>
@@ -13112,7 +13112,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I404" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K404" s="0">
         <x:v>5</x:v>
@@ -13138,7 +13138,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I405" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K405" s="0">
         <x:v>5</x:v>
@@ -13164,7 +13164,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I406" s="0">
-        <x:v>2.2</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K406" s="0">
         <x:v>5</x:v>
@@ -13190,7 +13190,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I407" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K407" s="0">
         <x:v>5</x:v>
@@ -13216,7 +13216,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I408" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K408" s="0">
         <x:v>5</x:v>
@@ -13242,7 +13242,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I409" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K409" s="0">
         <x:v>5</x:v>
@@ -13268,7 +13268,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I410" s="0">
-        <x:v>0.62</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K410" s="0">
         <x:v>5</x:v>
@@ -13294,7 +13294,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I411" s="0">
-        <x:v>95.99</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K411" s="0">
         <x:v>5</x:v>
@@ -13346,7 +13346,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I413" s="0">
-        <x:v>1502.21</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K413" s="0">
         <x:v>5</x:v>
@@ -13372,7 +13372,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I414" s="0">
-        <x:v>0.38</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K414" s="0">
         <x:v>5</x:v>
@@ -13398,7 +13398,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I415" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K415" s="0">
         <x:v>5</x:v>
@@ -13424,7 +13424,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I416" s="0">
-        <x:v>114.84</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K416" s="0">
         <x:v>5</x:v>
@@ -13450,7 +13450,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I417" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K417" s="0">
         <x:v>5</x:v>
@@ -13476,7 +13476,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I418" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K418" s="0">
         <x:v>5</x:v>
@@ -13502,7 +13502,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I419" s="0">
-        <x:v>21.92</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K419" s="0">
         <x:v>5</x:v>
@@ -13528,7 +13528,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I420" s="0">
-        <x:v>128.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K420" s="0">
         <x:v>5</x:v>
@@ -13554,7 +13554,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I421" s="0">
-        <x:v>211.24</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K421" s="0">
         <x:v>5</x:v>
@@ -13580,7 +13580,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I422" s="0">
-        <x:v>5.76</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K422" s="0">
         <x:v>5</x:v>
@@ -13606,7 +13606,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I423" s="0">
-        <x:v>11.14</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K423" s="0">
         <x:v>5</x:v>
@@ -13632,7 +13632,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I424" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K424" s="0">
         <x:v>5</x:v>
@@ -13658,7 +13658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I425" s="0">
-        <x:v>1.25</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K425" s="0">
         <x:v>5</x:v>
@@ -13684,7 +13684,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I426" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K426" s="0">
         <x:v>5</x:v>
@@ -13710,7 +13710,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I427" s="0">
-        <x:v>30.34</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K427" s="0">
         <x:v>5</x:v>
@@ -13736,7 +13736,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I428" s="0">
-        <x:v>22.66</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K428" s="0">
         <x:v>5</x:v>
@@ -13762,7 +13762,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I429" s="0">
-        <x:v>18.82</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K429" s="0">
         <x:v>5</x:v>
@@ -13788,7 +13788,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I430" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K430" s="0">
         <x:v>5</x:v>
@@ -13814,7 +13814,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I431" s="0">
-        <x:v>3.19</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K431" s="0">
         <x:v>5</x:v>
@@ -13840,7 +13840,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I432" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K432" s="0">
         <x:v>5</x:v>
@@ -13866,7 +13866,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I433" s="0">
-        <x:v>1.54</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K433" s="0">
         <x:v>5</x:v>
@@ -13892,7 +13892,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I434" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K434" s="0">
         <x:v>5</x:v>
@@ -13918,7 +13918,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I435" s="0">
-        <x:v>30.34</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K435" s="0">
         <x:v>5</x:v>
@@ -13944,7 +13944,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I436" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K436" s="0">
         <x:v>5</x:v>
@@ -13970,7 +13970,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I437" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K437" s="0">
         <x:v>5</x:v>
@@ -13996,7 +13996,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I438" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K438" s="0">
         <x:v>5</x:v>
@@ -14022,7 +14022,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I439" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K439" s="0">
         <x:v>5</x:v>
@@ -14048,7 +14048,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I440" s="0">
-        <x:v>1.91</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K440" s="0">
         <x:v>5</x:v>
@@ -14074,7 +14074,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I441" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K441" s="0">
         <x:v>5</x:v>
@@ -14100,7 +14100,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I442" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K442" s="0">
         <x:v>5</x:v>
@@ -14126,7 +14126,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I443" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K443" s="0">
         <x:v>5</x:v>
@@ -14152,7 +14152,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I444" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K444" s="0">
         <x:v>5</x:v>
@@ -14178,7 +14178,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I445" s="0">
-        <x:v>0.51</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K445" s="0">
         <x:v>5</x:v>
@@ -14204,7 +14204,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I446" s="0">
-        <x:v>79.44</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K446" s="0">
         <x:v>5</x:v>
@@ -14256,7 +14256,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I448" s="0">
-        <x:v>2231.11</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K448" s="0">
         <x:v>5</x:v>
@@ -14282,7 +14282,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I449" s="0">
-        <x:v>0.36</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K449" s="0">
         <x:v>5</x:v>
@@ -14308,7 +14308,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I450" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K450" s="0">
         <x:v>5</x:v>
@@ -14334,7 +14334,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I451" s="0">
-        <x:v>117.74</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K451" s="0">
         <x:v>5</x:v>
@@ -14360,7 +14360,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I452" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K452" s="0">
         <x:v>5</x:v>
@@ -14386,7 +14386,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I453" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K453" s="0">
         <x:v>5</x:v>
@@ -14412,7 +14412,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I454" s="0">
-        <x:v>20.42</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K454" s="0">
         <x:v>5</x:v>
@@ -14438,7 +14438,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I455" s="0">
-        <x:v>119.52</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K455" s="0">
         <x:v>5</x:v>
@@ -14464,7 +14464,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I456" s="0">
-        <x:v>196.83</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K456" s="0">
         <x:v>5</x:v>
@@ -14490,7 +14490,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I457" s="0">
-        <x:v>5.37</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K457" s="0">
         <x:v>5</x:v>
@@ -14516,7 +14516,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I458" s="0">
-        <x:v>10.38</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K458" s="0">
         <x:v>5</x:v>
@@ -14542,7 +14542,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I459" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K459" s="0">
         <x:v>5</x:v>
@@ -14568,7 +14568,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I460" s="0">
-        <x:v>1.16</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K460" s="0">
         <x:v>5</x:v>
@@ -14594,7 +14594,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I461" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K461" s="0">
         <x:v>5</x:v>
@@ -14620,7 +14620,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I462" s="0">
-        <x:v>28.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K462" s="0">
         <x:v>5</x:v>
@@ -14646,7 +14646,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I463" s="0">
-        <x:v>21.11</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K463" s="0">
         <x:v>5</x:v>
@@ -14672,7 +14672,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I464" s="0">
-        <x:v>17.54</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K464" s="0">
         <x:v>5</x:v>
@@ -14698,7 +14698,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I465" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K465" s="0">
         <x:v>5</x:v>
@@ -14724,7 +14724,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I466" s="0">
-        <x:v>2.97</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K466" s="0">
         <x:v>5</x:v>
@@ -14750,7 +14750,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I467" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K467" s="0">
         <x:v>5</x:v>
@@ -14776,7 +14776,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I468" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K468" s="0">
         <x:v>5</x:v>
@@ -14802,7 +14802,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I469" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K469" s="0">
         <x:v>5</x:v>
@@ -14828,7 +14828,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I470" s="0">
-        <x:v>28.27</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K470" s="0">
         <x:v>5</x:v>
@@ -14854,7 +14854,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I471" s="0">
-        <x:v>0</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K471" s="0">
         <x:v>5</x:v>
@@ -14880,7 +14880,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I472" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K472" s="0">
         <x:v>5</x:v>
@@ -14906,7 +14906,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I473" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K473" s="0">
         <x:v>5</x:v>
@@ -14932,7 +14932,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I474" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K474" s="0">
         <x:v>5</x:v>
@@ -14958,7 +14958,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I475" s="0">
-        <x:v>1.78</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K475" s="0">
         <x:v>5</x:v>
@@ -14984,7 +14984,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I476" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K476" s="0">
         <x:v>5</x:v>
@@ -15010,7 +15010,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I477" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K477" s="0">
         <x:v>5</x:v>
@@ -15036,7 +15036,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I478" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K478" s="0">
         <x:v>5</x:v>
@@ -15062,7 +15062,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I479" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K479" s="0">
         <x:v>5</x:v>
@@ -15088,7 +15088,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I480" s="0">
-        <x:v>0.48</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K480" s="0">
         <x:v>5</x:v>
@@ -15114,7 +15114,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I481" s="0">
-        <x:v>74.02</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="K481" s="0">
         <x:v>5</x:v>

--- a/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
+++ b/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
@@ -2790,7 +2790,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K7" s="0">
         <x:v>5</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K8" s="0">
         <x:v>5</x:v>
@@ -2842,7 +2842,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K9" s="0">
         <x:v>5</x:v>
@@ -2868,7 +2868,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K10" s="0">
         <x:v>5</x:v>
@@ -2894,7 +2894,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K11" s="0">
         <x:v>5</x:v>
@@ -2920,7 +2920,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K12" s="0">
         <x:v>5</x:v>
@@ -2946,7 +2946,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K13" s="0">
         <x:v>5</x:v>
@@ -2972,7 +2972,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K14" s="0">
         <x:v>5</x:v>
@@ -2998,7 +2998,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K15" s="0">
         <x:v>5</x:v>
@@ -3024,7 +3024,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K16" s="0">
         <x:v>5</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K17" s="0">
         <x:v>5</x:v>
@@ -3076,7 +3076,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K18" s="0">
         <x:v>5</x:v>
@@ -3102,7 +3102,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K19" s="0">
         <x:v>5</x:v>
@@ -3128,7 +3128,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K20" s="0">
         <x:v>5</x:v>
@@ -3154,7 +3154,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K21" s="0">
         <x:v>5</x:v>
@@ -3180,7 +3180,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K22" s="0">
         <x:v>5</x:v>
@@ -3206,7 +3206,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K23" s="0">
         <x:v>5</x:v>
@@ -3232,7 +3232,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K24" s="0">
         <x:v>5</x:v>
@@ -3258,7 +3258,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K25" s="0">
         <x:v>5</x:v>
@@ -3284,7 +3284,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K26" s="0">
         <x:v>5</x:v>
@@ -3310,7 +3310,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K27" s="0">
         <x:v>5</x:v>
@@ -3336,7 +3336,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K28" s="0">
         <x:v>5</x:v>
@@ -3362,7 +3362,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K29" s="0">
         <x:v>5</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K30" s="0">
         <x:v>5</x:v>
@@ -3414,7 +3414,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K31" s="0">
         <x:v>5</x:v>
@@ -3440,7 +3440,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K32" s="0">
         <x:v>5</x:v>
@@ -3466,7 +3466,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K33" s="0">
         <x:v>5</x:v>
@@ -3492,7 +3492,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K34" s="0">
         <x:v>5</x:v>
@@ -3518,7 +3518,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K35" s="0">
         <x:v>5</x:v>
@@ -3544,7 +3544,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K36" s="0">
         <x:v>5</x:v>
@@ -3570,7 +3570,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K37" s="0">
         <x:v>5</x:v>
@@ -3596,7 +3596,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K38" s="0">
         <x:v>5</x:v>
@@ -3622,7 +3622,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K39" s="0">
         <x:v>5</x:v>
@@ -3674,7 +3674,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K41" s="0">
         <x:v>5</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K42" s="0">
         <x:v>5</x:v>
@@ -3726,7 +3726,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K43" s="0">
         <x:v>5</x:v>
@@ -3752,7 +3752,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K44" s="0">
         <x:v>5</x:v>
@@ -3778,7 +3778,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K45" s="0">
         <x:v>5</x:v>
@@ -3804,7 +3804,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K46" s="0">
         <x:v>5</x:v>
@@ -3830,7 +3830,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K47" s="0">
         <x:v>5</x:v>
@@ -3856,7 +3856,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K48" s="0">
         <x:v>5</x:v>
@@ -3882,7 +3882,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K49" s="0">
         <x:v>5</x:v>
@@ -3908,7 +3908,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K50" s="0">
         <x:v>5</x:v>
@@ -3934,7 +3934,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K51" s="0">
         <x:v>5</x:v>
@@ -3960,7 +3960,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K52" s="0">
         <x:v>5</x:v>
@@ -3986,7 +3986,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K53" s="0">
         <x:v>5</x:v>
@@ -4012,7 +4012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K54" s="0">
         <x:v>5</x:v>
@@ -4038,7 +4038,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K55" s="0">
         <x:v>5</x:v>
@@ -4064,7 +4064,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K56" s="0">
         <x:v>5</x:v>
@@ -4090,7 +4090,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K57" s="0">
         <x:v>5</x:v>
@@ -4116,7 +4116,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K58" s="0">
         <x:v>5</x:v>
@@ -4142,7 +4142,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K59" s="0">
         <x:v>5</x:v>
@@ -4168,7 +4168,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K60" s="0">
         <x:v>5</x:v>
@@ -4194,7 +4194,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K61" s="0">
         <x:v>5</x:v>
@@ -4220,7 +4220,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K62" s="0">
         <x:v>5</x:v>
@@ -4246,7 +4246,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K63" s="0">
         <x:v>5</x:v>
@@ -4272,7 +4272,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K64" s="0">
         <x:v>5</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K65" s="0">
         <x:v>5</x:v>
@@ -4324,7 +4324,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K66" s="0">
         <x:v>5</x:v>
@@ -4350,7 +4350,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K67" s="0">
         <x:v>5</x:v>
@@ -4376,7 +4376,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K68" s="0">
         <x:v>5</x:v>
@@ -4402,7 +4402,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K69" s="0">
         <x:v>5</x:v>
@@ -4428,7 +4428,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K70" s="0">
         <x:v>5</x:v>
@@ -4454,7 +4454,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K71" s="0">
         <x:v>5</x:v>
@@ -4480,7 +4480,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K72" s="0">
         <x:v>5</x:v>
@@ -4506,7 +4506,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K73" s="0">
         <x:v>5</x:v>
@@ -4558,7 +4558,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K75" s="0">
         <x:v>5</x:v>
@@ -4584,7 +4584,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K76" s="0">
         <x:v>5</x:v>
@@ -4610,7 +4610,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K77" s="0">
         <x:v>5</x:v>
@@ -4636,7 +4636,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K78" s="0">
         <x:v>5</x:v>
@@ -4662,7 +4662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K79" s="0">
         <x:v>5</x:v>
@@ -4688,7 +4688,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K80" s="0">
         <x:v>5</x:v>
@@ -4714,7 +4714,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K81" s="0">
         <x:v>5</x:v>
@@ -4740,7 +4740,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K82" s="0">
         <x:v>5</x:v>
@@ -4766,7 +4766,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K83" s="0">
         <x:v>5</x:v>
@@ -4792,7 +4792,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K84" s="0">
         <x:v>5</x:v>
@@ -4818,7 +4818,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K85" s="0">
         <x:v>5</x:v>
@@ -4844,7 +4844,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K86" s="0">
         <x:v>5</x:v>
@@ -4870,7 +4870,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K87" s="0">
         <x:v>5</x:v>
@@ -4896,7 +4896,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K88" s="0">
         <x:v>5</x:v>
@@ -4922,7 +4922,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K89" s="0">
         <x:v>5</x:v>
@@ -4948,7 +4948,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K90" s="0">
         <x:v>5</x:v>
@@ -4974,7 +4974,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K91" s="0">
         <x:v>5</x:v>
@@ -5000,7 +5000,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K92" s="0">
         <x:v>5</x:v>
@@ -5026,7 +5026,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K93" s="0">
         <x:v>5</x:v>
@@ -5052,7 +5052,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K94" s="0">
         <x:v>5</x:v>
@@ -5078,7 +5078,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K95" s="0">
         <x:v>5</x:v>
@@ -5104,7 +5104,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K96" s="0">
         <x:v>5</x:v>
@@ -5130,7 +5130,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K97" s="0">
         <x:v>5</x:v>
@@ -5156,7 +5156,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K98" s="0">
         <x:v>5</x:v>
@@ -5182,7 +5182,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K99" s="0">
         <x:v>5</x:v>
@@ -5208,7 +5208,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K100" s="0">
         <x:v>5</x:v>
@@ -5234,7 +5234,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K101" s="0">
         <x:v>5</x:v>
@@ -5260,7 +5260,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K102" s="0">
         <x:v>5</x:v>
@@ -5286,7 +5286,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K103" s="0">
         <x:v>5</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K104" s="0">
         <x:v>5</x:v>
@@ -5338,7 +5338,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K105" s="0">
         <x:v>5</x:v>
@@ -5364,7 +5364,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K106" s="0">
         <x:v>5</x:v>
@@ -5390,7 +5390,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K107" s="0">
         <x:v>5</x:v>
@@ -5442,7 +5442,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K109" s="0">
         <x:v>5</x:v>
@@ -5468,7 +5468,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K110" s="0">
         <x:v>5</x:v>
@@ -5494,7 +5494,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K111" s="0">
         <x:v>5</x:v>
@@ -5520,7 +5520,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K112" s="0">
         <x:v>5</x:v>
@@ -5546,7 +5546,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K113" s="0">
         <x:v>5</x:v>
@@ -5572,7 +5572,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K114" s="0">
         <x:v>5</x:v>
@@ -5598,7 +5598,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K115" s="0">
         <x:v>5</x:v>
@@ -5624,7 +5624,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K116" s="0">
         <x:v>5</x:v>
@@ -5650,7 +5650,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K117" s="0">
         <x:v>5</x:v>
@@ -5676,7 +5676,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K118" s="0">
         <x:v>5</x:v>
@@ -5702,7 +5702,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K119" s="0">
         <x:v>5</x:v>
@@ -5728,7 +5728,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K120" s="0">
         <x:v>5</x:v>
@@ -5754,7 +5754,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K121" s="0">
         <x:v>5</x:v>
@@ -5780,7 +5780,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K122" s="0">
         <x:v>5</x:v>
@@ -5806,7 +5806,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K123" s="0">
         <x:v>5</x:v>
@@ -5832,7 +5832,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K124" s="0">
         <x:v>5</x:v>
@@ -5858,7 +5858,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K125" s="0">
         <x:v>5</x:v>
@@ -5884,7 +5884,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K126" s="0">
         <x:v>5</x:v>
@@ -5910,7 +5910,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K127" s="0">
         <x:v>5</x:v>
@@ -5936,7 +5936,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K128" s="0">
         <x:v>5</x:v>
@@ -5962,7 +5962,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K129" s="0">
         <x:v>5</x:v>
@@ -5988,7 +5988,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K130" s="0">
         <x:v>5</x:v>
@@ -6014,7 +6014,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K131" s="0">
         <x:v>5</x:v>
@@ -6040,7 +6040,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K132" s="0">
         <x:v>5</x:v>
@@ -6066,7 +6066,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K133" s="0">
         <x:v>5</x:v>
@@ -6092,7 +6092,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K134" s="0">
         <x:v>5</x:v>
@@ -6118,7 +6118,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K135" s="0">
         <x:v>5</x:v>
@@ -6144,7 +6144,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K136" s="0">
         <x:v>5</x:v>
@@ -6170,7 +6170,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K137" s="0">
         <x:v>5</x:v>
@@ -6196,7 +6196,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K138" s="0">
         <x:v>5</x:v>
@@ -6222,7 +6222,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K139" s="0">
         <x:v>5</x:v>
@@ -6248,7 +6248,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K140" s="0">
         <x:v>5</x:v>
@@ -6300,7 +6300,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K142" s="0">
         <x:v>5</x:v>
@@ -6326,7 +6326,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K143" s="0">
         <x:v>5</x:v>
@@ -6352,7 +6352,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K144" s="0">
         <x:v>5</x:v>
@@ -6378,7 +6378,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K145" s="0">
         <x:v>5</x:v>
@@ -6404,7 +6404,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K146" s="0">
         <x:v>5</x:v>
@@ -6430,7 +6430,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K147" s="0">
         <x:v>5</x:v>
@@ -6456,7 +6456,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K148" s="0">
         <x:v>5</x:v>
@@ -6482,7 +6482,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K149" s="0">
         <x:v>5</x:v>
@@ -6508,7 +6508,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K150" s="0">
         <x:v>5</x:v>
@@ -6534,7 +6534,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K151" s="0">
         <x:v>5</x:v>
@@ -6560,7 +6560,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K152" s="0">
         <x:v>5</x:v>
@@ -6586,7 +6586,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K153" s="0">
         <x:v>5</x:v>
@@ -6612,7 +6612,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K154" s="0">
         <x:v>5</x:v>
@@ -6638,7 +6638,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K155" s="0">
         <x:v>5</x:v>
@@ -6664,7 +6664,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K156" s="0">
         <x:v>5</x:v>
@@ -6690,7 +6690,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K157" s="0">
         <x:v>5</x:v>
@@ -6716,7 +6716,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K158" s="0">
         <x:v>5</x:v>
@@ -6742,7 +6742,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K159" s="0">
         <x:v>5</x:v>
@@ -6768,7 +6768,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K160" s="0">
         <x:v>5</x:v>
@@ -6794,7 +6794,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K161" s="0">
         <x:v>5</x:v>
@@ -6820,7 +6820,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K162" s="0">
         <x:v>5</x:v>
@@ -6846,7 +6846,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K163" s="0">
         <x:v>5</x:v>
@@ -6872,7 +6872,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K164" s="0">
         <x:v>5</x:v>
@@ -6898,7 +6898,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K165" s="0">
         <x:v>5</x:v>
@@ -6924,7 +6924,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K166" s="0">
         <x:v>5</x:v>
@@ -6950,7 +6950,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K167" s="0">
         <x:v>5</x:v>
@@ -6976,7 +6976,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K168" s="0">
         <x:v>5</x:v>
@@ -7002,7 +7002,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K169" s="0">
         <x:v>5</x:v>
@@ -7028,7 +7028,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K170" s="0">
         <x:v>5</x:v>
@@ -7054,7 +7054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K171" s="0">
         <x:v>5</x:v>
@@ -7080,7 +7080,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K172" s="0">
         <x:v>5</x:v>
@@ -7106,7 +7106,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K173" s="0">
         <x:v>5</x:v>
@@ -7132,7 +7132,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K174" s="0">
         <x:v>5</x:v>
@@ -7184,7 +7184,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K176" s="0">
         <x:v>5</x:v>
@@ -7210,7 +7210,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K177" s="0">
         <x:v>5</x:v>
@@ -7236,7 +7236,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K178" s="0">
         <x:v>5</x:v>
@@ -7262,7 +7262,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K179" s="0">
         <x:v>5</x:v>
@@ -7288,7 +7288,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K180" s="0">
         <x:v>5</x:v>
@@ -7314,7 +7314,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K181" s="0">
         <x:v>5</x:v>
@@ -7340,7 +7340,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K182" s="0">
         <x:v>5</x:v>
@@ -7366,7 +7366,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K183" s="0">
         <x:v>5</x:v>
@@ -7392,7 +7392,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K184" s="0">
         <x:v>5</x:v>
@@ -7418,7 +7418,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K185" s="0">
         <x:v>5</x:v>
@@ -7444,7 +7444,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K186" s="0">
         <x:v>5</x:v>
@@ -7470,7 +7470,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K187" s="0">
         <x:v>5</x:v>
@@ -7496,7 +7496,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K188" s="0">
         <x:v>5</x:v>
@@ -7522,7 +7522,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K189" s="0">
         <x:v>5</x:v>
@@ -7548,7 +7548,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K190" s="0">
         <x:v>5</x:v>
@@ -7574,7 +7574,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K191" s="0">
         <x:v>5</x:v>
@@ -7600,7 +7600,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K192" s="0">
         <x:v>5</x:v>
@@ -7626,7 +7626,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K193" s="0">
         <x:v>5</x:v>
@@ -7652,7 +7652,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K194" s="0">
         <x:v>5</x:v>
@@ -7678,7 +7678,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K195" s="0">
         <x:v>5</x:v>
@@ -7704,7 +7704,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I196" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K196" s="0">
         <x:v>5</x:v>
@@ -7730,7 +7730,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I197" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K197" s="0">
         <x:v>5</x:v>
@@ -7756,7 +7756,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I198" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K198" s="0">
         <x:v>5</x:v>
@@ -7782,7 +7782,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I199" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K199" s="0">
         <x:v>5</x:v>
@@ -7808,7 +7808,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I200" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K200" s="0">
         <x:v>5</x:v>
@@ -7834,7 +7834,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I201" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K201" s="0">
         <x:v>5</x:v>
@@ -7860,7 +7860,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I202" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K202" s="0">
         <x:v>5</x:v>
@@ -7886,7 +7886,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I203" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K203" s="0">
         <x:v>5</x:v>
@@ -7912,7 +7912,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I204" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K204" s="0">
         <x:v>5</x:v>
@@ -7938,7 +7938,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I205" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K205" s="0">
         <x:v>5</x:v>
@@ -7964,7 +7964,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I206" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K206" s="0">
         <x:v>5</x:v>
@@ -7990,7 +7990,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I207" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K207" s="0">
         <x:v>5</x:v>
@@ -8042,7 +8042,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I209" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K209" s="0">
         <x:v>5</x:v>
@@ -8068,7 +8068,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I210" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K210" s="0">
         <x:v>5</x:v>
@@ -8094,7 +8094,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I211" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K211" s="0">
         <x:v>5</x:v>
@@ -8120,7 +8120,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I212" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K212" s="0">
         <x:v>5</x:v>
@@ -8146,7 +8146,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I213" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K213" s="0">
         <x:v>5</x:v>
@@ -8172,7 +8172,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I214" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K214" s="0">
         <x:v>5</x:v>
@@ -8198,7 +8198,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I215" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K215" s="0">
         <x:v>5</x:v>
@@ -8224,7 +8224,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I216" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K216" s="0">
         <x:v>5</x:v>
@@ -8250,7 +8250,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I217" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K217" s="0">
         <x:v>5</x:v>
@@ -8276,7 +8276,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I218" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K218" s="0">
         <x:v>5</x:v>
@@ -8302,7 +8302,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I219" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K219" s="0">
         <x:v>5</x:v>
@@ -8328,7 +8328,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I220" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K220" s="0">
         <x:v>5</x:v>
@@ -8354,7 +8354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I221" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K221" s="0">
         <x:v>5</x:v>
@@ -8380,7 +8380,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I222" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K222" s="0">
         <x:v>5</x:v>
@@ -8406,7 +8406,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I223" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K223" s="0">
         <x:v>5</x:v>
@@ -8432,7 +8432,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I224" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K224" s="0">
         <x:v>5</x:v>
@@ -8458,7 +8458,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I225" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K225" s="0">
         <x:v>5</x:v>
@@ -8484,7 +8484,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I226" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K226" s="0">
         <x:v>5</x:v>
@@ -8510,7 +8510,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I227" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K227" s="0">
         <x:v>5</x:v>
@@ -8536,7 +8536,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I228" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K228" s="0">
         <x:v>5</x:v>
@@ -8562,7 +8562,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I229" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K229" s="0">
         <x:v>5</x:v>
@@ -8588,7 +8588,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I230" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K230" s="0">
         <x:v>5</x:v>
@@ -8614,7 +8614,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I231" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K231" s="0">
         <x:v>5</x:v>
@@ -8640,7 +8640,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I232" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K232" s="0">
         <x:v>5</x:v>
@@ -8666,7 +8666,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I233" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K233" s="0">
         <x:v>5</x:v>
@@ -8692,7 +8692,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I234" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K234" s="0">
         <x:v>5</x:v>
@@ -8718,7 +8718,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I235" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K235" s="0">
         <x:v>5</x:v>
@@ -8744,7 +8744,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I236" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K236" s="0">
         <x:v>5</x:v>
@@ -8770,7 +8770,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I237" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K237" s="0">
         <x:v>5</x:v>
@@ -8796,7 +8796,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I238" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K238" s="0">
         <x:v>5</x:v>
@@ -8822,7 +8822,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I239" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K239" s="0">
         <x:v>5</x:v>
@@ -8848,7 +8848,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I240" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K240" s="0">
         <x:v>5</x:v>
@@ -8900,7 +8900,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I242" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K242" s="0">
         <x:v>5</x:v>
@@ -8926,7 +8926,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I243" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K243" s="0">
         <x:v>5</x:v>
@@ -8952,7 +8952,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I244" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K244" s="0">
         <x:v>5</x:v>
@@ -8978,7 +8978,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I245" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K245" s="0">
         <x:v>5</x:v>
@@ -9004,7 +9004,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I246" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K246" s="0">
         <x:v>5</x:v>
@@ -9030,7 +9030,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I247" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K247" s="0">
         <x:v>5</x:v>
@@ -9056,7 +9056,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I248" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K248" s="0">
         <x:v>5</x:v>
@@ -9082,7 +9082,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I249" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K249" s="0">
         <x:v>5</x:v>
@@ -9108,7 +9108,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I250" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K250" s="0">
         <x:v>5</x:v>
@@ -9134,7 +9134,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I251" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K251" s="0">
         <x:v>5</x:v>
@@ -9160,7 +9160,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I252" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K252" s="0">
         <x:v>5</x:v>
@@ -9186,7 +9186,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I253" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K253" s="0">
         <x:v>5</x:v>
@@ -9212,7 +9212,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I254" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K254" s="0">
         <x:v>5</x:v>
@@ -9238,7 +9238,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I255" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K255" s="0">
         <x:v>5</x:v>
@@ -9264,7 +9264,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I256" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K256" s="0">
         <x:v>5</x:v>
@@ -9290,7 +9290,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I257" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K257" s="0">
         <x:v>5</x:v>
@@ -9316,7 +9316,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I258" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K258" s="0">
         <x:v>5</x:v>
@@ -9342,7 +9342,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I259" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K259" s="0">
         <x:v>5</x:v>
@@ -9368,7 +9368,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I260" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K260" s="0">
         <x:v>5</x:v>
@@ -9394,7 +9394,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I261" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K261" s="0">
         <x:v>5</x:v>
@@ -9420,7 +9420,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I262" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K262" s="0">
         <x:v>5</x:v>
@@ -9446,7 +9446,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I263" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K263" s="0">
         <x:v>5</x:v>
@@ -9472,7 +9472,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I264" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K264" s="0">
         <x:v>5</x:v>
@@ -9498,7 +9498,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I265" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K265" s="0">
         <x:v>5</x:v>
@@ -9524,7 +9524,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I266" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K266" s="0">
         <x:v>5</x:v>
@@ -9550,7 +9550,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I267" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K267" s="0">
         <x:v>5</x:v>
@@ -9576,7 +9576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I268" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K268" s="0">
         <x:v>5</x:v>
@@ -9602,7 +9602,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I269" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K269" s="0">
         <x:v>5</x:v>
@@ -9628,7 +9628,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I270" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K270" s="0">
         <x:v>5</x:v>
@@ -9654,7 +9654,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I271" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K271" s="0">
         <x:v>5</x:v>
@@ -9680,7 +9680,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I272" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K272" s="0">
         <x:v>5</x:v>
@@ -9706,7 +9706,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I273" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K273" s="0">
         <x:v>5</x:v>
@@ -9732,7 +9732,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I274" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K274" s="0">
         <x:v>5</x:v>
@@ -9784,7 +9784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I276" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K276" s="0">
         <x:v>5</x:v>
@@ -9810,7 +9810,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I277" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K277" s="0">
         <x:v>5</x:v>
@@ -9836,7 +9836,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I278" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K278" s="0">
         <x:v>5</x:v>
@@ -9862,7 +9862,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I279" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K279" s="0">
         <x:v>5</x:v>
@@ -9888,7 +9888,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I280" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K280" s="0">
         <x:v>5</x:v>
@@ -9914,7 +9914,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I281" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K281" s="0">
         <x:v>5</x:v>
@@ -9940,7 +9940,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I282" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K282" s="0">
         <x:v>5</x:v>
@@ -9966,7 +9966,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I283" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K283" s="0">
         <x:v>5</x:v>
@@ -9992,7 +9992,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I284" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K284" s="0">
         <x:v>5</x:v>
@@ -10018,7 +10018,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I285" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K285" s="0">
         <x:v>5</x:v>
@@ -10044,7 +10044,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I286" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K286" s="0">
         <x:v>5</x:v>
@@ -10070,7 +10070,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I287" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K287" s="0">
         <x:v>5</x:v>
@@ -10096,7 +10096,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I288" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K288" s="0">
         <x:v>5</x:v>
@@ -10122,7 +10122,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I289" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K289" s="0">
         <x:v>5</x:v>
@@ -10148,7 +10148,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I290" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K290" s="0">
         <x:v>5</x:v>
@@ -10174,7 +10174,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I291" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K291" s="0">
         <x:v>5</x:v>
@@ -10200,7 +10200,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I292" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K292" s="0">
         <x:v>5</x:v>
@@ -10226,7 +10226,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I293" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K293" s="0">
         <x:v>5</x:v>
@@ -10252,7 +10252,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I294" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K294" s="0">
         <x:v>5</x:v>
@@ -10278,7 +10278,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I295" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K295" s="0">
         <x:v>5</x:v>
@@ -10304,7 +10304,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I296" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K296" s="0">
         <x:v>5</x:v>
@@ -10330,7 +10330,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I297" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K297" s="0">
         <x:v>5</x:v>
@@ -10356,7 +10356,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I298" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K298" s="0">
         <x:v>5</x:v>
@@ -10382,7 +10382,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I299" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K299" s="0">
         <x:v>5</x:v>
@@ -10408,7 +10408,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I300" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K300" s="0">
         <x:v>5</x:v>
@@ -10434,7 +10434,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I301" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K301" s="0">
         <x:v>5</x:v>
@@ -10460,7 +10460,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I302" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K302" s="0">
         <x:v>5</x:v>
@@ -10486,7 +10486,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I303" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K303" s="0">
         <x:v>5</x:v>
@@ -10512,7 +10512,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I304" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K304" s="0">
         <x:v>5</x:v>
@@ -10538,7 +10538,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I305" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K305" s="0">
         <x:v>5</x:v>
@@ -10564,7 +10564,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I306" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K306" s="0">
         <x:v>5</x:v>
@@ -10590,7 +10590,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I307" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K307" s="0">
         <x:v>5</x:v>
@@ -10642,7 +10642,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I309" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K309" s="0">
         <x:v>5</x:v>
@@ -10668,7 +10668,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I310" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K310" s="0">
         <x:v>5</x:v>
@@ -10694,7 +10694,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I311" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K311" s="0">
         <x:v>5</x:v>
@@ -10720,7 +10720,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I312" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K312" s="0">
         <x:v>5</x:v>
@@ -10746,7 +10746,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I313" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K313" s="0">
         <x:v>5</x:v>
@@ -10772,7 +10772,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I314" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K314" s="0">
         <x:v>5</x:v>
@@ -10798,7 +10798,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I315" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K315" s="0">
         <x:v>5</x:v>
@@ -10824,7 +10824,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I316" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K316" s="0">
         <x:v>5</x:v>
@@ -10850,7 +10850,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I317" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K317" s="0">
         <x:v>5</x:v>
@@ -10876,7 +10876,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I318" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K318" s="0">
         <x:v>5</x:v>
@@ -10902,7 +10902,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I319" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K319" s="0">
         <x:v>5</x:v>
@@ -10928,7 +10928,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I320" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K320" s="0">
         <x:v>5</x:v>
@@ -10954,7 +10954,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I321" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K321" s="0">
         <x:v>5</x:v>
@@ -10980,7 +10980,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I322" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K322" s="0">
         <x:v>5</x:v>
@@ -11006,7 +11006,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I323" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K323" s="0">
         <x:v>5</x:v>
@@ -11032,7 +11032,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I324" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K324" s="0">
         <x:v>5</x:v>
@@ -11058,7 +11058,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I325" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K325" s="0">
         <x:v>5</x:v>
@@ -11084,7 +11084,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I326" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K326" s="0">
         <x:v>5</x:v>
@@ -11110,7 +11110,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I327" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K327" s="0">
         <x:v>5</x:v>
@@ -11136,7 +11136,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I328" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K328" s="0">
         <x:v>5</x:v>
@@ -11162,7 +11162,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I329" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K329" s="0">
         <x:v>5</x:v>
@@ -11188,7 +11188,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I330" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K330" s="0">
         <x:v>5</x:v>
@@ -11214,7 +11214,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I331" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K331" s="0">
         <x:v>5</x:v>
@@ -11240,7 +11240,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I332" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K332" s="0">
         <x:v>5</x:v>
@@ -11266,7 +11266,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I333" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K333" s="0">
         <x:v>5</x:v>
@@ -11292,7 +11292,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I334" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K334" s="0">
         <x:v>5</x:v>
@@ -11318,7 +11318,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I335" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K335" s="0">
         <x:v>5</x:v>
@@ -11344,7 +11344,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I336" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K336" s="0">
         <x:v>5</x:v>
@@ -11370,7 +11370,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I337" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K337" s="0">
         <x:v>5</x:v>
@@ -11396,7 +11396,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I338" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K338" s="0">
         <x:v>5</x:v>
@@ -11422,7 +11422,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I339" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K339" s="0">
         <x:v>5</x:v>
@@ -11448,7 +11448,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I340" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K340" s="0">
         <x:v>5</x:v>
@@ -11474,7 +11474,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I341" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K341" s="0">
         <x:v>5</x:v>
@@ -11526,7 +11526,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I343" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K343" s="0">
         <x:v>5</x:v>
@@ -11552,7 +11552,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I344" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K344" s="0">
         <x:v>5</x:v>
@@ -11578,7 +11578,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I345" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K345" s="0">
         <x:v>5</x:v>
@@ -11604,7 +11604,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I346" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K346" s="0">
         <x:v>5</x:v>
@@ -11630,7 +11630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I347" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K347" s="0">
         <x:v>5</x:v>
@@ -11656,7 +11656,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I348" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K348" s="0">
         <x:v>5</x:v>
@@ -11682,7 +11682,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I349" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K349" s="0">
         <x:v>5</x:v>
@@ -11708,7 +11708,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I350" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K350" s="0">
         <x:v>5</x:v>
@@ -11734,7 +11734,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I351" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K351" s="0">
         <x:v>5</x:v>
@@ -11760,7 +11760,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I352" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K352" s="0">
         <x:v>5</x:v>
@@ -11786,7 +11786,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I353" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K353" s="0">
         <x:v>5</x:v>
@@ -11812,7 +11812,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I354" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K354" s="0">
         <x:v>5</x:v>
@@ -11838,7 +11838,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I355" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K355" s="0">
         <x:v>5</x:v>
@@ -11864,7 +11864,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I356" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K356" s="0">
         <x:v>5</x:v>
@@ -11890,7 +11890,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I357" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K357" s="0">
         <x:v>5</x:v>
@@ -11916,7 +11916,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I358" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K358" s="0">
         <x:v>5</x:v>
@@ -11942,7 +11942,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I359" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K359" s="0">
         <x:v>5</x:v>
@@ -11968,7 +11968,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I360" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K360" s="0">
         <x:v>5</x:v>
@@ -11994,7 +11994,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I361" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K361" s="0">
         <x:v>5</x:v>
@@ -12020,7 +12020,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I362" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K362" s="0">
         <x:v>5</x:v>
@@ -12046,7 +12046,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I363" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K363" s="0">
         <x:v>5</x:v>
@@ -12072,7 +12072,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I364" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K364" s="0">
         <x:v>5</x:v>
@@ -12098,7 +12098,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I365" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K365" s="0">
         <x:v>5</x:v>
@@ -12124,7 +12124,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I366" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K366" s="0">
         <x:v>5</x:v>
@@ -12150,7 +12150,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I367" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K367" s="0">
         <x:v>5</x:v>
@@ -12176,7 +12176,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I368" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K368" s="0">
         <x:v>5</x:v>
@@ -12202,7 +12202,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I369" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K369" s="0">
         <x:v>5</x:v>
@@ -12228,7 +12228,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I370" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K370" s="0">
         <x:v>5</x:v>
@@ -12254,7 +12254,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I371" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K371" s="0">
         <x:v>5</x:v>
@@ -12280,7 +12280,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I372" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K372" s="0">
         <x:v>5</x:v>
@@ -12306,7 +12306,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I373" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K373" s="0">
         <x:v>5</x:v>
@@ -12332,7 +12332,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I374" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K374" s="0">
         <x:v>5</x:v>
@@ -12358,7 +12358,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I375" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K375" s="0">
         <x:v>5</x:v>
@@ -12384,7 +12384,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I376" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K376" s="0">
         <x:v>5</x:v>
@@ -12436,7 +12436,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I378" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K378" s="0">
         <x:v>5</x:v>
@@ -12462,7 +12462,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I379" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K379" s="0">
         <x:v>5</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I380" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K380" s="0">
         <x:v>5</x:v>
@@ -12514,7 +12514,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I381" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K381" s="0">
         <x:v>5</x:v>
@@ -12540,7 +12540,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I382" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K382" s="0">
         <x:v>5</x:v>
@@ -12566,7 +12566,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I383" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K383" s="0">
         <x:v>5</x:v>
@@ -12592,7 +12592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I384" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K384" s="0">
         <x:v>5</x:v>
@@ -12618,7 +12618,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I385" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K385" s="0">
         <x:v>5</x:v>
@@ -12644,7 +12644,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I386" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K386" s="0">
         <x:v>5</x:v>
@@ -12670,7 +12670,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I387" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K387" s="0">
         <x:v>5</x:v>
@@ -12696,7 +12696,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I388" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K388" s="0">
         <x:v>5</x:v>
@@ -12722,7 +12722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I389" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K389" s="0">
         <x:v>5</x:v>
@@ -12748,7 +12748,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I390" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K390" s="0">
         <x:v>5</x:v>
@@ -12774,7 +12774,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I391" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K391" s="0">
         <x:v>5</x:v>
@@ -12800,7 +12800,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I392" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K392" s="0">
         <x:v>5</x:v>
@@ -12826,7 +12826,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I393" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K393" s="0">
         <x:v>5</x:v>
@@ -12852,7 +12852,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I394" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K394" s="0">
         <x:v>5</x:v>
@@ -12878,7 +12878,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I395" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K395" s="0">
         <x:v>5</x:v>
@@ -12904,7 +12904,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I396" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K396" s="0">
         <x:v>5</x:v>
@@ -12930,7 +12930,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I397" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K397" s="0">
         <x:v>5</x:v>
@@ -12956,7 +12956,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I398" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K398" s="0">
         <x:v>5</x:v>
@@ -12982,7 +12982,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I399" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K399" s="0">
         <x:v>5</x:v>
@@ -13008,7 +13008,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I400" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K400" s="0">
         <x:v>5</x:v>
@@ -13034,7 +13034,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I401" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K401" s="0">
         <x:v>5</x:v>
@@ -13060,7 +13060,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I402" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K402" s="0">
         <x:v>5</x:v>
@@ -13086,7 +13086,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I403" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K403" s="0">
         <x:v>5</x:v>
@@ -13112,7 +13112,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I404" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K404" s="0">
         <x:v>5</x:v>
@@ -13138,7 +13138,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I405" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K405" s="0">
         <x:v>5</x:v>
@@ -13164,7 +13164,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I406" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K406" s="0">
         <x:v>5</x:v>
@@ -13190,7 +13190,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I407" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K407" s="0">
         <x:v>5</x:v>
@@ -13216,7 +13216,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I408" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K408" s="0">
         <x:v>5</x:v>
@@ -13242,7 +13242,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I409" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K409" s="0">
         <x:v>5</x:v>
@@ -13268,7 +13268,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I410" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K410" s="0">
         <x:v>5</x:v>
@@ -13294,7 +13294,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I411" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K411" s="0">
         <x:v>5</x:v>
@@ -13346,7 +13346,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I413" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K413" s="0">
         <x:v>5</x:v>
@@ -13372,7 +13372,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I414" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K414" s="0">
         <x:v>5</x:v>
@@ -13398,7 +13398,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I415" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K415" s="0">
         <x:v>5</x:v>
@@ -13424,7 +13424,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I416" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K416" s="0">
         <x:v>5</x:v>
@@ -13450,7 +13450,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I417" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K417" s="0">
         <x:v>5</x:v>
@@ -13476,7 +13476,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I418" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K418" s="0">
         <x:v>5</x:v>
@@ -13502,7 +13502,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I419" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K419" s="0">
         <x:v>5</x:v>
@@ -13528,7 +13528,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I420" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K420" s="0">
         <x:v>5</x:v>
@@ -13554,7 +13554,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I421" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K421" s="0">
         <x:v>5</x:v>
@@ -13580,7 +13580,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I422" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K422" s="0">
         <x:v>5</x:v>
@@ -13606,7 +13606,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I423" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K423" s="0">
         <x:v>5</x:v>
@@ -13632,7 +13632,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I424" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K424" s="0">
         <x:v>5</x:v>
@@ -13658,7 +13658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I425" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K425" s="0">
         <x:v>5</x:v>
@@ -13684,7 +13684,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I426" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K426" s="0">
         <x:v>5</x:v>
@@ -13710,7 +13710,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I427" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K427" s="0">
         <x:v>5</x:v>
@@ -13736,7 +13736,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I428" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K428" s="0">
         <x:v>5</x:v>
@@ -13762,7 +13762,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I429" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K429" s="0">
         <x:v>5</x:v>
@@ -13788,7 +13788,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I430" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K430" s="0">
         <x:v>5</x:v>
@@ -13814,7 +13814,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I431" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K431" s="0">
         <x:v>5</x:v>
@@ -13840,7 +13840,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I432" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K432" s="0">
         <x:v>5</x:v>
@@ -13866,7 +13866,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I433" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K433" s="0">
         <x:v>5</x:v>
@@ -13892,7 +13892,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I434" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K434" s="0">
         <x:v>5</x:v>
@@ -13918,7 +13918,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I435" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K435" s="0">
         <x:v>5</x:v>
@@ -13944,7 +13944,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I436" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K436" s="0">
         <x:v>5</x:v>
@@ -13970,7 +13970,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I437" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K437" s="0">
         <x:v>5</x:v>
@@ -13996,7 +13996,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I438" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K438" s="0">
         <x:v>5</x:v>
@@ -14022,7 +14022,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I439" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K439" s="0">
         <x:v>5</x:v>
@@ -14048,7 +14048,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I440" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K440" s="0">
         <x:v>5</x:v>
@@ -14074,7 +14074,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I441" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K441" s="0">
         <x:v>5</x:v>
@@ -14100,7 +14100,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I442" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K442" s="0">
         <x:v>5</x:v>
@@ -14126,7 +14126,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I443" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K443" s="0">
         <x:v>5</x:v>
@@ -14152,7 +14152,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I444" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K444" s="0">
         <x:v>5</x:v>
@@ -14178,7 +14178,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I445" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K445" s="0">
         <x:v>5</x:v>
@@ -14204,7 +14204,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I446" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K446" s="0">
         <x:v>5</x:v>
@@ -14256,7 +14256,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I448" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K448" s="0">
         <x:v>5</x:v>
@@ -14282,7 +14282,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I449" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K449" s="0">
         <x:v>5</x:v>
@@ -14308,7 +14308,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I450" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K450" s="0">
         <x:v>5</x:v>
@@ -14334,7 +14334,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I451" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K451" s="0">
         <x:v>5</x:v>
@@ -14360,7 +14360,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I452" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K452" s="0">
         <x:v>5</x:v>
@@ -14386,7 +14386,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I453" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K453" s="0">
         <x:v>5</x:v>
@@ -14412,7 +14412,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I454" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K454" s="0">
         <x:v>5</x:v>
@@ -14438,7 +14438,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I455" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K455" s="0">
         <x:v>5</x:v>
@@ -14464,7 +14464,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I456" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K456" s="0">
         <x:v>5</x:v>
@@ -14490,7 +14490,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I457" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K457" s="0">
         <x:v>5</x:v>
@@ -14516,7 +14516,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I458" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K458" s="0">
         <x:v>5</x:v>
@@ -14542,7 +14542,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I459" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K459" s="0">
         <x:v>5</x:v>
@@ -14568,7 +14568,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I460" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K460" s="0">
         <x:v>5</x:v>
@@ -14594,7 +14594,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I461" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K461" s="0">
         <x:v>5</x:v>
@@ -14620,7 +14620,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I462" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K462" s="0">
         <x:v>5</x:v>
@@ -14646,7 +14646,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I463" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K463" s="0">
         <x:v>5</x:v>
@@ -14672,7 +14672,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I464" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K464" s="0">
         <x:v>5</x:v>
@@ -14698,7 +14698,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I465" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K465" s="0">
         <x:v>5</x:v>
@@ -14724,7 +14724,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I466" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K466" s="0">
         <x:v>5</x:v>
@@ -14750,7 +14750,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I467" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K467" s="0">
         <x:v>5</x:v>
@@ -14776,7 +14776,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I468" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K468" s="0">
         <x:v>5</x:v>
@@ -14802,7 +14802,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I469" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K469" s="0">
         <x:v>5</x:v>
@@ -14828,7 +14828,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I470" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K470" s="0">
         <x:v>5</x:v>
@@ -14854,7 +14854,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I471" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K471" s="0">
         <x:v>5</x:v>
@@ -14880,7 +14880,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I472" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K472" s="0">
         <x:v>5</x:v>
@@ -14906,7 +14906,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I473" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K473" s="0">
         <x:v>5</x:v>
@@ -14932,7 +14932,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I474" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K474" s="0">
         <x:v>5</x:v>
@@ -14958,7 +14958,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I475" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K475" s="0">
         <x:v>5</x:v>
@@ -14984,7 +14984,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I476" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K476" s="0">
         <x:v>5</x:v>
@@ -15010,7 +15010,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I477" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K477" s="0">
         <x:v>5</x:v>
@@ -15036,7 +15036,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I478" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K478" s="0">
         <x:v>5</x:v>
@@ -15062,7 +15062,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I479" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K479" s="0">
         <x:v>5</x:v>
@@ -15088,7 +15088,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I480" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K480" s="0">
         <x:v>5</x:v>
@@ -15114,7 +15114,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I481" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="K481" s="0">
         <x:v>5</x:v>

--- a/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
+++ b/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
@@ -114,6 +114,9 @@
     <x:t>HP S5 Pro 524pf FHD MNTR</x:t>
   </x:si>
   <x:si>
+    <x:t>Max Qty: 2012</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -141,6 +144,9 @@
     <x:t>55623728-HP EliteBook 8 G2a 14 (14" Touch, Ryzen 5, 16GB, 512GB)</x:t>
   </x:si>
   <x:si>
+    <x:t>Max Qty: 880</x:t>
+  </x:si>
+  <x:si>
     <x:t>4.01</x:t>
   </x:si>
   <x:si>
@@ -445,6 +451,9 @@
   </x:si>
   <x:si>
     <x:t>55623739-HP EliteBook 8 G2a 14 (14" Touch, Ryzen 7, 32GB, 512GB)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Max Qty: 31</x:t>
   </x:si>
   <x:si>
     <x:t>5.01</x:t>
@@ -2683,7 +2692,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2012</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>213.92</x:v>
@@ -2691,25 +2700,28 @@
       <x:c r="K3" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="W3" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:27">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2012</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>184.78</x:v>
@@ -2717,25 +2729,28 @@
       <x:c r="K4" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="W4" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:27">
       <x:c r="A5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>2012</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>240</x:v>
@@ -2743,25 +2758,28 @@
       <x:c r="K5" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="W5" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:27">
       <x:c r="A6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>2387.94</x:v>
@@ -2769,22 +2787,25 @@
       <x:c r="K6" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W6" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:27">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1</x:v>
@@ -2801,16 +2822,16 @@
     </x:row>
     <x:row r="8" spans="1:27">
       <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1</x:v>
@@ -2827,16 +2848,16 @@
     </x:row>
     <x:row r="9" spans="1:27">
       <x:c r="A9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1</x:v>
@@ -2853,16 +2874,16 @@
     </x:row>
     <x:row r="10" spans="1:27">
       <x:c r="A10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>1</x:v>
@@ -2879,16 +2900,16 @@
     </x:row>
     <x:row r="11" spans="1:27">
       <x:c r="A11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1</x:v>
@@ -2905,16 +2926,16 @@
     </x:row>
     <x:row r="12" spans="1:27">
       <x:c r="A12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1</x:v>
@@ -2931,16 +2952,16 @@
     </x:row>
     <x:row r="13" spans="1:27">
       <x:c r="A13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1</x:v>
@@ -2957,16 +2978,16 @@
     </x:row>
     <x:row r="14" spans="1:27">
       <x:c r="A14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>1</x:v>
@@ -2983,16 +3004,16 @@
     </x:row>
     <x:row r="15" spans="1:27">
       <x:c r="A15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>1</x:v>
@@ -3009,16 +3030,16 @@
     </x:row>
     <x:row r="16" spans="1:27">
       <x:c r="A16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F16" s="0">
         <x:v>1</x:v>
@@ -3035,16 +3056,16 @@
     </x:row>
     <x:row r="17" spans="1:27">
       <x:c r="A17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1</x:v>
@@ -3061,16 +3082,16 @@
     </x:row>
     <x:row r="18" spans="1:27">
       <x:c r="A18" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1</x:v>
@@ -3087,16 +3108,16 @@
     </x:row>
     <x:row r="19" spans="1:27">
       <x:c r="A19" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1</x:v>
@@ -3113,16 +3134,16 @@
     </x:row>
     <x:row r="20" spans="1:27">
       <x:c r="A20" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1</x:v>
@@ -3139,16 +3160,16 @@
     </x:row>
     <x:row r="21" spans="1:27">
       <x:c r="A21" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1</x:v>
@@ -3165,16 +3186,16 @@
     </x:row>
     <x:row r="22" spans="1:27">
       <x:c r="A22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1</x:v>
@@ -3191,16 +3212,16 @@
     </x:row>
     <x:row r="23" spans="1:27">
       <x:c r="A23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>1</x:v>
@@ -3217,16 +3238,16 @@
     </x:row>
     <x:row r="24" spans="1:27">
       <x:c r="A24" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>1</x:v>
@@ -3243,16 +3264,16 @@
     </x:row>
     <x:row r="25" spans="1:27">
       <x:c r="A25" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>1</x:v>
@@ -3269,16 +3290,16 @@
     </x:row>
     <x:row r="26" spans="1:27">
       <x:c r="A26" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1</x:v>
@@ -3295,16 +3316,16 @@
     </x:row>
     <x:row r="27" spans="1:27">
       <x:c r="A27" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1</x:v>
@@ -3321,16 +3342,16 @@
     </x:row>
     <x:row r="28" spans="1:27">
       <x:c r="A28" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1</x:v>
@@ -3347,16 +3368,16 @@
     </x:row>
     <x:row r="29" spans="1:27">
       <x:c r="A29" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>1</x:v>
@@ -3373,16 +3394,16 @@
     </x:row>
     <x:row r="30" spans="1:27">
       <x:c r="A30" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F30" s="0">
         <x:v>1</x:v>
@@ -3399,16 +3420,16 @@
     </x:row>
     <x:row r="31" spans="1:27">
       <x:c r="A31" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1</x:v>
@@ -3425,16 +3446,16 @@
     </x:row>
     <x:row r="32" spans="1:27">
       <x:c r="A32" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F32" s="0">
         <x:v>1</x:v>
@@ -3451,16 +3472,16 @@
     </x:row>
     <x:row r="33" spans="1:27">
       <x:c r="A33" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F33" s="0">
         <x:v>1</x:v>
@@ -3477,16 +3498,16 @@
     </x:row>
     <x:row r="34" spans="1:27">
       <x:c r="A34" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F34" s="0">
         <x:v>1</x:v>
@@ -3503,16 +3524,16 @@
     </x:row>
     <x:row r="35" spans="1:27">
       <x:c r="A35" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F35" s="0">
         <x:v>1</x:v>
@@ -3529,16 +3550,16 @@
     </x:row>
     <x:row r="36" spans="1:27">
       <x:c r="A36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F36" s="0">
         <x:v>1</x:v>
@@ -3555,16 +3576,16 @@
     </x:row>
     <x:row r="37" spans="1:27">
       <x:c r="A37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>1</x:v>
@@ -3581,16 +3602,16 @@
     </x:row>
     <x:row r="38" spans="1:27">
       <x:c r="A38" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F38" s="0">
         <x:v>1</x:v>
@@ -3607,16 +3628,16 @@
     </x:row>
     <x:row r="39" spans="1:27">
       <x:c r="A39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F39" s="0">
         <x:v>1</x:v>
@@ -3633,19 +3654,19 @@
     </x:row>
     <x:row r="40" spans="1:27">
       <x:c r="A40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>3014.2</x:v>
@@ -3653,22 +3674,25 @@
       <x:c r="K40" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R40" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W40" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:27">
       <x:c r="A41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F41" s="0">
         <x:v>1</x:v>
@@ -3685,16 +3709,16 @@
     </x:row>
     <x:row r="42" spans="1:27">
       <x:c r="A42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F42" s="0">
         <x:v>1</x:v>
@@ -3711,16 +3735,16 @@
     </x:row>
     <x:row r="43" spans="1:27">
       <x:c r="A43" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F43" s="0">
         <x:v>1</x:v>
@@ -3737,16 +3761,16 @@
     </x:row>
     <x:row r="44" spans="1:27">
       <x:c r="A44" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F44" s="0">
         <x:v>1</x:v>
@@ -3763,16 +3787,16 @@
     </x:row>
     <x:row r="45" spans="1:27">
       <x:c r="A45" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F45" s="0">
         <x:v>1</x:v>
@@ -3789,16 +3813,16 @@
     </x:row>
     <x:row r="46" spans="1:27">
       <x:c r="A46" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F46" s="0">
         <x:v>1</x:v>
@@ -3815,16 +3839,16 @@
     </x:row>
     <x:row r="47" spans="1:27">
       <x:c r="A47" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F47" s="0">
         <x:v>1</x:v>
@@ -3841,16 +3865,16 @@
     </x:row>
     <x:row r="48" spans="1:27">
       <x:c r="A48" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F48" s="0">
         <x:v>1</x:v>
@@ -3867,16 +3891,16 @@
     </x:row>
     <x:row r="49" spans="1:27">
       <x:c r="A49" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F49" s="0">
         <x:v>1</x:v>
@@ -3893,16 +3917,16 @@
     </x:row>
     <x:row r="50" spans="1:27">
       <x:c r="A50" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F50" s="0">
         <x:v>1</x:v>
@@ -3919,16 +3943,16 @@
     </x:row>
     <x:row r="51" spans="1:27">
       <x:c r="A51" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F51" s="0">
         <x:v>1</x:v>
@@ -3945,16 +3969,16 @@
     </x:row>
     <x:row r="52" spans="1:27">
       <x:c r="A52" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F52" s="0">
         <x:v>1</x:v>
@@ -3971,16 +3995,16 @@
     </x:row>
     <x:row r="53" spans="1:27">
       <x:c r="A53" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F53" s="0">
         <x:v>1</x:v>
@@ -3997,16 +4021,16 @@
     </x:row>
     <x:row r="54" spans="1:27">
       <x:c r="A54" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F54" s="0">
         <x:v>1</x:v>
@@ -4023,16 +4047,16 @@
     </x:row>
     <x:row r="55" spans="1:27">
       <x:c r="A55" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F55" s="0">
         <x:v>1</x:v>
@@ -4049,16 +4073,16 @@
     </x:row>
     <x:row r="56" spans="1:27">
       <x:c r="A56" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F56" s="0">
         <x:v>1</x:v>
@@ -4075,16 +4099,16 @@
     </x:row>
     <x:row r="57" spans="1:27">
       <x:c r="A57" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F57" s="0">
         <x:v>1</x:v>
@@ -4101,16 +4125,16 @@
     </x:row>
     <x:row r="58" spans="1:27">
       <x:c r="A58" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F58" s="0">
         <x:v>1</x:v>
@@ -4127,16 +4151,16 @@
     </x:row>
     <x:row r="59" spans="1:27">
       <x:c r="A59" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F59" s="0">
         <x:v>1</x:v>
@@ -4153,16 +4177,16 @@
     </x:row>
     <x:row r="60" spans="1:27">
       <x:c r="A60" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F60" s="0">
         <x:v>1</x:v>
@@ -4179,16 +4203,16 @@
     </x:row>
     <x:row r="61" spans="1:27">
       <x:c r="A61" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F61" s="0">
         <x:v>1</x:v>
@@ -4205,16 +4229,16 @@
     </x:row>
     <x:row r="62" spans="1:27">
       <x:c r="A62" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F62" s="0">
         <x:v>1</x:v>
@@ -4231,16 +4255,16 @@
     </x:row>
     <x:row r="63" spans="1:27">
       <x:c r="A63" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F63" s="0">
         <x:v>1</x:v>
@@ -4257,16 +4281,16 @@
     </x:row>
     <x:row r="64" spans="1:27">
       <x:c r="A64" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F64" s="0">
         <x:v>1</x:v>
@@ -4283,16 +4307,16 @@
     </x:row>
     <x:row r="65" spans="1:27">
       <x:c r="A65" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F65" s="0">
         <x:v>1</x:v>
@@ -4309,16 +4333,16 @@
     </x:row>
     <x:row r="66" spans="1:27">
       <x:c r="A66" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F66" s="0">
         <x:v>1</x:v>
@@ -4335,16 +4359,16 @@
     </x:row>
     <x:row r="67" spans="1:27">
       <x:c r="A67" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F67" s="0">
         <x:v>1</x:v>
@@ -4361,16 +4385,16 @@
     </x:row>
     <x:row r="68" spans="1:27">
       <x:c r="A68" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F68" s="0">
         <x:v>1</x:v>
@@ -4387,16 +4411,16 @@
     </x:row>
     <x:row r="69" spans="1:27">
       <x:c r="A69" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F69" s="0">
         <x:v>1</x:v>
@@ -4413,16 +4437,16 @@
     </x:row>
     <x:row r="70" spans="1:27">
       <x:c r="A70" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F70" s="0">
         <x:v>1</x:v>
@@ -4439,16 +4463,16 @@
     </x:row>
     <x:row r="71" spans="1:27">
       <x:c r="A71" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F71" s="0">
         <x:v>1</x:v>
@@ -4465,16 +4489,16 @@
     </x:row>
     <x:row r="72" spans="1:27">
       <x:c r="A72" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F72" s="0">
         <x:v>1</x:v>
@@ -4491,16 +4515,16 @@
     </x:row>
     <x:row r="73" spans="1:27">
       <x:c r="A73" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F73" s="0">
         <x:v>1</x:v>
@@ -4517,19 +4541,19 @@
     </x:row>
     <x:row r="74" spans="1:27">
       <x:c r="A74" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I74" s="0">
         <x:v>2380.27</x:v>
@@ -4537,22 +4561,25 @@
       <x:c r="K74" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R74" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W74" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:27">
       <x:c r="A75" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F75" s="0">
         <x:v>1</x:v>
@@ -4569,16 +4596,16 @@
     </x:row>
     <x:row r="76" spans="1:27">
       <x:c r="A76" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F76" s="0">
         <x:v>1</x:v>
@@ -4595,16 +4622,16 @@
     </x:row>
     <x:row r="77" spans="1:27">
       <x:c r="A77" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F77" s="0">
         <x:v>1</x:v>
@@ -4621,16 +4648,16 @@
     </x:row>
     <x:row r="78" spans="1:27">
       <x:c r="A78" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F78" s="0">
         <x:v>1</x:v>
@@ -4647,16 +4674,16 @@
     </x:row>
     <x:row r="79" spans="1:27">
       <x:c r="A79" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F79" s="0">
         <x:v>1</x:v>
@@ -4673,16 +4700,16 @@
     </x:row>
     <x:row r="80" spans="1:27">
       <x:c r="A80" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F80" s="0">
         <x:v>1</x:v>
@@ -4699,16 +4726,16 @@
     </x:row>
     <x:row r="81" spans="1:27">
       <x:c r="A81" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F81" s="0">
         <x:v>1</x:v>
@@ -4725,16 +4752,16 @@
     </x:row>
     <x:row r="82" spans="1:27">
       <x:c r="A82" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F82" s="0">
         <x:v>1</x:v>
@@ -4751,16 +4778,16 @@
     </x:row>
     <x:row r="83" spans="1:27">
       <x:c r="A83" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F83" s="0">
         <x:v>1</x:v>
@@ -4777,16 +4804,16 @@
     </x:row>
     <x:row r="84" spans="1:27">
       <x:c r="A84" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F84" s="0">
         <x:v>1</x:v>
@@ -4803,16 +4830,16 @@
     </x:row>
     <x:row r="85" spans="1:27">
       <x:c r="A85" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F85" s="0">
         <x:v>1</x:v>
@@ -4829,16 +4856,16 @@
     </x:row>
     <x:row r="86" spans="1:27">
       <x:c r="A86" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F86" s="0">
         <x:v>1</x:v>
@@ -4855,16 +4882,16 @@
     </x:row>
     <x:row r="87" spans="1:27">
       <x:c r="A87" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F87" s="0">
         <x:v>1</x:v>
@@ -4881,16 +4908,16 @@
     </x:row>
     <x:row r="88" spans="1:27">
       <x:c r="A88" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F88" s="0">
         <x:v>1</x:v>
@@ -4907,16 +4934,16 @@
     </x:row>
     <x:row r="89" spans="1:27">
       <x:c r="A89" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F89" s="0">
         <x:v>1</x:v>
@@ -4933,16 +4960,16 @@
     </x:row>
     <x:row r="90" spans="1:27">
       <x:c r="A90" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F90" s="0">
         <x:v>1</x:v>
@@ -4959,16 +4986,16 @@
     </x:row>
     <x:row r="91" spans="1:27">
       <x:c r="A91" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F91" s="0">
         <x:v>1</x:v>
@@ -4985,16 +5012,16 @@
     </x:row>
     <x:row r="92" spans="1:27">
       <x:c r="A92" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F92" s="0">
         <x:v>1</x:v>
@@ -5011,16 +5038,16 @@
     </x:row>
     <x:row r="93" spans="1:27">
       <x:c r="A93" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F93" s="0">
         <x:v>1</x:v>
@@ -5037,16 +5064,16 @@
     </x:row>
     <x:row r="94" spans="1:27">
       <x:c r="A94" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F94" s="0">
         <x:v>1</x:v>
@@ -5063,16 +5090,16 @@
     </x:row>
     <x:row r="95" spans="1:27">
       <x:c r="A95" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F95" s="0">
         <x:v>1</x:v>
@@ -5089,16 +5116,16 @@
     </x:row>
     <x:row r="96" spans="1:27">
       <x:c r="A96" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F96" s="0">
         <x:v>1</x:v>
@@ -5115,16 +5142,16 @@
     </x:row>
     <x:row r="97" spans="1:27">
       <x:c r="A97" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F97" s="0">
         <x:v>1</x:v>
@@ -5141,16 +5168,16 @@
     </x:row>
     <x:row r="98" spans="1:27">
       <x:c r="A98" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F98" s="0">
         <x:v>1</x:v>
@@ -5167,16 +5194,16 @@
     </x:row>
     <x:row r="99" spans="1:27">
       <x:c r="A99" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F99" s="0">
         <x:v>1</x:v>
@@ -5193,16 +5220,16 @@
     </x:row>
     <x:row r="100" spans="1:27">
       <x:c r="A100" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F100" s="0">
         <x:v>1</x:v>
@@ -5219,16 +5246,16 @@
     </x:row>
     <x:row r="101" spans="1:27">
       <x:c r="A101" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F101" s="0">
         <x:v>1</x:v>
@@ -5245,16 +5272,16 @@
     </x:row>
     <x:row r="102" spans="1:27">
       <x:c r="A102" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F102" s="0">
         <x:v>1</x:v>
@@ -5271,16 +5298,16 @@
     </x:row>
     <x:row r="103" spans="1:27">
       <x:c r="A103" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F103" s="0">
         <x:v>1</x:v>
@@ -5297,16 +5324,16 @@
     </x:row>
     <x:row r="104" spans="1:27">
       <x:c r="A104" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F104" s="0">
         <x:v>1</x:v>
@@ -5323,16 +5350,16 @@
     </x:row>
     <x:row r="105" spans="1:27">
       <x:c r="A105" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F105" s="0">
         <x:v>1</x:v>
@@ -5349,16 +5376,16 @@
     </x:row>
     <x:row r="106" spans="1:27">
       <x:c r="A106" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F106" s="0">
         <x:v>1</x:v>
@@ -5375,16 +5402,16 @@
     </x:row>
     <x:row r="107" spans="1:27">
       <x:c r="A107" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F107" s="0">
         <x:v>1</x:v>
@@ -5401,19 +5428,19 @@
     </x:row>
     <x:row r="108" spans="1:27">
       <x:c r="A108" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I108" s="0">
         <x:v>2481.87</x:v>
@@ -5421,22 +5448,25 @@
       <x:c r="K108" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R108" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W108" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:27">
       <x:c r="A109" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F109" s="0">
         <x:v>1</x:v>
@@ -5453,16 +5483,16 @@
     </x:row>
     <x:row r="110" spans="1:27">
       <x:c r="A110" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F110" s="0">
         <x:v>1</x:v>
@@ -5479,16 +5509,16 @@
     </x:row>
     <x:row r="111" spans="1:27">
       <x:c r="A111" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F111" s="0">
         <x:v>1</x:v>
@@ -5505,16 +5535,16 @@
     </x:row>
     <x:row r="112" spans="1:27">
       <x:c r="A112" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F112" s="0">
         <x:v>1</x:v>
@@ -5531,16 +5561,16 @@
     </x:row>
     <x:row r="113" spans="1:27">
       <x:c r="A113" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F113" s="0">
         <x:v>1</x:v>
@@ -5557,16 +5587,16 @@
     </x:row>
     <x:row r="114" spans="1:27">
       <x:c r="A114" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F114" s="0">
         <x:v>1</x:v>
@@ -5583,16 +5613,16 @@
     </x:row>
     <x:row r="115" spans="1:27">
       <x:c r="A115" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F115" s="0">
         <x:v>1</x:v>
@@ -5609,16 +5639,16 @@
     </x:row>
     <x:row r="116" spans="1:27">
       <x:c r="A116" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F116" s="0">
         <x:v>1</x:v>
@@ -5635,16 +5665,16 @@
     </x:row>
     <x:row r="117" spans="1:27">
       <x:c r="A117" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F117" s="0">
         <x:v>1</x:v>
@@ -5661,16 +5691,16 @@
     </x:row>
     <x:row r="118" spans="1:27">
       <x:c r="A118" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F118" s="0">
         <x:v>1</x:v>
@@ -5687,16 +5717,16 @@
     </x:row>
     <x:row r="119" spans="1:27">
       <x:c r="A119" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F119" s="0">
         <x:v>1</x:v>
@@ -5713,16 +5743,16 @@
     </x:row>
     <x:row r="120" spans="1:27">
       <x:c r="A120" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F120" s="0">
         <x:v>1</x:v>
@@ -5739,16 +5769,16 @@
     </x:row>
     <x:row r="121" spans="1:27">
       <x:c r="A121" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F121" s="0">
         <x:v>1</x:v>
@@ -5765,16 +5795,16 @@
     </x:row>
     <x:row r="122" spans="1:27">
       <x:c r="A122" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F122" s="0">
         <x:v>1</x:v>
@@ -5791,16 +5821,16 @@
     </x:row>
     <x:row r="123" spans="1:27">
       <x:c r="A123" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F123" s="0">
         <x:v>1</x:v>
@@ -5817,16 +5847,16 @@
     </x:row>
     <x:row r="124" spans="1:27">
       <x:c r="A124" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F124" s="0">
         <x:v>1</x:v>
@@ -5843,16 +5873,16 @@
     </x:row>
     <x:row r="125" spans="1:27">
       <x:c r="A125" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F125" s="0">
         <x:v>1</x:v>
@@ -5869,16 +5899,16 @@
     </x:row>
     <x:row r="126" spans="1:27">
       <x:c r="A126" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F126" s="0">
         <x:v>1</x:v>
@@ -5895,16 +5925,16 @@
     </x:row>
     <x:row r="127" spans="1:27">
       <x:c r="A127" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F127" s="0">
         <x:v>1</x:v>
@@ -5921,16 +5951,16 @@
     </x:row>
     <x:row r="128" spans="1:27">
       <x:c r="A128" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F128" s="0">
         <x:v>1</x:v>
@@ -5947,16 +5977,16 @@
     </x:row>
     <x:row r="129" spans="1:27">
       <x:c r="A129" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F129" s="0">
         <x:v>1</x:v>
@@ -5973,16 +6003,16 @@
     </x:row>
     <x:row r="130" spans="1:27">
       <x:c r="A130" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="E130" s="0" t="s">
-        <x:v>307</x:v>
       </x:c>
       <x:c r="F130" s="0">
         <x:v>1</x:v>
@@ -5999,16 +6029,16 @@
     </x:row>
     <x:row r="131" spans="1:27">
       <x:c r="A131" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F131" s="0">
         <x:v>1</x:v>
@@ -6025,16 +6055,16 @@
     </x:row>
     <x:row r="132" spans="1:27">
       <x:c r="A132" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F132" s="0">
         <x:v>1</x:v>
@@ -6051,16 +6081,16 @@
     </x:row>
     <x:row r="133" spans="1:27">
       <x:c r="A133" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F133" s="0">
         <x:v>1</x:v>
@@ -6077,16 +6107,16 @@
     </x:row>
     <x:row r="134" spans="1:27">
       <x:c r="A134" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F134" s="0">
         <x:v>1</x:v>
@@ -6103,16 +6133,16 @@
     </x:row>
     <x:row r="135" spans="1:27">
       <x:c r="A135" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F135" s="0">
         <x:v>1</x:v>
@@ -6129,16 +6159,16 @@
     </x:row>
     <x:row r="136" spans="1:27">
       <x:c r="A136" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F136" s="0">
         <x:v>1</x:v>
@@ -6155,16 +6185,16 @@
     </x:row>
     <x:row r="137" spans="1:27">
       <x:c r="A137" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F137" s="0">
         <x:v>1</x:v>
@@ -6181,16 +6211,16 @@
     </x:row>
     <x:row r="138" spans="1:27">
       <x:c r="A138" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F138" s="0">
         <x:v>1</x:v>
@@ -6207,16 +6237,16 @@
     </x:row>
     <x:row r="139" spans="1:27">
       <x:c r="A139" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F139" s="0">
         <x:v>1</x:v>
@@ -6233,16 +6263,16 @@
     </x:row>
     <x:row r="140" spans="1:27">
       <x:c r="A140" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F140" s="0">
         <x:v>1</x:v>
@@ -6259,19 +6289,19 @@
     </x:row>
     <x:row r="141" spans="1:27">
       <x:c r="A141" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F141" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I141" s="0">
         <x:v>2989.02</x:v>
@@ -6279,22 +6309,25 @@
       <x:c r="K141" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R141" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W141" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:27">
       <x:c r="A142" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F142" s="0">
         <x:v>1</x:v>
@@ -6311,16 +6344,16 @@
     </x:row>
     <x:row r="143" spans="1:27">
       <x:c r="A143" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F143" s="0">
         <x:v>1</x:v>
@@ -6337,16 +6370,16 @@
     </x:row>
     <x:row r="144" spans="1:27">
       <x:c r="A144" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F144" s="0">
         <x:v>1</x:v>
@@ -6363,16 +6396,16 @@
     </x:row>
     <x:row r="145" spans="1:27">
       <x:c r="A145" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F145" s="0">
         <x:v>1</x:v>
@@ -6389,16 +6422,16 @@
     </x:row>
     <x:row r="146" spans="1:27">
       <x:c r="A146" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F146" s="0">
         <x:v>1</x:v>
@@ -6415,16 +6448,16 @@
     </x:row>
     <x:row r="147" spans="1:27">
       <x:c r="A147" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F147" s="0">
         <x:v>1</x:v>
@@ -6441,16 +6474,16 @@
     </x:row>
     <x:row r="148" spans="1:27">
       <x:c r="A148" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F148" s="0">
         <x:v>1</x:v>
@@ -6467,16 +6500,16 @@
     </x:row>
     <x:row r="149" spans="1:27">
       <x:c r="A149" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F149" s="0">
         <x:v>1</x:v>
@@ -6493,16 +6526,16 @@
     </x:row>
     <x:row r="150" spans="1:27">
       <x:c r="A150" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F150" s="0">
         <x:v>1</x:v>
@@ -6519,16 +6552,16 @@
     </x:row>
     <x:row r="151" spans="1:27">
       <x:c r="A151" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F151" s="0">
         <x:v>1</x:v>
@@ -6545,16 +6578,16 @@
     </x:row>
     <x:row r="152" spans="1:27">
       <x:c r="A152" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F152" s="0">
         <x:v>1</x:v>
@@ -6571,16 +6604,16 @@
     </x:row>
     <x:row r="153" spans="1:27">
       <x:c r="A153" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F153" s="0">
         <x:v>1</x:v>
@@ -6597,16 +6630,16 @@
     </x:row>
     <x:row r="154" spans="1:27">
       <x:c r="A154" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F154" s="0">
         <x:v>1</x:v>
@@ -6623,16 +6656,16 @@
     </x:row>
     <x:row r="155" spans="1:27">
       <x:c r="A155" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F155" s="0">
         <x:v>1</x:v>
@@ -6649,16 +6682,16 @@
     </x:row>
     <x:row r="156" spans="1:27">
       <x:c r="A156" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F156" s="0">
         <x:v>1</x:v>
@@ -6675,16 +6708,16 @@
     </x:row>
     <x:row r="157" spans="1:27">
       <x:c r="A157" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F157" s="0">
         <x:v>1</x:v>
@@ -6701,16 +6734,16 @@
     </x:row>
     <x:row r="158" spans="1:27">
       <x:c r="A158" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F158" s="0">
         <x:v>1</x:v>
@@ -6727,16 +6760,16 @@
     </x:row>
     <x:row r="159" spans="1:27">
       <x:c r="A159" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F159" s="0">
         <x:v>1</x:v>
@@ -6753,16 +6786,16 @@
     </x:row>
     <x:row r="160" spans="1:27">
       <x:c r="A160" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F160" s="0">
         <x:v>1</x:v>
@@ -6779,16 +6812,16 @@
     </x:row>
     <x:row r="161" spans="1:27">
       <x:c r="A161" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F161" s="0">
         <x:v>1</x:v>
@@ -6805,16 +6838,16 @@
     </x:row>
     <x:row r="162" spans="1:27">
       <x:c r="A162" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F162" s="0">
         <x:v>1</x:v>
@@ -6831,16 +6864,16 @@
     </x:row>
     <x:row r="163" spans="1:27">
       <x:c r="A163" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F163" s="0">
         <x:v>1</x:v>
@@ -6857,16 +6890,16 @@
     </x:row>
     <x:row r="164" spans="1:27">
       <x:c r="A164" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F164" s="0">
         <x:v>1</x:v>
@@ -6883,16 +6916,16 @@
     </x:row>
     <x:row r="165" spans="1:27">
       <x:c r="A165" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F165" s="0">
         <x:v>1</x:v>
@@ -6909,16 +6942,16 @@
     </x:row>
     <x:row r="166" spans="1:27">
       <x:c r="A166" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F166" s="0">
         <x:v>1</x:v>
@@ -6935,16 +6968,16 @@
     </x:row>
     <x:row r="167" spans="1:27">
       <x:c r="A167" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F167" s="0">
         <x:v>1</x:v>
@@ -6961,16 +6994,16 @@
     </x:row>
     <x:row r="168" spans="1:27">
       <x:c r="A168" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F168" s="0">
         <x:v>1</x:v>
@@ -6987,16 +7020,16 @@
     </x:row>
     <x:row r="169" spans="1:27">
       <x:c r="A169" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F169" s="0">
         <x:v>1</x:v>
@@ -7013,16 +7046,16 @@
     </x:row>
     <x:row r="170" spans="1:27">
       <x:c r="A170" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F170" s="0">
         <x:v>1</x:v>
@@ -7039,16 +7072,16 @@
     </x:row>
     <x:row r="171" spans="1:27">
       <x:c r="A171" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F171" s="0">
         <x:v>1</x:v>
@@ -7065,16 +7098,16 @@
     </x:row>
     <x:row r="172" spans="1:27">
       <x:c r="A172" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F172" s="0">
         <x:v>1</x:v>
@@ -7091,16 +7124,16 @@
     </x:row>
     <x:row r="173" spans="1:27">
       <x:c r="A173" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F173" s="0">
         <x:v>1</x:v>
@@ -7117,16 +7150,16 @@
     </x:row>
     <x:row r="174" spans="1:27">
       <x:c r="A174" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F174" s="0">
         <x:v>1</x:v>
@@ -7143,19 +7176,19 @@
     </x:row>
     <x:row r="175" spans="1:27">
       <x:c r="A175" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I175" s="0">
         <x:v>1815.45</x:v>
@@ -7163,22 +7196,25 @@
       <x:c r="K175" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R175" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W175" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:27">
       <x:c r="A176" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F176" s="0">
         <x:v>1</x:v>
@@ -7195,16 +7231,16 @@
     </x:row>
     <x:row r="177" spans="1:27">
       <x:c r="A177" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F177" s="0">
         <x:v>1</x:v>
@@ -7221,16 +7257,16 @@
     </x:row>
     <x:row r="178" spans="1:27">
       <x:c r="A178" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F178" s="0">
         <x:v>1</x:v>
@@ -7247,16 +7283,16 @@
     </x:row>
     <x:row r="179" spans="1:27">
       <x:c r="A179" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F179" s="0">
         <x:v>1</x:v>
@@ -7273,16 +7309,16 @@
     </x:row>
     <x:row r="180" spans="1:27">
       <x:c r="A180" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F180" s="0">
         <x:v>1</x:v>
@@ -7299,16 +7335,16 @@
     </x:row>
     <x:row r="181" spans="1:27">
       <x:c r="A181" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F181" s="0">
         <x:v>1</x:v>
@@ -7325,16 +7361,16 @@
     </x:row>
     <x:row r="182" spans="1:27">
       <x:c r="A182" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F182" s="0">
         <x:v>1</x:v>
@@ -7351,16 +7387,16 @@
     </x:row>
     <x:row r="183" spans="1:27">
       <x:c r="A183" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F183" s="0">
         <x:v>1</x:v>
@@ -7377,16 +7413,16 @@
     </x:row>
     <x:row r="184" spans="1:27">
       <x:c r="A184" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F184" s="0">
         <x:v>1</x:v>
@@ -7403,16 +7439,16 @@
     </x:row>
     <x:row r="185" spans="1:27">
       <x:c r="A185" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F185" s="0">
         <x:v>1</x:v>
@@ -7429,16 +7465,16 @@
     </x:row>
     <x:row r="186" spans="1:27">
       <x:c r="A186" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F186" s="0">
         <x:v>1</x:v>
@@ -7455,16 +7491,16 @@
     </x:row>
     <x:row r="187" spans="1:27">
       <x:c r="A187" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F187" s="0">
         <x:v>1</x:v>
@@ -7481,16 +7517,16 @@
     </x:row>
     <x:row r="188" spans="1:27">
       <x:c r="A188" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F188" s="0">
         <x:v>1</x:v>
@@ -7507,16 +7543,16 @@
     </x:row>
     <x:row r="189" spans="1:27">
       <x:c r="A189" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F189" s="0">
         <x:v>1</x:v>
@@ -7533,16 +7569,16 @@
     </x:row>
     <x:row r="190" spans="1:27">
       <x:c r="A190" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F190" s="0">
         <x:v>1</x:v>
@@ -7559,16 +7595,16 @@
     </x:row>
     <x:row r="191" spans="1:27">
       <x:c r="A191" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F191" s="0">
         <x:v>1</x:v>
@@ -7585,16 +7621,16 @@
     </x:row>
     <x:row r="192" spans="1:27">
       <x:c r="A192" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F192" s="0">
         <x:v>1</x:v>
@@ -7611,16 +7647,16 @@
     </x:row>
     <x:row r="193" spans="1:27">
       <x:c r="A193" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F193" s="0">
         <x:v>1</x:v>
@@ -7637,16 +7673,16 @@
     </x:row>
     <x:row r="194" spans="1:27">
       <x:c r="A194" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F194" s="0">
         <x:v>1</x:v>
@@ -7663,16 +7699,16 @@
     </x:row>
     <x:row r="195" spans="1:27">
       <x:c r="A195" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F195" s="0">
         <x:v>1</x:v>
@@ -7689,16 +7725,16 @@
     </x:row>
     <x:row r="196" spans="1:27">
       <x:c r="A196" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F196" s="0">
         <x:v>1</x:v>
@@ -7715,16 +7751,16 @@
     </x:row>
     <x:row r="197" spans="1:27">
       <x:c r="A197" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F197" s="0">
         <x:v>1</x:v>
@@ -7741,16 +7777,16 @@
     </x:row>
     <x:row r="198" spans="1:27">
       <x:c r="A198" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F198" s="0">
         <x:v>1</x:v>
@@ -7767,16 +7803,16 @@
     </x:row>
     <x:row r="199" spans="1:27">
       <x:c r="A199" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F199" s="0">
         <x:v>1</x:v>
@@ -7793,16 +7829,16 @@
     </x:row>
     <x:row r="200" spans="1:27">
       <x:c r="A200" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F200" s="0">
         <x:v>1</x:v>
@@ -7819,16 +7855,16 @@
     </x:row>
     <x:row r="201" spans="1:27">
       <x:c r="A201" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F201" s="0">
         <x:v>1</x:v>
@@ -7845,16 +7881,16 @@
     </x:row>
     <x:row r="202" spans="1:27">
       <x:c r="A202" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F202" s="0">
         <x:v>1</x:v>
@@ -7871,16 +7907,16 @@
     </x:row>
     <x:row r="203" spans="1:27">
       <x:c r="A203" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F203" s="0">
         <x:v>1</x:v>
@@ -7897,16 +7933,16 @@
     </x:row>
     <x:row r="204" spans="1:27">
       <x:c r="A204" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F204" s="0">
         <x:v>1</x:v>
@@ -7923,16 +7959,16 @@
     </x:row>
     <x:row r="205" spans="1:27">
       <x:c r="A205" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F205" s="0">
         <x:v>1</x:v>
@@ -7949,16 +7985,16 @@
     </x:row>
     <x:row r="206" spans="1:27">
       <x:c r="A206" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F206" s="0">
         <x:v>1</x:v>
@@ -7975,16 +8011,16 @@
     </x:row>
     <x:row r="207" spans="1:27">
       <x:c r="A207" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F207" s="0">
         <x:v>1</x:v>
@@ -8001,19 +8037,19 @@
     </x:row>
     <x:row r="208" spans="1:27">
       <x:c r="A208" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F208" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I208" s="0">
         <x:v>1871</x:v>
@@ -8021,22 +8057,25 @@
       <x:c r="K208" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R208" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W208" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:27">
       <x:c r="A209" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F209" s="0">
         <x:v>1</x:v>
@@ -8053,16 +8092,16 @@
     </x:row>
     <x:row r="210" spans="1:27">
       <x:c r="A210" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F210" s="0">
         <x:v>1</x:v>
@@ -8079,16 +8118,16 @@
     </x:row>
     <x:row r="211" spans="1:27">
       <x:c r="A211" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F211" s="0">
         <x:v>1</x:v>
@@ -8105,16 +8144,16 @@
     </x:row>
     <x:row r="212" spans="1:27">
       <x:c r="A212" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F212" s="0">
         <x:v>1</x:v>
@@ -8131,16 +8170,16 @@
     </x:row>
     <x:row r="213" spans="1:27">
       <x:c r="A213" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F213" s="0">
         <x:v>1</x:v>
@@ -8157,16 +8196,16 @@
     </x:row>
     <x:row r="214" spans="1:27">
       <x:c r="A214" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F214" s="0">
         <x:v>1</x:v>
@@ -8183,16 +8222,16 @@
     </x:row>
     <x:row r="215" spans="1:27">
       <x:c r="A215" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F215" s="0">
         <x:v>1</x:v>
@@ -8209,16 +8248,16 @@
     </x:row>
     <x:row r="216" spans="1:27">
       <x:c r="A216" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F216" s="0">
         <x:v>1</x:v>
@@ -8235,16 +8274,16 @@
     </x:row>
     <x:row r="217" spans="1:27">
       <x:c r="A217" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F217" s="0">
         <x:v>1</x:v>
@@ -8261,16 +8300,16 @@
     </x:row>
     <x:row r="218" spans="1:27">
       <x:c r="A218" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F218" s="0">
         <x:v>1</x:v>
@@ -8287,16 +8326,16 @@
     </x:row>
     <x:row r="219" spans="1:27">
       <x:c r="A219" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F219" s="0">
         <x:v>1</x:v>
@@ -8313,16 +8352,16 @@
     </x:row>
     <x:row r="220" spans="1:27">
       <x:c r="A220" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F220" s="0">
         <x:v>1</x:v>
@@ -8339,16 +8378,16 @@
     </x:row>
     <x:row r="221" spans="1:27">
       <x:c r="A221" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F221" s="0">
         <x:v>1</x:v>
@@ -8365,16 +8404,16 @@
     </x:row>
     <x:row r="222" spans="1:27">
       <x:c r="A222" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F222" s="0">
         <x:v>1</x:v>
@@ -8391,16 +8430,16 @@
     </x:row>
     <x:row r="223" spans="1:27">
       <x:c r="A223" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F223" s="0">
         <x:v>1</x:v>
@@ -8417,16 +8456,16 @@
     </x:row>
     <x:row r="224" spans="1:27">
       <x:c r="A224" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F224" s="0">
         <x:v>1</x:v>
@@ -8443,16 +8482,16 @@
     </x:row>
     <x:row r="225" spans="1:27">
       <x:c r="A225" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F225" s="0">
         <x:v>1</x:v>
@@ -8469,16 +8508,16 @@
     </x:row>
     <x:row r="226" spans="1:27">
       <x:c r="A226" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F226" s="0">
         <x:v>1</x:v>
@@ -8495,16 +8534,16 @@
     </x:row>
     <x:row r="227" spans="1:27">
       <x:c r="A227" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F227" s="0">
         <x:v>1</x:v>
@@ -8521,16 +8560,16 @@
     </x:row>
     <x:row r="228" spans="1:27">
       <x:c r="A228" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E228" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F228" s="0">
         <x:v>1</x:v>
@@ -8547,16 +8586,16 @@
     </x:row>
     <x:row r="229" spans="1:27">
       <x:c r="A229" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E229" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F229" s="0">
         <x:v>1</x:v>
@@ -8573,16 +8612,16 @@
     </x:row>
     <x:row r="230" spans="1:27">
       <x:c r="A230" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E230" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F230" s="0">
         <x:v>1</x:v>
@@ -8599,16 +8638,16 @@
     </x:row>
     <x:row r="231" spans="1:27">
       <x:c r="A231" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E231" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F231" s="0">
         <x:v>1</x:v>
@@ -8625,16 +8664,16 @@
     </x:row>
     <x:row r="232" spans="1:27">
       <x:c r="A232" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E232" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F232" s="0">
         <x:v>1</x:v>
@@ -8651,16 +8690,16 @@
     </x:row>
     <x:row r="233" spans="1:27">
       <x:c r="A233" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E233" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F233" s="0">
         <x:v>1</x:v>
@@ -8677,16 +8716,16 @@
     </x:row>
     <x:row r="234" spans="1:27">
       <x:c r="A234" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E234" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F234" s="0">
         <x:v>1</x:v>
@@ -8703,16 +8742,16 @@
     </x:row>
     <x:row r="235" spans="1:27">
       <x:c r="A235" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E235" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F235" s="0">
         <x:v>1</x:v>
@@ -8729,16 +8768,16 @@
     </x:row>
     <x:row r="236" spans="1:27">
       <x:c r="A236" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E236" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F236" s="0">
         <x:v>1</x:v>
@@ -8755,16 +8794,16 @@
     </x:row>
     <x:row r="237" spans="1:27">
       <x:c r="A237" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E237" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F237" s="0">
         <x:v>1</x:v>
@@ -8781,16 +8820,16 @@
     </x:row>
     <x:row r="238" spans="1:27">
       <x:c r="A238" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E238" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F238" s="0">
         <x:v>1</x:v>
@@ -8807,16 +8846,16 @@
     </x:row>
     <x:row r="239" spans="1:27">
       <x:c r="A239" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E239" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F239" s="0">
         <x:v>1</x:v>
@@ -8833,16 +8872,16 @@
     </x:row>
     <x:row r="240" spans="1:27">
       <x:c r="A240" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E240" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F240" s="0">
         <x:v>1</x:v>
@@ -8859,19 +8898,19 @@
     </x:row>
     <x:row r="241" spans="1:27">
       <x:c r="A241" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E241" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F241" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I241" s="0">
         <x:v>2571</x:v>
@@ -8879,22 +8918,25 @@
       <x:c r="K241" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R241" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W241" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="242" spans="1:27">
       <x:c r="A242" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E242" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F242" s="0">
         <x:v>1</x:v>
@@ -8911,16 +8953,16 @@
     </x:row>
     <x:row r="243" spans="1:27">
       <x:c r="A243" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E243" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F243" s="0">
         <x:v>1</x:v>
@@ -8937,16 +8979,16 @@
     </x:row>
     <x:row r="244" spans="1:27">
       <x:c r="A244" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E244" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F244" s="0">
         <x:v>1</x:v>
@@ -8963,16 +9005,16 @@
     </x:row>
     <x:row r="245" spans="1:27">
       <x:c r="A245" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E245" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F245" s="0">
         <x:v>1</x:v>
@@ -8989,16 +9031,16 @@
     </x:row>
     <x:row r="246" spans="1:27">
       <x:c r="A246" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E246" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F246" s="0">
         <x:v>1</x:v>
@@ -9015,16 +9057,16 @@
     </x:row>
     <x:row r="247" spans="1:27">
       <x:c r="A247" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E247" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F247" s="0">
         <x:v>1</x:v>
@@ -9041,16 +9083,16 @@
     </x:row>
     <x:row r="248" spans="1:27">
       <x:c r="A248" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E248" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F248" s="0">
         <x:v>1</x:v>
@@ -9067,16 +9109,16 @@
     </x:row>
     <x:row r="249" spans="1:27">
       <x:c r="A249" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E249" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F249" s="0">
         <x:v>1</x:v>
@@ -9093,16 +9135,16 @@
     </x:row>
     <x:row r="250" spans="1:27">
       <x:c r="A250" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E250" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F250" s="0">
         <x:v>1</x:v>
@@ -9119,16 +9161,16 @@
     </x:row>
     <x:row r="251" spans="1:27">
       <x:c r="A251" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E251" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F251" s="0">
         <x:v>1</x:v>
@@ -9145,16 +9187,16 @@
     </x:row>
     <x:row r="252" spans="1:27">
       <x:c r="A252" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E252" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F252" s="0">
         <x:v>1</x:v>
@@ -9171,16 +9213,16 @@
     </x:row>
     <x:row r="253" spans="1:27">
       <x:c r="A253" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E253" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F253" s="0">
         <x:v>1</x:v>
@@ -9197,16 +9239,16 @@
     </x:row>
     <x:row r="254" spans="1:27">
       <x:c r="A254" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E254" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F254" s="0">
         <x:v>1</x:v>
@@ -9223,16 +9265,16 @@
     </x:row>
     <x:row r="255" spans="1:27">
       <x:c r="A255" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E255" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F255" s="0">
         <x:v>1</x:v>
@@ -9249,16 +9291,16 @@
     </x:row>
     <x:row r="256" spans="1:27">
       <x:c r="A256" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E256" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F256" s="0">
         <x:v>1</x:v>
@@ -9275,16 +9317,16 @@
     </x:row>
     <x:row r="257" spans="1:27">
       <x:c r="A257" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E257" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F257" s="0">
         <x:v>1</x:v>
@@ -9301,16 +9343,16 @@
     </x:row>
     <x:row r="258" spans="1:27">
       <x:c r="A258" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E258" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F258" s="0">
         <x:v>1</x:v>
@@ -9327,16 +9369,16 @@
     </x:row>
     <x:row r="259" spans="1:27">
       <x:c r="A259" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E259" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F259" s="0">
         <x:v>1</x:v>
@@ -9353,16 +9395,16 @@
     </x:row>
     <x:row r="260" spans="1:27">
       <x:c r="A260" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E260" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F260" s="0">
         <x:v>1</x:v>
@@ -9379,16 +9421,16 @@
     </x:row>
     <x:row r="261" spans="1:27">
       <x:c r="A261" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E261" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F261" s="0">
         <x:v>1</x:v>
@@ -9405,16 +9447,16 @@
     </x:row>
     <x:row r="262" spans="1:27">
       <x:c r="A262" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E262" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F262" s="0">
         <x:v>1</x:v>
@@ -9431,16 +9473,16 @@
     </x:row>
     <x:row r="263" spans="1:27">
       <x:c r="A263" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E263" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F263" s="0">
         <x:v>1</x:v>
@@ -9457,16 +9499,16 @@
     </x:row>
     <x:row r="264" spans="1:27">
       <x:c r="A264" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E264" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F264" s="0">
         <x:v>1</x:v>
@@ -9483,16 +9525,16 @@
     </x:row>
     <x:row r="265" spans="1:27">
       <x:c r="A265" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E265" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F265" s="0">
         <x:v>1</x:v>
@@ -9509,16 +9551,16 @@
     </x:row>
     <x:row r="266" spans="1:27">
       <x:c r="A266" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E266" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F266" s="0">
         <x:v>1</x:v>
@@ -9535,16 +9577,16 @@
     </x:row>
     <x:row r="267" spans="1:27">
       <x:c r="A267" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E267" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F267" s="0">
         <x:v>1</x:v>
@@ -9561,16 +9603,16 @@
     </x:row>
     <x:row r="268" spans="1:27">
       <x:c r="A268" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E268" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F268" s="0">
         <x:v>1</x:v>
@@ -9587,16 +9629,16 @@
     </x:row>
     <x:row r="269" spans="1:27">
       <x:c r="A269" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E269" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F269" s="0">
         <x:v>1</x:v>
@@ -9613,16 +9655,16 @@
     </x:row>
     <x:row r="270" spans="1:27">
       <x:c r="A270" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E270" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F270" s="0">
         <x:v>1</x:v>
@@ -9639,16 +9681,16 @@
     </x:row>
     <x:row r="271" spans="1:27">
       <x:c r="A271" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E271" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F271" s="0">
         <x:v>1</x:v>
@@ -9665,16 +9707,16 @@
     </x:row>
     <x:row r="272" spans="1:27">
       <x:c r="A272" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E272" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F272" s="0">
         <x:v>1</x:v>
@@ -9691,16 +9733,16 @@
     </x:row>
     <x:row r="273" spans="1:27">
       <x:c r="A273" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E273" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F273" s="0">
         <x:v>1</x:v>
@@ -9717,16 +9759,16 @@
     </x:row>
     <x:row r="274" spans="1:27">
       <x:c r="A274" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E274" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F274" s="0">
         <x:v>1</x:v>
@@ -9743,19 +9785,19 @@
     </x:row>
     <x:row r="275" spans="1:27">
       <x:c r="A275" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="E275" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F275" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I275" s="0">
         <x:v>2478</x:v>
@@ -9763,22 +9805,25 @@
       <x:c r="K275" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R275" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W275" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="276" spans="1:27">
       <x:c r="A276" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E276" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F276" s="0">
         <x:v>1</x:v>
@@ -9795,16 +9840,16 @@
     </x:row>
     <x:row r="277" spans="1:27">
       <x:c r="A277" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E277" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F277" s="0">
         <x:v>1</x:v>
@@ -9821,16 +9866,16 @@
     </x:row>
     <x:row r="278" spans="1:27">
       <x:c r="A278" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E278" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F278" s="0">
         <x:v>1</x:v>
@@ -9847,16 +9892,16 @@
     </x:row>
     <x:row r="279" spans="1:27">
       <x:c r="A279" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E279" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F279" s="0">
         <x:v>1</x:v>
@@ -9873,16 +9918,16 @@
     </x:row>
     <x:row r="280" spans="1:27">
       <x:c r="A280" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E280" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F280" s="0">
         <x:v>1</x:v>
@@ -9899,16 +9944,16 @@
     </x:row>
     <x:row r="281" spans="1:27">
       <x:c r="A281" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E281" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F281" s="0">
         <x:v>1</x:v>
@@ -9925,16 +9970,16 @@
     </x:row>
     <x:row r="282" spans="1:27">
       <x:c r="A282" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E282" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F282" s="0">
         <x:v>1</x:v>
@@ -9951,16 +9996,16 @@
     </x:row>
     <x:row r="283" spans="1:27">
       <x:c r="A283" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E283" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F283" s="0">
         <x:v>1</x:v>
@@ -9977,16 +10022,16 @@
     </x:row>
     <x:row r="284" spans="1:27">
       <x:c r="A284" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E284" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F284" s="0">
         <x:v>1</x:v>
@@ -10003,16 +10048,16 @@
     </x:row>
     <x:row r="285" spans="1:27">
       <x:c r="A285" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E285" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F285" s="0">
         <x:v>1</x:v>
@@ -10029,16 +10074,16 @@
     </x:row>
     <x:row r="286" spans="1:27">
       <x:c r="A286" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E286" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F286" s="0">
         <x:v>1</x:v>
@@ -10055,16 +10100,16 @@
     </x:row>
     <x:row r="287" spans="1:27">
       <x:c r="A287" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E287" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F287" s="0">
         <x:v>1</x:v>
@@ -10081,16 +10126,16 @@
     </x:row>
     <x:row r="288" spans="1:27">
       <x:c r="A288" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E288" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F288" s="0">
         <x:v>1</x:v>
@@ -10107,16 +10152,16 @@
     </x:row>
     <x:row r="289" spans="1:27">
       <x:c r="A289" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E289" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F289" s="0">
         <x:v>1</x:v>
@@ -10133,16 +10178,16 @@
     </x:row>
     <x:row r="290" spans="1:27">
       <x:c r="A290" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E290" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F290" s="0">
         <x:v>1</x:v>
@@ -10159,16 +10204,16 @@
     </x:row>
     <x:row r="291" spans="1:27">
       <x:c r="A291" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E291" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F291" s="0">
         <x:v>1</x:v>
@@ -10185,16 +10230,16 @@
     </x:row>
     <x:row r="292" spans="1:27">
       <x:c r="A292" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E292" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F292" s="0">
         <x:v>1</x:v>
@@ -10211,16 +10256,16 @@
     </x:row>
     <x:row r="293" spans="1:27">
       <x:c r="A293" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E293" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F293" s="0">
         <x:v>1</x:v>
@@ -10237,16 +10282,16 @@
     </x:row>
     <x:row r="294" spans="1:27">
       <x:c r="A294" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E294" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F294" s="0">
         <x:v>1</x:v>
@@ -10263,16 +10308,16 @@
     </x:row>
     <x:row r="295" spans="1:27">
       <x:c r="A295" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E295" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F295" s="0">
         <x:v>1</x:v>
@@ -10289,16 +10334,16 @@
     </x:row>
     <x:row r="296" spans="1:27">
       <x:c r="A296" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E296" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F296" s="0">
         <x:v>1</x:v>
@@ -10315,16 +10360,16 @@
     </x:row>
     <x:row r="297" spans="1:27">
       <x:c r="A297" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E297" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F297" s="0">
         <x:v>1</x:v>
@@ -10341,16 +10386,16 @@
     </x:row>
     <x:row r="298" spans="1:27">
       <x:c r="A298" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E298" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F298" s="0">
         <x:v>1</x:v>
@@ -10367,16 +10412,16 @@
     </x:row>
     <x:row r="299" spans="1:27">
       <x:c r="A299" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E299" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F299" s="0">
         <x:v>1</x:v>
@@ -10393,16 +10438,16 @@
     </x:row>
     <x:row r="300" spans="1:27">
       <x:c r="A300" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E300" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F300" s="0">
         <x:v>1</x:v>
@@ -10419,16 +10464,16 @@
     </x:row>
     <x:row r="301" spans="1:27">
       <x:c r="A301" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E301" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F301" s="0">
         <x:v>1</x:v>
@@ -10445,16 +10490,16 @@
     </x:row>
     <x:row r="302" spans="1:27">
       <x:c r="A302" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E302" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F302" s="0">
         <x:v>1</x:v>
@@ -10471,16 +10516,16 @@
     </x:row>
     <x:row r="303" spans="1:27">
       <x:c r="A303" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E303" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F303" s="0">
         <x:v>1</x:v>
@@ -10497,16 +10542,16 @@
     </x:row>
     <x:row r="304" spans="1:27">
       <x:c r="A304" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E304" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F304" s="0">
         <x:v>1</x:v>
@@ -10523,16 +10568,16 @@
     </x:row>
     <x:row r="305" spans="1:27">
       <x:c r="A305" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E305" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F305" s="0">
         <x:v>1</x:v>
@@ -10549,16 +10594,16 @@
     </x:row>
     <x:row r="306" spans="1:27">
       <x:c r="A306" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E306" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F306" s="0">
         <x:v>1</x:v>
@@ -10575,16 +10620,16 @@
     </x:row>
     <x:row r="307" spans="1:27">
       <x:c r="A307" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E307" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F307" s="0">
         <x:v>1</x:v>
@@ -10601,19 +10646,19 @@
     </x:row>
     <x:row r="308" spans="1:27">
       <x:c r="A308" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E308" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F308" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I308" s="0">
         <x:v>1971</x:v>
@@ -10621,22 +10666,25 @@
       <x:c r="K308" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R308" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W308" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="309" spans="1:27">
       <x:c r="A309" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E309" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F309" s="0">
         <x:v>1</x:v>
@@ -10653,16 +10701,16 @@
     </x:row>
     <x:row r="310" spans="1:27">
       <x:c r="A310" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E310" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F310" s="0">
         <x:v>1</x:v>
@@ -10679,16 +10727,16 @@
     </x:row>
     <x:row r="311" spans="1:27">
       <x:c r="A311" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E311" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F311" s="0">
         <x:v>1</x:v>
@@ -10705,16 +10753,16 @@
     </x:row>
     <x:row r="312" spans="1:27">
       <x:c r="A312" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E312" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F312" s="0">
         <x:v>1</x:v>
@@ -10731,16 +10779,16 @@
     </x:row>
     <x:row r="313" spans="1:27">
       <x:c r="A313" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E313" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F313" s="0">
         <x:v>1</x:v>
@@ -10757,16 +10805,16 @@
     </x:row>
     <x:row r="314" spans="1:27">
       <x:c r="A314" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E314" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F314" s="0">
         <x:v>1</x:v>
@@ -10783,16 +10831,16 @@
     </x:row>
     <x:row r="315" spans="1:27">
       <x:c r="A315" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E315" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F315" s="0">
         <x:v>1</x:v>
@@ -10809,16 +10857,16 @@
     </x:row>
     <x:row r="316" spans="1:27">
       <x:c r="A316" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E316" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F316" s="0">
         <x:v>1</x:v>
@@ -10835,16 +10883,16 @@
     </x:row>
     <x:row r="317" spans="1:27">
       <x:c r="A317" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E317" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F317" s="0">
         <x:v>1</x:v>
@@ -10861,16 +10909,16 @@
     </x:row>
     <x:row r="318" spans="1:27">
       <x:c r="A318" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E318" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F318" s="0">
         <x:v>1</x:v>
@@ -10887,16 +10935,16 @@
     </x:row>
     <x:row r="319" spans="1:27">
       <x:c r="A319" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E319" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F319" s="0">
         <x:v>1</x:v>
@@ -10913,16 +10961,16 @@
     </x:row>
     <x:row r="320" spans="1:27">
       <x:c r="A320" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E320" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F320" s="0">
         <x:v>1</x:v>
@@ -10939,16 +10987,16 @@
     </x:row>
     <x:row r="321" spans="1:27">
       <x:c r="A321" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E321" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F321" s="0">
         <x:v>1</x:v>
@@ -10965,16 +11013,16 @@
     </x:row>
     <x:row r="322" spans="1:27">
       <x:c r="A322" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E322" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F322" s="0">
         <x:v>1</x:v>
@@ -10991,16 +11039,16 @@
     </x:row>
     <x:row r="323" spans="1:27">
       <x:c r="A323" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E323" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F323" s="0">
         <x:v>1</x:v>
@@ -11017,16 +11065,16 @@
     </x:row>
     <x:row r="324" spans="1:27">
       <x:c r="A324" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E324" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F324" s="0">
         <x:v>1</x:v>
@@ -11043,16 +11091,16 @@
     </x:row>
     <x:row r="325" spans="1:27">
       <x:c r="A325" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E325" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F325" s="0">
         <x:v>1</x:v>
@@ -11069,16 +11117,16 @@
     </x:row>
     <x:row r="326" spans="1:27">
       <x:c r="A326" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E326" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F326" s="0">
         <x:v>1</x:v>
@@ -11095,16 +11143,16 @@
     </x:row>
     <x:row r="327" spans="1:27">
       <x:c r="A327" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E327" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F327" s="0">
         <x:v>1</x:v>
@@ -11121,16 +11169,16 @@
     </x:row>
     <x:row r="328" spans="1:27">
       <x:c r="A328" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E328" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F328" s="0">
         <x:v>1</x:v>
@@ -11147,16 +11195,16 @@
     </x:row>
     <x:row r="329" spans="1:27">
       <x:c r="A329" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E329" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F329" s="0">
         <x:v>1</x:v>
@@ -11173,16 +11221,16 @@
     </x:row>
     <x:row r="330" spans="1:27">
       <x:c r="A330" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E330" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F330" s="0">
         <x:v>1</x:v>
@@ -11199,16 +11247,16 @@
     </x:row>
     <x:row r="331" spans="1:27">
       <x:c r="A331" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E331" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F331" s="0">
         <x:v>1</x:v>
@@ -11225,16 +11273,16 @@
     </x:row>
     <x:row r="332" spans="1:27">
       <x:c r="A332" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E332" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F332" s="0">
         <x:v>1</x:v>
@@ -11251,16 +11299,16 @@
     </x:row>
     <x:row r="333" spans="1:27">
       <x:c r="A333" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E333" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F333" s="0">
         <x:v>1</x:v>
@@ -11277,16 +11325,16 @@
     </x:row>
     <x:row r="334" spans="1:27">
       <x:c r="A334" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E334" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F334" s="0">
         <x:v>1</x:v>
@@ -11303,16 +11351,16 @@
     </x:row>
     <x:row r="335" spans="1:27">
       <x:c r="A335" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E335" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F335" s="0">
         <x:v>1</x:v>
@@ -11329,16 +11377,16 @@
     </x:row>
     <x:row r="336" spans="1:27">
       <x:c r="A336" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E336" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F336" s="0">
         <x:v>1</x:v>
@@ -11355,16 +11403,16 @@
     </x:row>
     <x:row r="337" spans="1:27">
       <x:c r="A337" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E337" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F337" s="0">
         <x:v>1</x:v>
@@ -11381,16 +11429,16 @@
     </x:row>
     <x:row r="338" spans="1:27">
       <x:c r="A338" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E338" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F338" s="0">
         <x:v>1</x:v>
@@ -11407,16 +11455,16 @@
     </x:row>
     <x:row r="339" spans="1:27">
       <x:c r="A339" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E339" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F339" s="0">
         <x:v>1</x:v>
@@ -11433,16 +11481,16 @@
     </x:row>
     <x:row r="340" spans="1:27">
       <x:c r="A340" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E340" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F340" s="0">
         <x:v>1</x:v>
@@ -11459,16 +11507,16 @@
     </x:row>
     <x:row r="341" spans="1:27">
       <x:c r="A341" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E341" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F341" s="0">
         <x:v>1</x:v>
@@ -11485,19 +11533,19 @@
     </x:row>
     <x:row r="342" spans="1:27">
       <x:c r="A342" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="E342" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F342" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I342" s="0">
         <x:v>2678</x:v>
@@ -11505,22 +11553,25 @@
       <x:c r="K342" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R342" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W342" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="343" spans="1:27">
       <x:c r="A343" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E343" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F343" s="0">
         <x:v>1</x:v>
@@ -11537,16 +11588,16 @@
     </x:row>
     <x:row r="344" spans="1:27">
       <x:c r="A344" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E344" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F344" s="0">
         <x:v>1</x:v>
@@ -11563,16 +11614,16 @@
     </x:row>
     <x:row r="345" spans="1:27">
       <x:c r="A345" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E345" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F345" s="0">
         <x:v>1</x:v>
@@ -11589,16 +11640,16 @@
     </x:row>
     <x:row r="346" spans="1:27">
       <x:c r="A346" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E346" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F346" s="0">
         <x:v>1</x:v>
@@ -11615,16 +11666,16 @@
     </x:row>
     <x:row r="347" spans="1:27">
       <x:c r="A347" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E347" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F347" s="0">
         <x:v>1</x:v>
@@ -11641,16 +11692,16 @@
     </x:row>
     <x:row r="348" spans="1:27">
       <x:c r="A348" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E348" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F348" s="0">
         <x:v>1</x:v>
@@ -11667,16 +11718,16 @@
     </x:row>
     <x:row r="349" spans="1:27">
       <x:c r="A349" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E349" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F349" s="0">
         <x:v>1</x:v>
@@ -11693,16 +11744,16 @@
     </x:row>
     <x:row r="350" spans="1:27">
       <x:c r="A350" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E350" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F350" s="0">
         <x:v>1</x:v>
@@ -11719,16 +11770,16 @@
     </x:row>
     <x:row r="351" spans="1:27">
       <x:c r="A351" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E351" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F351" s="0">
         <x:v>1</x:v>
@@ -11745,16 +11796,16 @@
     </x:row>
     <x:row r="352" spans="1:27">
       <x:c r="A352" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E352" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F352" s="0">
         <x:v>1</x:v>
@@ -11771,16 +11822,16 @@
     </x:row>
     <x:row r="353" spans="1:27">
       <x:c r="A353" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E353" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F353" s="0">
         <x:v>1</x:v>
@@ -11797,16 +11848,16 @@
     </x:row>
     <x:row r="354" spans="1:27">
       <x:c r="A354" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E354" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F354" s="0">
         <x:v>1</x:v>
@@ -11823,16 +11874,16 @@
     </x:row>
     <x:row r="355" spans="1:27">
       <x:c r="A355" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E355" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F355" s="0">
         <x:v>1</x:v>
@@ -11849,16 +11900,16 @@
     </x:row>
     <x:row r="356" spans="1:27">
       <x:c r="A356" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E356" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F356" s="0">
         <x:v>1</x:v>
@@ -11875,16 +11926,16 @@
     </x:row>
     <x:row r="357" spans="1:27">
       <x:c r="A357" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E357" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F357" s="0">
         <x:v>1</x:v>
@@ -11901,16 +11952,16 @@
     </x:row>
     <x:row r="358" spans="1:27">
       <x:c r="A358" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E358" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F358" s="0">
         <x:v>1</x:v>
@@ -11927,16 +11978,16 @@
     </x:row>
     <x:row r="359" spans="1:27">
       <x:c r="A359" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E359" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F359" s="0">
         <x:v>1</x:v>
@@ -11953,16 +12004,16 @@
     </x:row>
     <x:row r="360" spans="1:27">
       <x:c r="A360" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D360" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E360" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F360" s="0">
         <x:v>1</x:v>
@@ -11979,16 +12030,16 @@
     </x:row>
     <x:row r="361" spans="1:27">
       <x:c r="A361" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D361" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E361" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F361" s="0">
         <x:v>1</x:v>
@@ -12005,16 +12056,16 @@
     </x:row>
     <x:row r="362" spans="1:27">
       <x:c r="A362" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D362" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E362" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F362" s="0">
         <x:v>1</x:v>
@@ -12031,16 +12082,16 @@
     </x:row>
     <x:row r="363" spans="1:27">
       <x:c r="A363" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D363" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E363" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F363" s="0">
         <x:v>1</x:v>
@@ -12057,16 +12108,16 @@
     </x:row>
     <x:row r="364" spans="1:27">
       <x:c r="A364" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D364" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E364" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F364" s="0">
         <x:v>1</x:v>
@@ -12083,16 +12134,16 @@
     </x:row>
     <x:row r="365" spans="1:27">
       <x:c r="A365" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D365" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E365" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F365" s="0">
         <x:v>1</x:v>
@@ -12109,16 +12160,16 @@
     </x:row>
     <x:row r="366" spans="1:27">
       <x:c r="A366" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D366" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E366" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F366" s="0">
         <x:v>1</x:v>
@@ -12135,16 +12186,16 @@
     </x:row>
     <x:row r="367" spans="1:27">
       <x:c r="A367" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D367" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E367" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F367" s="0">
         <x:v>1</x:v>
@@ -12161,16 +12212,16 @@
     </x:row>
     <x:row r="368" spans="1:27">
       <x:c r="A368" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D368" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E368" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F368" s="0">
         <x:v>1</x:v>
@@ -12187,16 +12238,16 @@
     </x:row>
     <x:row r="369" spans="1:27">
       <x:c r="A369" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D369" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E369" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F369" s="0">
         <x:v>1</x:v>
@@ -12213,16 +12264,16 @@
     </x:row>
     <x:row r="370" spans="1:27">
       <x:c r="A370" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D370" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E370" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F370" s="0">
         <x:v>1</x:v>
@@ -12239,16 +12290,16 @@
     </x:row>
     <x:row r="371" spans="1:27">
       <x:c r="A371" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D371" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E371" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F371" s="0">
         <x:v>1</x:v>
@@ -12265,16 +12316,16 @@
     </x:row>
     <x:row r="372" spans="1:27">
       <x:c r="A372" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D372" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E372" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F372" s="0">
         <x:v>1</x:v>
@@ -12291,16 +12342,16 @@
     </x:row>
     <x:row r="373" spans="1:27">
       <x:c r="A373" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D373" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E373" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F373" s="0">
         <x:v>1</x:v>
@@ -12317,16 +12368,16 @@
     </x:row>
     <x:row r="374" spans="1:27">
       <x:c r="A374" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D374" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E374" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F374" s="0">
         <x:v>1</x:v>
@@ -12343,16 +12394,16 @@
     </x:row>
     <x:row r="375" spans="1:27">
       <x:c r="A375" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E375" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F375" s="0">
         <x:v>1</x:v>
@@ -12369,16 +12420,16 @@
     </x:row>
     <x:row r="376" spans="1:27">
       <x:c r="A376" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E376" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F376" s="0">
         <x:v>1</x:v>
@@ -12395,19 +12446,19 @@
     </x:row>
     <x:row r="377" spans="1:27">
       <x:c r="A377" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D377" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="E377" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="F377" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I377" s="0">
         <x:v>2061</x:v>
@@ -12415,22 +12466,25 @@
       <x:c r="K377" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R377" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W377" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="378" spans="1:27">
       <x:c r="A378" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D378" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E378" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F378" s="0">
         <x:v>1</x:v>
@@ -12447,16 +12501,16 @@
     </x:row>
     <x:row r="379" spans="1:27">
       <x:c r="A379" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D379" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E379" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F379" s="0">
         <x:v>1</x:v>
@@ -12473,16 +12527,16 @@
     </x:row>
     <x:row r="380" spans="1:27">
       <x:c r="A380" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D380" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E380" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F380" s="0">
         <x:v>1</x:v>
@@ -12499,16 +12553,16 @@
     </x:row>
     <x:row r="381" spans="1:27">
       <x:c r="A381" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D381" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E381" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F381" s="0">
         <x:v>1</x:v>
@@ -12525,16 +12579,16 @@
     </x:row>
     <x:row r="382" spans="1:27">
       <x:c r="A382" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D382" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E382" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F382" s="0">
         <x:v>1</x:v>
@@ -12551,16 +12605,16 @@
     </x:row>
     <x:row r="383" spans="1:27">
       <x:c r="A383" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D383" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E383" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F383" s="0">
         <x:v>1</x:v>
@@ -12577,16 +12631,16 @@
     </x:row>
     <x:row r="384" spans="1:27">
       <x:c r="A384" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D384" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E384" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F384" s="0">
         <x:v>1</x:v>
@@ -12603,16 +12657,16 @@
     </x:row>
     <x:row r="385" spans="1:27">
       <x:c r="A385" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D385" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E385" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F385" s="0">
         <x:v>1</x:v>
@@ -12629,16 +12683,16 @@
     </x:row>
     <x:row r="386" spans="1:27">
       <x:c r="A386" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D386" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E386" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F386" s="0">
         <x:v>1</x:v>
@@ -12655,16 +12709,16 @@
     </x:row>
     <x:row r="387" spans="1:27">
       <x:c r="A387" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D387" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E387" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F387" s="0">
         <x:v>1</x:v>
@@ -12681,16 +12735,16 @@
     </x:row>
     <x:row r="388" spans="1:27">
       <x:c r="A388" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D388" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E388" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F388" s="0">
         <x:v>1</x:v>
@@ -12707,16 +12761,16 @@
     </x:row>
     <x:row r="389" spans="1:27">
       <x:c r="A389" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D389" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E389" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F389" s="0">
         <x:v>1</x:v>
@@ -12733,16 +12787,16 @@
     </x:row>
     <x:row r="390" spans="1:27">
       <x:c r="A390" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D390" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E390" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F390" s="0">
         <x:v>1</x:v>
@@ -12759,16 +12813,16 @@
     </x:row>
     <x:row r="391" spans="1:27">
       <x:c r="A391" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D391" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E391" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F391" s="0">
         <x:v>1</x:v>
@@ -12785,16 +12839,16 @@
     </x:row>
     <x:row r="392" spans="1:27">
       <x:c r="A392" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D392" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E392" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F392" s="0">
         <x:v>1</x:v>
@@ -12811,16 +12865,16 @@
     </x:row>
     <x:row r="393" spans="1:27">
       <x:c r="A393" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D393" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E393" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F393" s="0">
         <x:v>1</x:v>
@@ -12837,16 +12891,16 @@
     </x:row>
     <x:row r="394" spans="1:27">
       <x:c r="A394" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D394" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E394" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F394" s="0">
         <x:v>1</x:v>
@@ -12863,16 +12917,16 @@
     </x:row>
     <x:row r="395" spans="1:27">
       <x:c r="A395" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D395" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E395" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F395" s="0">
         <x:v>1</x:v>
@@ -12889,16 +12943,16 @@
     </x:row>
     <x:row r="396" spans="1:27">
       <x:c r="A396" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D396" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E396" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F396" s="0">
         <x:v>1</x:v>
@@ -12915,16 +12969,16 @@
     </x:row>
     <x:row r="397" spans="1:27">
       <x:c r="A397" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D397" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E397" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F397" s="0">
         <x:v>1</x:v>
@@ -12941,16 +12995,16 @@
     </x:row>
     <x:row r="398" spans="1:27">
       <x:c r="A398" s="0" t="s">
-        <x:v>614</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D398" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E398" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F398" s="0">
         <x:v>1</x:v>
@@ -12967,16 +13021,16 @@
     </x:row>
     <x:row r="399" spans="1:27">
       <x:c r="A399" s="0" t="s">
-        <x:v>615</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D399" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E399" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F399" s="0">
         <x:v>1</x:v>
@@ -12993,16 +13047,16 @@
     </x:row>
     <x:row r="400" spans="1:27">
       <x:c r="A400" s="0" t="s">
-        <x:v>616</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D400" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E400" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F400" s="0">
         <x:v>1</x:v>
@@ -13019,16 +13073,16 @@
     </x:row>
     <x:row r="401" spans="1:27">
       <x:c r="A401" s="0" t="s">
-        <x:v>617</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D401" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E401" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F401" s="0">
         <x:v>1</x:v>
@@ -13045,16 +13099,16 @@
     </x:row>
     <x:row r="402" spans="1:27">
       <x:c r="A402" s="0" t="s">
-        <x:v>618</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D402" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E402" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F402" s="0">
         <x:v>1</x:v>
@@ -13071,16 +13125,16 @@
     </x:row>
     <x:row r="403" spans="1:27">
       <x:c r="A403" s="0" t="s">
-        <x:v>619</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D403" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E403" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F403" s="0">
         <x:v>1</x:v>
@@ -13097,16 +13151,16 @@
     </x:row>
     <x:row r="404" spans="1:27">
       <x:c r="A404" s="0" t="s">
-        <x:v>620</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D404" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E404" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F404" s="0">
         <x:v>1</x:v>
@@ -13123,16 +13177,16 @@
     </x:row>
     <x:row r="405" spans="1:27">
       <x:c r="A405" s="0" t="s">
-        <x:v>621</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D405" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E405" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F405" s="0">
         <x:v>1</x:v>
@@ -13149,16 +13203,16 @@
     </x:row>
     <x:row r="406" spans="1:27">
       <x:c r="A406" s="0" t="s">
-        <x:v>622</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D406" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E406" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F406" s="0">
         <x:v>1</x:v>
@@ -13175,16 +13229,16 @@
     </x:row>
     <x:row r="407" spans="1:27">
       <x:c r="A407" s="0" t="s">
-        <x:v>623</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D407" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E407" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F407" s="0">
         <x:v>1</x:v>
@@ -13201,16 +13255,16 @@
     </x:row>
     <x:row r="408" spans="1:27">
       <x:c r="A408" s="0" t="s">
-        <x:v>624</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D408" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E408" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F408" s="0">
         <x:v>1</x:v>
@@ -13227,16 +13281,16 @@
     </x:row>
     <x:row r="409" spans="1:27">
       <x:c r="A409" s="0" t="s">
-        <x:v>625</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D409" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E409" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F409" s="0">
         <x:v>1</x:v>
@@ -13253,16 +13307,16 @@
     </x:row>
     <x:row r="410" spans="1:27">
       <x:c r="A410" s="0" t="s">
-        <x:v>626</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D410" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E410" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F410" s="0">
         <x:v>1</x:v>
@@ -13279,16 +13333,16 @@
     </x:row>
     <x:row r="411" spans="1:27">
       <x:c r="A411" s="0" t="s">
-        <x:v>627</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D411" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E411" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F411" s="0">
         <x:v>1</x:v>
@@ -13305,19 +13359,19 @@
     </x:row>
     <x:row r="412" spans="1:27">
       <x:c r="A412" s="0" t="s">
-        <x:v>628</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D412" s="0" t="s">
-        <x:v>629</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="E412" s="0" t="s">
-        <x:v>630</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="F412" s="0">
-        <x:v>880</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I412" s="0">
         <x:v>2186</x:v>
@@ -13325,22 +13379,25 @@
       <x:c r="K412" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R412" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="W412" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="413" spans="1:27">
       <x:c r="A413" s="0" t="s">
-        <x:v>631</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D413" s="0" t="s">
-        <x:v>632</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E413" s="0" t="s">
-        <x:v>633</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="F413" s="0">
         <x:v>1</x:v>
@@ -13357,16 +13414,16 @@
     </x:row>
     <x:row r="414" spans="1:27">
       <x:c r="A414" s="0" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D414" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E414" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F414" s="0">
         <x:v>1</x:v>
@@ -13383,16 +13440,16 @@
     </x:row>
     <x:row r="415" spans="1:27">
       <x:c r="A415" s="0" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D415" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E415" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F415" s="0">
         <x:v>1</x:v>
@@ -13409,16 +13466,16 @@
     </x:row>
     <x:row r="416" spans="1:27">
       <x:c r="A416" s="0" t="s">
-        <x:v>636</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D416" s="0" t="s">
-        <x:v>637</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E416" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F416" s="0">
         <x:v>1</x:v>
@@ -13435,16 +13492,16 @@
     </x:row>
     <x:row r="417" spans="1:27">
       <x:c r="A417" s="0" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D417" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E417" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F417" s="0">
         <x:v>1</x:v>
@@ -13461,16 +13518,16 @@
     </x:row>
     <x:row r="418" spans="1:27">
       <x:c r="A418" s="0" t="s">
-        <x:v>639</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D418" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E418" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F418" s="0">
         <x:v>1</x:v>
@@ -13487,16 +13544,16 @@
     </x:row>
     <x:row r="419" spans="1:27">
       <x:c r="A419" s="0" t="s">
-        <x:v>640</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D419" s="0" t="s">
-        <x:v>641</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="E419" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F419" s="0">
         <x:v>1</x:v>
@@ -13513,16 +13570,16 @@
     </x:row>
     <x:row r="420" spans="1:27">
       <x:c r="A420" s="0" t="s">
-        <x:v>642</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D420" s="0" t="s">
-        <x:v>643</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="E420" s="0" t="s">
-        <x:v>644</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="F420" s="0">
         <x:v>1</x:v>
@@ -13539,16 +13596,16 @@
     </x:row>
     <x:row r="421" spans="1:27">
       <x:c r="A421" s="0" t="s">
-        <x:v>645</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D421" s="0" t="s">
-        <x:v>646</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="E421" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F421" s="0">
         <x:v>1</x:v>
@@ -13565,16 +13622,16 @@
     </x:row>
     <x:row r="422" spans="1:27">
       <x:c r="A422" s="0" t="s">
-        <x:v>647</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D422" s="0" t="s">
-        <x:v>648</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E422" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F422" s="0">
         <x:v>1</x:v>
@@ -13591,16 +13648,16 @@
     </x:row>
     <x:row r="423" spans="1:27">
       <x:c r="A423" s="0" t="s">
-        <x:v>649</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D423" s="0" t="s">
-        <x:v>650</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E423" s="0" t="s">
-        <x:v>651</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="F423" s="0">
         <x:v>1</x:v>
@@ -13617,16 +13674,16 @@
     </x:row>
     <x:row r="424" spans="1:27">
       <x:c r="A424" s="0" t="s">
-        <x:v>652</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="B424" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D424" s="0" t="s">
-        <x:v>653</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="E424" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F424" s="0">
         <x:v>1</x:v>
@@ -13643,16 +13700,16 @@
     </x:row>
     <x:row r="425" spans="1:27">
       <x:c r="A425" s="0" t="s">
-        <x:v>654</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B425" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D425" s="0" t="s">
-        <x:v>655</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E425" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F425" s="0">
         <x:v>1</x:v>
@@ -13669,16 +13726,16 @@
     </x:row>
     <x:row r="426" spans="1:27">
       <x:c r="A426" s="0" t="s">
-        <x:v>656</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B426" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D426" s="0" t="s">
-        <x:v>657</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E426" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F426" s="0">
         <x:v>1</x:v>
@@ -13695,16 +13752,16 @@
     </x:row>
     <x:row r="427" spans="1:27">
       <x:c r="A427" s="0" t="s">
-        <x:v>658</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B427" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D427" s="0" t="s">
-        <x:v>659</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E427" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F427" s="0">
         <x:v>1</x:v>
@@ -13721,16 +13778,16 @@
     </x:row>
     <x:row r="428" spans="1:27">
       <x:c r="A428" s="0" t="s">
-        <x:v>660</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B428" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D428" s="0" t="s">
-        <x:v>661</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E428" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F428" s="0">
         <x:v>1</x:v>
@@ -13747,16 +13804,16 @@
     </x:row>
     <x:row r="429" spans="1:27">
       <x:c r="A429" s="0" t="s">
-        <x:v>662</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B429" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D429" s="0" t="s">
-        <x:v>663</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E429" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F429" s="0">
         <x:v>1</x:v>
@@ -13773,16 +13830,16 @@
     </x:row>
     <x:row r="430" spans="1:27">
       <x:c r="A430" s="0" t="s">
-        <x:v>664</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B430" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D430" s="0" t="s">
-        <x:v>665</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E430" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F430" s="0">
         <x:v>1</x:v>
@@ -13799,16 +13856,16 @@
     </x:row>
     <x:row r="431" spans="1:27">
       <x:c r="A431" s="0" t="s">
-        <x:v>666</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B431" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D431" s="0" t="s">
-        <x:v>667</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="E431" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F431" s="0">
         <x:v>1</x:v>
@@ -13825,16 +13882,16 @@
     </x:row>
     <x:row r="432" spans="1:27">
       <x:c r="A432" s="0" t="s">
-        <x:v>668</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B432" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D432" s="0" t="s">
-        <x:v>669</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E432" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F432" s="0">
         <x:v>1</x:v>
@@ -13851,16 +13908,16 @@
     </x:row>
     <x:row r="433" spans="1:27">
       <x:c r="A433" s="0" t="s">
-        <x:v>670</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B433" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D433" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E433" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F433" s="0">
         <x:v>1</x:v>
@@ -13877,16 +13934,16 @@
     </x:row>
     <x:row r="434" spans="1:27">
       <x:c r="A434" s="0" t="s">
-        <x:v>671</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="B434" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D434" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E434" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F434" s="0">
         <x:v>1</x:v>
@@ -13903,16 +13960,16 @@
     </x:row>
     <x:row r="435" spans="1:27">
       <x:c r="A435" s="0" t="s">
-        <x:v>672</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B435" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D435" s="0" t="s">
-        <x:v>673</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E435" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F435" s="0">
         <x:v>1</x:v>
@@ -13929,16 +13986,16 @@
     </x:row>
     <x:row r="436" spans="1:27">
       <x:c r="A436" s="0" t="s">
-        <x:v>674</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B436" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D436" s="0" t="s">
-        <x:v>675</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E436" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F436" s="0">
         <x:v>1</x:v>
@@ -13955,16 +14012,16 @@
     </x:row>
     <x:row r="437" spans="1:27">
       <x:c r="A437" s="0" t="s">
-        <x:v>676</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B437" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D437" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E437" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F437" s="0">
         <x:v>1</x:v>
@@ -13981,16 +14038,16 @@
     </x:row>
     <x:row r="438" spans="1:27">
       <x:c r="A438" s="0" t="s">
-        <x:v>677</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B438" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D438" s="0" t="s">
-        <x:v>678</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E438" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F438" s="0">
         <x:v>1</x:v>
@@ -14007,16 +14064,16 @@
     </x:row>
     <x:row r="439" spans="1:27">
       <x:c r="A439" s="0" t="s">
-        <x:v>679</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="B439" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D439" s="0" t="s">
-        <x:v>680</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E439" s="0" t="s">
-        <x:v>681</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="F439" s="0">
         <x:v>1</x:v>
@@ -14033,16 +14090,16 @@
     </x:row>
     <x:row r="440" spans="1:27">
       <x:c r="A440" s="0" t="s">
-        <x:v>682</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B440" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D440" s="0" t="s">
-        <x:v>683</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="E440" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F440" s="0">
         <x:v>1</x:v>
@@ -14059,16 +14116,16 @@
     </x:row>
     <x:row r="441" spans="1:27">
       <x:c r="A441" s="0" t="s">
-        <x:v>684</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="B441" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D441" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E441" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F441" s="0">
         <x:v>1</x:v>
@@ -14085,16 +14142,16 @@
     </x:row>
     <x:row r="442" spans="1:27">
       <x:c r="A442" s="0" t="s">
-        <x:v>685</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B442" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D442" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E442" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F442" s="0">
         <x:v>1</x:v>
@@ -14111,16 +14168,16 @@
     </x:row>
     <x:row r="443" spans="1:27">
       <x:c r="A443" s="0" t="s">
-        <x:v>686</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B443" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D443" s="0" t="s">
-        <x:v>687</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E443" s="0" t="s">
-        <x:v>688</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="F443" s="0">
         <x:v>1</x:v>
@@ -14137,16 +14194,16 @@
     </x:row>
     <x:row r="444" spans="1:27">
       <x:c r="A444" s="0" t="s">
-        <x:v>689</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="B444" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D444" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E444" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F444" s="0">
         <x:v>1</x:v>
@@ -14163,16 +14220,16 @@
     </x:row>
     <x:row r="445" spans="1:27">
       <x:c r="A445" s="0" t="s">
-        <x:v>690</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="B445" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D445" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E445" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F445" s="0">
         <x:v>1</x:v>
@@ -14189,16 +14246,16 @@
     </x:row>
     <x:row r="446" spans="1:27">
       <x:c r="A446" s="0" t="s">
-        <x:v>691</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="B446" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D446" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E446" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F446" s="0">
         <x:v>1</x:v>
@@ -14215,19 +14272,19 @@
     </x:row>
     <x:row r="447" spans="1:27">
       <x:c r="A447" s="0" t="s">
-        <x:v>692</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="B447" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D447" s="0" t="s">
-        <x:v>693</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="E447" s="0" t="s">
-        <x:v>694</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="F447" s="0">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I447" s="0">
         <x:v>2879</x:v>
@@ -14235,22 +14292,25 @@
       <x:c r="K447" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="R447" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="W447" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="448" spans="1:27">
       <x:c r="A448" s="0" t="s">
-        <x:v>695</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="B448" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D448" s="0" t="s">
-        <x:v>696</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="E448" s="0" t="s">
-        <x:v>697</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="F448" s="0">
         <x:v>1</x:v>
@@ -14267,16 +14327,16 @@
     </x:row>
     <x:row r="449" spans="1:27">
       <x:c r="A449" s="0" t="s">
-        <x:v>698</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="B449" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D449" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E449" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F449" s="0">
         <x:v>1</x:v>
@@ -14293,16 +14353,16 @@
     </x:row>
     <x:row r="450" spans="1:27">
       <x:c r="A450" s="0" t="s">
-        <x:v>699</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="B450" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D450" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E450" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F450" s="0">
         <x:v>1</x:v>
@@ -14319,16 +14379,16 @@
     </x:row>
     <x:row r="451" spans="1:27">
       <x:c r="A451" s="0" t="s">
-        <x:v>700</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B451" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D451" s="0" t="s">
-        <x:v>701</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="E451" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F451" s="0">
         <x:v>1</x:v>
@@ -14345,16 +14405,16 @@
     </x:row>
     <x:row r="452" spans="1:27">
       <x:c r="A452" s="0" t="s">
-        <x:v>702</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="B452" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D452" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E452" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F452" s="0">
         <x:v>1</x:v>
@@ -14371,16 +14431,16 @@
     </x:row>
     <x:row r="453" spans="1:27">
       <x:c r="A453" s="0" t="s">
-        <x:v>703</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B453" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D453" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E453" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F453" s="0">
         <x:v>1</x:v>
@@ -14397,16 +14457,16 @@
     </x:row>
     <x:row r="454" spans="1:27">
       <x:c r="A454" s="0" t="s">
-        <x:v>704</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B454" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D454" s="0" t="s">
-        <x:v>641</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="E454" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F454" s="0">
         <x:v>1</x:v>
@@ -14423,16 +14483,16 @@
     </x:row>
     <x:row r="455" spans="1:27">
       <x:c r="A455" s="0" t="s">
-        <x:v>705</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B455" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D455" s="0" t="s">
-        <x:v>643</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="E455" s="0" t="s">
-        <x:v>644</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="F455" s="0">
         <x:v>1</x:v>
@@ -14449,16 +14509,16 @@
     </x:row>
     <x:row r="456" spans="1:27">
       <x:c r="A456" s="0" t="s">
-        <x:v>706</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B456" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D456" s="0" t="s">
-        <x:v>646</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="E456" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F456" s="0">
         <x:v>1</x:v>
@@ -14475,16 +14535,16 @@
     </x:row>
     <x:row r="457" spans="1:27">
       <x:c r="A457" s="0" t="s">
-        <x:v>707</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B457" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D457" s="0" t="s">
-        <x:v>648</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E457" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F457" s="0">
         <x:v>1</x:v>
@@ -14501,16 +14561,16 @@
     </x:row>
     <x:row r="458" spans="1:27">
       <x:c r="A458" s="0" t="s">
-        <x:v>708</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B458" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D458" s="0" t="s">
-        <x:v>650</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E458" s="0" t="s">
-        <x:v>651</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="F458" s="0">
         <x:v>1</x:v>
@@ -14527,16 +14587,16 @@
     </x:row>
     <x:row r="459" spans="1:27">
       <x:c r="A459" s="0" t="s">
-        <x:v>709</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B459" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D459" s="0" t="s">
-        <x:v>653</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="E459" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F459" s="0">
         <x:v>1</x:v>
@@ -14553,16 +14613,16 @@
     </x:row>
     <x:row r="460" spans="1:27">
       <x:c r="A460" s="0" t="s">
-        <x:v>710</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B460" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D460" s="0" t="s">
-        <x:v>655</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E460" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F460" s="0">
         <x:v>1</x:v>
@@ -14579,16 +14639,16 @@
     </x:row>
     <x:row r="461" spans="1:27">
       <x:c r="A461" s="0" t="s">
-        <x:v>711</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="B461" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D461" s="0" t="s">
-        <x:v>657</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E461" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F461" s="0">
         <x:v>1</x:v>
@@ -14605,16 +14665,16 @@
     </x:row>
     <x:row r="462" spans="1:27">
       <x:c r="A462" s="0" t="s">
-        <x:v>712</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B462" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D462" s="0" t="s">
-        <x:v>659</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E462" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F462" s="0">
         <x:v>1</x:v>
@@ -14631,16 +14691,16 @@
     </x:row>
     <x:row r="463" spans="1:27">
       <x:c r="A463" s="0" t="s">
-        <x:v>713</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B463" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D463" s="0" t="s">
-        <x:v>661</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E463" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F463" s="0">
         <x:v>1</x:v>
@@ -14657,16 +14717,16 @@
     </x:row>
     <x:row r="464" spans="1:27">
       <x:c r="A464" s="0" t="s">
-        <x:v>714</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B464" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D464" s="0" t="s">
-        <x:v>663</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E464" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F464" s="0">
         <x:v>1</x:v>
@@ -14683,16 +14743,16 @@
     </x:row>
     <x:row r="465" spans="1:27">
       <x:c r="A465" s="0" t="s">
-        <x:v>715</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B465" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D465" s="0" t="s">
-        <x:v>665</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E465" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F465" s="0">
         <x:v>1</x:v>
@@ -14709,16 +14769,16 @@
     </x:row>
     <x:row r="466" spans="1:27">
       <x:c r="A466" s="0" t="s">
-        <x:v>716</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B466" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D466" s="0" t="s">
-        <x:v>667</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="E466" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F466" s="0">
         <x:v>1</x:v>
@@ -14735,16 +14795,16 @@
     </x:row>
     <x:row r="467" spans="1:27">
       <x:c r="A467" s="0" t="s">
-        <x:v>717</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="B467" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D467" s="0" t="s">
-        <x:v>669</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E467" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F467" s="0">
         <x:v>1</x:v>
@@ -14761,16 +14821,16 @@
     </x:row>
     <x:row r="468" spans="1:27">
       <x:c r="A468" s="0" t="s">
-        <x:v>718</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B468" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D468" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E468" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F468" s="0">
         <x:v>1</x:v>
@@ -14787,16 +14847,16 @@
     </x:row>
     <x:row r="469" spans="1:27">
       <x:c r="A469" s="0" t="s">
-        <x:v>719</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B469" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D469" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E469" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F469" s="0">
         <x:v>1</x:v>
@@ -14813,16 +14873,16 @@
     </x:row>
     <x:row r="470" spans="1:27">
       <x:c r="A470" s="0" t="s">
-        <x:v>720</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B470" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D470" s="0" t="s">
-        <x:v>673</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E470" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F470" s="0">
         <x:v>1</x:v>
@@ -14839,16 +14899,16 @@
     </x:row>
     <x:row r="471" spans="1:27">
       <x:c r="A471" s="0" t="s">
-        <x:v>721</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B471" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D471" s="0" t="s">
-        <x:v>675</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E471" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F471" s="0">
         <x:v>1</x:v>
@@ -14865,16 +14925,16 @@
     </x:row>
     <x:row r="472" spans="1:27">
       <x:c r="A472" s="0" t="s">
-        <x:v>722</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B472" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D472" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E472" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F472" s="0">
         <x:v>1</x:v>
@@ -14891,16 +14951,16 @@
     </x:row>
     <x:row r="473" spans="1:27">
       <x:c r="A473" s="0" t="s">
-        <x:v>723</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="B473" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D473" s="0" t="s">
-        <x:v>678</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E473" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F473" s="0">
         <x:v>1</x:v>
@@ -14917,16 +14977,16 @@
     </x:row>
     <x:row r="474" spans="1:27">
       <x:c r="A474" s="0" t="s">
-        <x:v>724</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B474" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D474" s="0" t="s">
-        <x:v>680</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E474" s="0" t="s">
-        <x:v>681</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="F474" s="0">
         <x:v>1</x:v>
@@ -14943,16 +15003,16 @@
     </x:row>
     <x:row r="475" spans="1:27">
       <x:c r="A475" s="0" t="s">
-        <x:v>725</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B475" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D475" s="0" t="s">
-        <x:v>683</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="E475" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F475" s="0">
         <x:v>1</x:v>
@@ -14969,16 +15029,16 @@
     </x:row>
     <x:row r="476" spans="1:27">
       <x:c r="A476" s="0" t="s">
-        <x:v>726</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B476" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D476" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E476" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F476" s="0">
         <x:v>1</x:v>
@@ -14995,16 +15055,16 @@
     </x:row>
     <x:row r="477" spans="1:27">
       <x:c r="A477" s="0" t="s">
-        <x:v>727</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B477" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D477" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E477" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F477" s="0">
         <x:v>1</x:v>
@@ -15021,16 +15081,16 @@
     </x:row>
     <x:row r="478" spans="1:27">
       <x:c r="A478" s="0" t="s">
-        <x:v>728</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B478" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D478" s="0" t="s">
-        <x:v>729</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E478" s="0" t="s">
-        <x:v>730</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="F478" s="0">
         <x:v>1</x:v>
@@ -15047,16 +15107,16 @@
     </x:row>
     <x:row r="479" spans="1:27">
       <x:c r="A479" s="0" t="s">
-        <x:v>731</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B479" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D479" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E479" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F479" s="0">
         <x:v>1</x:v>
@@ -15073,16 +15133,16 @@
     </x:row>
     <x:row r="480" spans="1:27">
       <x:c r="A480" s="0" t="s">
-        <x:v>732</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B480" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D480" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E480" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F480" s="0">
         <x:v>1</x:v>
@@ -15099,16 +15159,16 @@
     </x:row>
     <x:row r="481" spans="1:27">
       <x:c r="A481" s="0" t="s">
-        <x:v>733</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B481" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D481" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E481" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F481" s="0">
         <x:v>1</x:v>
@@ -15125,10 +15185,10 @@
     </x:row>
     <x:row r="482" spans="1:27">
       <x:c r="B482" s="0" t="s">
-        <x:v>734</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="D482" s="0" t="s">
-        <x:v>735</x:v>
+        <x:v>738</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
+++ b/samples/outputs/Deals20260518T034809_HPI_Uplift_parsed.xlsx
@@ -147,7 +147,7 @@
     <x:t>Max Qty: 880</x:t>
   </x:si>
   <x:si>
-    <x:t>4.01</x:t>
+    <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>C89FGAV</x:t>
@@ -156,7 +156,7 @@
     <x:t>BU IDS UMA RAI5435 8 14 G2a</x:t>
   </x:si>
   <x:si>
-    <x:t>4.02</x:t>
+    <x:t>6</x:t>
   </x:si>
   <x:si>
     <x:t>8C9M7AV</x:t>
@@ -165,7 +165,7 @@
     <x:t>No Country of Origin Restriction</x:t>
   </x:si>
   <x:si>
-    <x:t>4.03</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>1Y629AV</x:t>
@@ -174,7 +174,7 @@
     <x:t>Electronic Energy Star labeling (EStar)</x:t>
   </x:si>
   <x:si>
-    <x:t>4.04</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>C89HLAV</x:t>
@@ -183,7 +183,7 @@
     <x:t>OST W11P6 NG STD</x:t>
   </x:si>
   <x:si>
-    <x:t>4.05</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>4SS11AV</x:t>
@@ -192,7 +192,7 @@
     <x:t>OS Localization</x:t>
   </x:si>
   <x:si>
-    <x:t>4.06</x:t>
+    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>4SS11AV#ABG</x:t>
@@ -201,7 +201,7 @@
     <x:t>OS Localization AUST</x:t>
   </x:si>
   <x:si>
-    <x:t>4.07</x:t>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>C89FWAV</x:t>
@@ -210,7 +210,7 @@
     <x:t>Intgrtd Cam DM 5MP 2PCS IR AI</x:t>
   </x:si>
   <x:si>
-    <x:t>4.08</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>C89GLAV</x:t>
@@ -219,7 +219,7 @@
     <x:t>LCD 14WUXGAAGLED300UWVATPf5MPIRISP+LP60H</x:t>
   </x:si>
   <x:si>
-    <x:t>4.09</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>C89HMAV</x:t>
@@ -228,7 +228,7 @@
     <x:t>RAM 16GB (1x16GB) DDR5 5600</x:t>
   </x:si>
   <x:si>
-    <x:t>4.10</x:t>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>C89JMAV</x:t>
@@ -237,7 +237,7 @@
     <x:t>SSD 512GB 2280 PCIe Gen5 NVMe Val</x:t>
   </x:si>
   <x:si>
-    <x:t>4.11</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>C89FRAV</x:t>
@@ -246,7 +246,7 @@
     <x:t>ID GLS ALU f62Wh</x:t>
   </x:si>
   <x:si>
-    <x:t>4.12</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>C89GZAV</x:t>
@@ -255,7 +255,7 @@
     <x:t>NFC WNC XRAV-1</x:t>
   </x:si>
   <x:si>
-    <x:t>4.13</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>C89K2AV</x:t>
@@ -264,7 +264,7 @@
     <x:t>WLAN MT 2230 MT7925 Wi-Fi 7+BT6.0AIM-TWW</x:t>
   </x:si>
   <x:si>
-    <x:t>4.14</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>C89GVAV</x:t>
@@ -273,7 +273,7 @@
     <x:t>MISC No WWAN</x:t>
   </x:si>
   <x:si>
-    <x:t>4.15</x:t>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>C8LH5AV</x:t>
@@ -282,7 +282,7 @@
     <x:t>MISC No Fingerprint Sensor</x:t>
   </x:si>
   <x:si>
-    <x:t>4.16</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>C89H1AV</x:t>
@@ -291,7 +291,7 @@
     <x:t>No SmartCard Reader</x:t>
   </x:si>
   <x:si>
-    <x:t>4.17</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>C89FDAV</x:t>
@@ -300,7 +300,7 @@
     <x:t>BATT MC 3C Long Life 62Whr FstCrg</x:t>
   </x:si>
   <x:si>
-    <x:t>4.18</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>C89F4AV</x:t>
@@ -309,7 +309,7 @@
     <x:t>ACADPT HP 65W GaN STD USB-C Str</x:t>
   </x:si>
   <x:si>
-    <x:t>4.19</x:t>
+    <x:t>23</x:t>
   </x:si>
   <x:si>
     <x:t>C89FXAV</x:t>
@@ -318,7 +318,7 @@
     <x:t>KBDPM CP BL SR</x:t>
   </x:si>
   <x:si>
-    <x:t>4.20</x:t>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>C89FXAV#ABG</x:t>
@@ -327,7 +327,7 @@
     <x:t>Clickpad Backlit spill-resistant Premium Keyboard</x:t>
   </x:si>
   <x:si>
-    <x:t>4.21</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>C89FQAV</x:t>
@@ -336,7 +336,7 @@
     <x:t>CNTRYLOC</x:t>
   </x:si>
   <x:si>
-    <x:t>4.22</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>C89FQAV#ABG</x:t>
@@ -345,7 +345,7 @@
     <x:t>Country Localization</x:t>
   </x:si>
   <x:si>
-    <x:t>4.23</x:t>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>68V61AV</x:t>
@@ -354,7 +354,7 @@
     <x:t>C5 1.0m stkr CNVTL Power Cord</x:t>
   </x:si>
   <x:si>
-    <x:t>4.24</x:t>
+    <x:t>28</x:t>
   </x:si>
   <x:si>
     <x:t>68V61AV#ABG</x:t>
@@ -363,7 +363,7 @@
     <x:t>C5 1.0m Sticker Conventional Power Cord</x:t>
   </x:si>
   <x:si>
-    <x:t>4.25</x:t>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>C89K0AV</x:t>
@@ -372,7 +372,7 @@
     <x:t>WARR 1/1/1</x:t>
   </x:si>
   <x:si>
-    <x:t>4.26</x:t>
+    <x:t>30</x:t>
   </x:si>
   <x:si>
     <x:t>C89K0AV#UUF</x:t>
@@ -381,7 +381,7 @@
     <x:t>1/1/1 Warranty</x:t>
   </x:si>
   <x:si>
-    <x:t>4.27</x:t>
+    <x:t>31</x:t>
   </x:si>
   <x:si>
     <x:t>791T2AV</x:t>
@@ -390,7 +390,7 @@
     <x:t>Pre-Boot UEFI Wi-Fi support</x:t>
   </x:si>
   <x:si>
-    <x:t>4.28</x:t>
+    <x:t>32</x:t>
   </x:si>
   <x:si>
     <x:t>4N738AV</x:t>
@@ -399,7 +399,7 @@
     <x:t>HP Tamper Lock Permanent Disable</x:t>
   </x:si>
   <x:si>
-    <x:t>4.29</x:t>
+    <x:t>33</x:t>
   </x:si>
   <x:si>
     <x:t>C89GYAV</x:t>
@@ -408,7 +408,7 @@
     <x:t>MISC Packaging Standard</x:t>
   </x:si>
   <x:si>
-    <x:t>4.30</x:t>
+    <x:t>34</x:t>
   </x:si>
   <x:si>
     <x:t>D18SMAV</x:t>
@@ -417,7 +417,7 @@
     <x:t>HP Sure Recover ELS Disable</x:t>
   </x:si>
   <x:si>
-    <x:t>4.31</x:t>
+    <x:t>35</x:t>
   </x:si>
   <x:si>
     <x:t>3E755AV</x:t>
@@ -426,7 +426,7 @@
     <x:t>Electronic TCO Certified labeling</x:t>
   </x:si>
   <x:si>
-    <x:t>4.32</x:t>
+    <x:t>36</x:t>
   </x:si>
   <x:si>
     <x:t>C7QH0AV</x:t>
@@ -435,7 +435,7 @@
     <x:t>MISC PremiumEnableHEVC(H.265)CODECAccele</x:t>
   </x:si>
   <x:si>
-    <x:t>4.33</x:t>
+    <x:t>37</x:t>
   </x:si>
   <x:si>
     <x:t>X7A78AV</x:t>
@@ -444,7 +444,7 @@
     <x:t>WRNTY16 BOOK-AP-1YR</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
+    <x:t>38</x:t>
   </x:si>
   <x:si>
     <x:t>55623739</x:t>
@@ -456,7 +456,7 @@
     <x:t>Max Qty: 31</x:t>
   </x:si>
   <x:si>
-    <x:t>5.01</x:t>
+    <x:t>39</x:t>
   </x:si>
   <x:si>
     <x:t>C89FLAV</x:t>
@@ -465,13 +465,13 @@
     <x:t>BU IDS UMA RAI7450 8 14 G2a</x:t>
   </x:si>
   <x:si>
-    <x:t>5.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.04</x:t>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
   </x:si>
   <x:si>
     <x:t>C89HKAV</x:t>
@@ -480,19 +480,19 @@
     <x:t>OST W11P6 NG PRE</x:t>
   </x:si>
   <x:si>
-    <x:t>5.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.09</x:t>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
   </x:si>
   <x:si>
     <x:t>C89J0AV</x:t>
@@ -501,79 +501,79 @@
     <x:t>RAM 32GB (2x16GB) DDR5 5600</x:t>
   </x:si>
   <x:si>
-    <x:t>5.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
   </x:si>
   <x:si>
     <x:t>55623750</x:t>
@@ -582,7 +582,7 @@
     <x:t>55623750-HP EliteBook 6 G2a 14 (14" Touch, Ryzen 5, 16GB, 512GB)</x:t>
   </x:si>
   <x:si>
-    <x:t>6.01</x:t>
+    <x:t>73</x:t>
   </x:si>
   <x:si>
     <x:t>CD3N3AV</x:t>
@@ -591,13 +591,13 @@
     <x:t>BU IDS UMA R5230 6 14 G2a</x:t>
   </x:si>
   <x:si>
-    <x:t>6.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.04</x:t>
+    <x:t>74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76</x:t>
   </x:si>
   <x:si>
     <x:t>CD4Y3AV</x:t>
@@ -606,37 +606,37 @@
     <x:t>OST W11P6</x:t>
   </x:si>
   <x:si>
-    <x:t>6.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.07</x:t>
+    <x:t>77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79</x:t>
   </x:si>
   <x:si>
     <x:t>CD4T3AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.08</x:t>
+    <x:t>80</x:t>
   </x:si>
   <x:si>
     <x:t>CD4V0AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.09</x:t>
+    <x:t>81</x:t>
   </x:si>
   <x:si>
     <x:t>CD4Y6AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.10</x:t>
+    <x:t>82</x:t>
   </x:si>
   <x:si>
     <x:t>CD5B4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.11</x:t>
+    <x:t>83</x:t>
   </x:si>
   <x:si>
     <x:t>CD4S9AV</x:t>
@@ -645,13 +645,13 @@
     <x:t>ID PKS ALU fWLAN</x:t>
   </x:si>
   <x:si>
-    <x:t>6.12</x:t>
+    <x:t>84</x:t>
   </x:si>
   <x:si>
     <x:t>CD4W2AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.13</x:t>
+    <x:t>85</x:t>
   </x:si>
   <x:si>
     <x:t>CD5C8AV</x:t>
@@ -660,25 +660,25 @@
     <x:t>WLAN MT 2230 MT7925 Wi-Fi 7 +BT 6.0 WW</x:t>
   </x:si>
   <x:si>
-    <x:t>6.14</x:t>
+    <x:t>86</x:t>
   </x:si>
   <x:si>
     <x:t>CD4V8AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.15</x:t>
+    <x:t>87</x:t>
   </x:si>
   <x:si>
     <x:t>CD4V4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.16</x:t>
+    <x:t>88</x:t>
   </x:si>
   <x:si>
     <x:t>CD4W4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.17</x:t>
+    <x:t>89</x:t>
   </x:si>
   <x:si>
     <x:t>CD4S6AV</x:t>
@@ -687,7 +687,7 @@
     <x:t>BATT PM 3C Long Life 68Whr FstCrg</x:t>
   </x:si>
   <x:si>
-    <x:t>6.18</x:t>
+    <x:t>90</x:t>
   </x:si>
   <x:si>
     <x:t>CD4R6AV</x:t>
@@ -696,7 +696,7 @@
     <x:t>ACADPT HP 100W GaNWMTFxdUSB-CHF</x:t>
   </x:si>
   <x:si>
-    <x:t>6.19</x:t>
+    <x:t>91</x:t>
   </x:si>
   <x:si>
     <x:t>CE2G7AV</x:t>
@@ -705,7 +705,7 @@
     <x:t>KBD CPfNFC BL SR</x:t>
   </x:si>
   <x:si>
-    <x:t>6.20</x:t>
+    <x:t>92</x:t>
   </x:si>
   <x:si>
     <x:t>CE2G7AV#ABG</x:t>
@@ -714,19 +714,19 @@
     <x:t>Clickpad for NFC backlit spill-resistant Standard Notebook Keyboard</x:t>
   </x:si>
   <x:si>
-    <x:t>6.21</x:t>
+    <x:t>93</x:t>
   </x:si>
   <x:si>
     <x:t>CE2H2AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.22</x:t>
+    <x:t>94</x:t>
   </x:si>
   <x:si>
     <x:t>CE2H2AV#ABG</x:t>
   </x:si>
   <x:si>
-    <x:t>6.23</x:t>
+    <x:t>95</x:t>
   </x:si>
   <x:si>
     <x:t>C5AK2AV</x:t>
@@ -735,7 +735,7 @@
     <x:t>DHONLY Non-Standard HF</x:t>
   </x:si>
   <x:si>
-    <x:t>6.24</x:t>
+    <x:t>96</x:t>
   </x:si>
   <x:si>
     <x:t>C5AK2AV#ABG</x:t>
@@ -744,40 +744,40 @@
     <x:t>Non-Standard Halogen Free Duckhead Only</x:t>
   </x:si>
   <x:si>
-    <x:t>6.25</x:t>
+    <x:t>97</x:t>
   </x:si>
   <x:si>
     <x:t>CE2H4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.26</x:t>
+    <x:t>98</x:t>
   </x:si>
   <x:si>
     <x:t>CE2H4AV#UUF</x:t>
   </x:si>
   <x:si>
-    <x:t>6.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.29</x:t>
+    <x:t>99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101</x:t>
   </x:si>
   <x:si>
     <x:t>CD4W1AV</x:t>
   </x:si>
   <x:si>
-    <x:t>6.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.33</x:t>
+    <x:t>102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105</x:t>
   </x:si>
   <x:si>
     <x:t>U85GJE</x:t>
@@ -786,7 +786,7 @@
     <x:t>HP 3y Onsite NB Supp</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
+    <x:t>106</x:t>
   </x:si>
   <x:si>
     <x:t>55623755</x:t>
@@ -795,7 +795,7 @@
     <x:t>55623755-HP EliteBook 6 G1a 14 (14" Touch, Ryzen 7, 32GB, 512GB)</x:t>
   </x:si>
   <x:si>
-    <x:t>7.01</x:t>
+    <x:t>107</x:t>
   </x:si>
   <x:si>
     <x:t>AY4Z7AV</x:t>
@@ -804,16 +804,16 @@
     <x:t>HP IDS UMA R7250 6 14 G1a BNBPC</x:t>
   </x:si>
   <x:si>
-    <x:t>7.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.03</x:t>
+    <x:t>108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109</x:t>
   </x:si>
   <x:si>
     <x:t>1Y632AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.04</x:t>
+    <x:t>110</x:t>
   </x:si>
   <x:si>
     <x:t>AY6G4AV</x:t>
@@ -822,13 +822,13 @@
     <x:t>OST Win 11 Pro 64</x:t>
   </x:si>
   <x:si>
-    <x:t>7.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.07</x:t>
+    <x:t>111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113</x:t>
   </x:si>
   <x:si>
     <x:t>AY6B0AV</x:t>
@@ -837,7 +837,7 @@
     <x:t>DM 5MP USB2 IR WFOV Intgrtd Cam</x:t>
   </x:si>
   <x:si>
-    <x:t>7.08</x:t>
+    <x:t>114</x:t>
   </x:si>
   <x:si>
     <x:t>AY6C8AV</x:t>
@@ -846,7 +846,7 @@
     <x:t>14.0AGWUXGAUWVALED300f5MPIR60HzTouchbntL</x:t>
   </x:si>
   <x:si>
-    <x:t>7.09</x:t>
+    <x:t>115</x:t>
   </x:si>
   <x:si>
     <x:t>AY6H5AV</x:t>
@@ -855,7 +855,7 @@
     <x:t>RAM 32GB (2x16GB) DDR5 5600 NMIC</x:t>
   </x:si>
   <x:si>
-    <x:t>7.10</x:t>
+    <x:t>116</x:t>
   </x:si>
   <x:si>
     <x:t>AY6K7AV</x:t>
@@ -864,7 +864,7 @@
     <x:t>SSD 512GB PCIe NVMe Value</x:t>
   </x:si>
   <x:si>
-    <x:t>7.11</x:t>
+    <x:t>117</x:t>
   </x:si>
   <x:si>
     <x:t>AY6A7AV</x:t>
@@ -873,7 +873,7 @@
     <x:t>PKS ALU fWLAN ID</x:t>
   </x:si>
   <x:si>
-    <x:t>7.12</x:t>
+    <x:t>118</x:t>
   </x:si>
   <x:si>
     <x:t>AY6D6AV</x:t>
@@ -882,7 +882,7 @@
     <x:t>No Near Field Communication (No NFC)</x:t>
   </x:si>
   <x:si>
-    <x:t>7.13</x:t>
+    <x:t>119</x:t>
   </x:si>
   <x:si>
     <x:t>AY6L5AV</x:t>
@@ -891,7 +891,7 @@
     <x:t>WLAN MT 2230 MT7925 Wi-Fi 7+BT5.4AIM-TWW</x:t>
   </x:si>
   <x:si>
-    <x:t>7.14</x:t>
+    <x:t>120</x:t>
   </x:si>
   <x:si>
     <x:t>AY6E0AV</x:t>
@@ -900,7 +900,7 @@
     <x:t>No WWAN</x:t>
   </x:si>
   <x:si>
-    <x:t>7.15</x:t>
+    <x:t>121</x:t>
   </x:si>
   <x:si>
     <x:t>AY6D5AV</x:t>
@@ -909,13 +909,13 @@
     <x:t>No Fingerprint Sensor</x:t>
   </x:si>
   <x:si>
-    <x:t>7.16</x:t>
+    <x:t>122</x:t>
   </x:si>
   <x:si>
     <x:t>AY6D7AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.17</x:t>
+    <x:t>123</x:t>
   </x:si>
   <x:si>
     <x:t>AY6A5AV</x:t>
@@ -924,7 +924,7 @@
     <x:t>RX Long Life 48Whr FstCrg 3 cell Batt</x:t>
   </x:si>
   <x:si>
-    <x:t>7.18</x:t>
+    <x:t>124</x:t>
   </x:si>
   <x:si>
     <x:t>AY6A1AV</x:t>
@@ -933,7 +933,7 @@
     <x:t>ACADPT 65 Watt nPFC USB-C</x:t>
   </x:si>
   <x:si>
-    <x:t>7.19</x:t>
+    <x:t>125</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W5AV</x:t>
@@ -942,7 +942,7 @@
     <x:t>Clickpad BL SR</x:t>
   </x:si>
   <x:si>
-    <x:t>7.20</x:t>
+    <x:t>126</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W5AV#ABG</x:t>
@@ -951,31 +951,31 @@
     <x:t>Australia - English localization</x:t>
   </x:si>
   <x:si>
-    <x:t>7.21</x:t>
+    <x:t>127</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W7AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.22</x:t>
+    <x:t>128</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W7AV#ABG</x:t>
   </x:si>
   <x:si>
-    <x:t>7.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.25</x:t>
+    <x:t>129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>131</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.26</x:t>
+    <x:t>132</x:t>
   </x:si>
   <x:si>
     <x:t>AZ0W4AV#UUF</x:t>
@@ -984,10 +984,10 @@
     <x:t>AP Eng localization</x:t>
   </x:si>
   <x:si>
-    <x:t>7.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.28</x:t>
+    <x:t>133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>134</x:t>
   </x:si>
   <x:si>
     <x:t>4N733AV</x:t>
@@ -996,7 +996,7 @@
     <x:t>HP Tamper Lock</x:t>
   </x:si>
   <x:si>
-    <x:t>7.29</x:t>
+    <x:t>135</x:t>
   </x:si>
   <x:si>
     <x:t>AY6E3AV</x:t>
@@ -1005,22 +1005,22 @@
     <x:t>Standard Packaging</x:t>
   </x:si>
   <x:si>
-    <x:t>7.30</x:t>
+    <x:t>136</x:t>
   </x:si>
   <x:si>
     <x:t>3E758AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.31</x:t>
+    <x:t>137</x:t>
   </x:si>
   <x:si>
     <x:t>X7B33AV</x:t>
   </x:si>
   <x:si>
-    <x:t>7.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
+    <x:t>138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139</x:t>
   </x:si>
   <x:si>
     <x:t>55623769</x:t>
@@ -1029,7 +1029,7 @@
     <x:t>55623769-HP EliteBook 6 G2a 14 (14" Touch, Ryzen 7, 32GB, 512GB)</x:t>
   </x:si>
   <x:si>
-    <x:t>8.01</x:t>
+    <x:t>140</x:t>
   </x:si>
   <x:si>
     <x:t>CD3P0AV</x:t>
@@ -1038,106 +1038,106 @@
     <x:t>BU IDS UMA R7250 6 14 G2a</x:t>
   </x:si>
   <x:si>
-    <x:t>8.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.09</x:t>
+    <x:t>141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>148</x:t>
   </x:si>
   <x:si>
     <x:t>CD4Z5AV</x:t>
   </x:si>
   <x:si>
-    <x:t>8.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
+    <x:t>149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>166</x:t>
+  </x:si>
+  <x:si>
+    <x:t>167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>173</x:t>
   </x:si>
   <x:si>
     <x:t>55623774</x:t>
@@ -1146,7 +1146,7 @@
     <x:t>55623774-HP EliteBook 6 G1a 14 (14" Touch, Ryzen 5, 16GB, 256GB)</x:t>
   </x:si>
   <x:si>
-    <x:t>9.01</x:t>
+    <x:t>174</x:t>
   </x:si>
   <x:si>
     <x:t>B4YC1AV</x:t>
@@ -1155,28 +1155,28 @@
     <x:t>HP IDS UMA R5230 6 14 G1a BNBPC</x:t>
   </x:si>
   <x:si>
-    <x:t>9.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.09</x:t>
+    <x:t>175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>182</x:t>
   </x:si>
   <x:si>
     <x:t>AY6G8AV</x:t>
@@ -1185,7 +1185,7 @@
     <x:t>16GB (1x16GB) DDR5 5600 SODIMM Mem</x:t>
   </x:si>
   <x:si>
-    <x:t>9.10</x:t>
+    <x:t>183</x:t>
   </x:si>
   <x:si>
     <x:t>AY6K1AV</x:t>
@@ -1194,73 +1194,73 @@
     <x:t>256GB PCIe NVMe Value SSD</x:t>
   </x:si>
   <x:si>
-    <x:t>9.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
+    <x:t>184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>186</x:t>
+  </x:si>
+  <x:si>
+    <x:t>187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>196</x:t>
+  </x:si>
+  <x:si>
+    <x:t>197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>198</x:t>
+  </x:si>
+  <x:si>
+    <x:t>199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>206</x:t>
   </x:si>
   <x:si>
     <x:t>55636494</x:t>
@@ -1269,103 +1269,103 @@
     <x:t>55636494-HP EliteBook 6 G1a 14 14in Touch, Ryzen 5, 16GB, 256GB.xlsx</x:t>
   </x:si>
   <x:si>
-    <x:t>10.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
+    <x:t>207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>208</x:t>
+  </x:si>
+  <x:si>
+    <x:t>209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>235</x:t>
+  </x:si>
+  <x:si>
+    <x:t>236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>238</x:t>
+  </x:si>
+  <x:si>
+    <x:t>239</x:t>
   </x:si>
   <x:si>
     <x:t>55636497</x:t>
@@ -1374,106 +1374,106 @@
     <x:t>55636497-HP EliteBook 6 G2a 14 14in Touch, Ryzen 7, 32GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>11.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
+    <x:t>240</x:t>
+  </x:si>
+  <x:si>
+    <x:t>241</x:t>
+  </x:si>
+  <x:si>
+    <x:t>242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>245</x:t>
+  </x:si>
+  <x:si>
+    <x:t>246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>249</x:t>
+  </x:si>
+  <x:si>
+    <x:t>250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252</x:t>
+  </x:si>
+  <x:si>
+    <x:t>253</x:t>
+  </x:si>
+  <x:si>
+    <x:t>254</x:t>
+  </x:si>
+  <x:si>
+    <x:t>255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>258</x:t>
+  </x:si>
+  <x:si>
+    <x:t>259</x:t>
+  </x:si>
+  <x:si>
+    <x:t>260</x:t>
+  </x:si>
+  <x:si>
+    <x:t>261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>264</x:t>
+  </x:si>
+  <x:si>
+    <x:t>265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>266</x:t>
+  </x:si>
+  <x:si>
+    <x:t>267</x:t>
+  </x:si>
+  <x:si>
+    <x:t>268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>270</x:t>
+  </x:si>
+  <x:si>
+    <x:t>271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>273</x:t>
   </x:si>
   <x:si>
     <x:t>55636500</x:t>
@@ -1482,103 +1482,103 @@
     <x:t>55636500-HP EliteBook 6 G1a 14 14in Touch, Ryzen 7, 32GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>12.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
+    <x:t>274</x:t>
+  </x:si>
+  <x:si>
+    <x:t>275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>277</x:t>
+  </x:si>
+  <x:si>
+    <x:t>278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>283</x:t>
+  </x:si>
+  <x:si>
+    <x:t>284</x:t>
+  </x:si>
+  <x:si>
+    <x:t>285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>293</x:t>
+  </x:si>
+  <x:si>
+    <x:t>294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>295</x:t>
+  </x:si>
+  <x:si>
+    <x:t>296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>297</x:t>
+  </x:si>
+  <x:si>
+    <x:t>298</x:t>
+  </x:si>
+  <x:si>
+    <x:t>299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>306</x:t>
   </x:si>
   <x:si>
     <x:t>55636501</x:t>
@@ -1587,106 +1587,106 @@
     <x:t>55636501-HP EliteBook 6 G2a 14 14in Touch, Ryzen 5, 16GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>13.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
+    <x:t>307</x:t>
+  </x:si>
+  <x:si>
+    <x:t>308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>311</x:t>
+  </x:si>
+  <x:si>
+    <x:t>312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>315</x:t>
+  </x:si>
+  <x:si>
+    <x:t>316</x:t>
+  </x:si>
+  <x:si>
+    <x:t>317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>318</x:t>
+  </x:si>
+  <x:si>
+    <x:t>319</x:t>
+  </x:si>
+  <x:si>
+    <x:t>320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>340</x:t>
   </x:si>
   <x:si>
     <x:t>55636502</x:t>
@@ -1695,112 +1695,112 @@
     <x:t>55636502-HP EliteBook 8 G2a 14 14in Touch, Ryzen 7, 32GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>14.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.34</x:t>
+    <x:t>341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>348</x:t>
+  </x:si>
+  <x:si>
+    <x:t>349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>350</x:t>
+  </x:si>
+  <x:si>
+    <x:t>351</x:t>
+  </x:si>
+  <x:si>
+    <x:t>352</x:t>
+  </x:si>
+  <x:si>
+    <x:t>353</x:t>
+  </x:si>
+  <x:si>
+    <x:t>354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>356</x:t>
+  </x:si>
+  <x:si>
+    <x:t>357</x:t>
+  </x:si>
+  <x:si>
+    <x:t>358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>367</x:t>
+  </x:si>
+  <x:si>
+    <x:t>368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>371</x:t>
+  </x:si>
+  <x:si>
+    <x:t>372</x:t>
+  </x:si>
+  <x:si>
+    <x:t>373</x:t>
+  </x:si>
+  <x:si>
+    <x:t>374</x:t>
   </x:si>
   <x:si>
     <x:t>U85BQE</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>375</x:t>
   </x:si>
   <x:si>
     <x:t>55636505</x:t>
@@ -1809,109 +1809,109 @@
     <x:t>55636505-HP EliteBook 8 G2a 14 14in Touch, Ryzen 5, 16GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>15.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
+    <x:t>376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>377</x:t>
+  </x:si>
+  <x:si>
+    <x:t>378</x:t>
+  </x:si>
+  <x:si>
+    <x:t>379</x:t>
+  </x:si>
+  <x:si>
+    <x:t>380</x:t>
+  </x:si>
+  <x:si>
+    <x:t>381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>382</x:t>
+  </x:si>
+  <x:si>
+    <x:t>383</x:t>
+  </x:si>
+  <x:si>
+    <x:t>384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>389</x:t>
+  </x:si>
+  <x:si>
+    <x:t>390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>391</x:t>
+  </x:si>
+  <x:si>
+    <x:t>392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>397</x:t>
+  </x:si>
+  <x:si>
+    <x:t>398</x:t>
+  </x:si>
+  <x:si>
+    <x:t>399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>410</x:t>
   </x:si>
   <x:si>
     <x:t>55636508</x:t>
@@ -1920,7 +1920,7 @@
     <x:t>55636508-HP EliteBook 8 G2i 13 13in Touch, Core Ultra 5, 16GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>16.01</x:t>
+    <x:t>411</x:t>
   </x:si>
   <x:si>
     <x:t>C57X5AV</x:t>
@@ -1929,31 +1929,31 @@
     <x:t>BU IDS UMA U5325 16GB 8 13 G2i</x:t>
   </x:si>
   <x:si>
-    <x:t>16.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.04</x:t>
+    <x:t>412</x:t>
+  </x:si>
+  <x:si>
+    <x:t>413</x:t>
+  </x:si>
+  <x:si>
+    <x:t>414</x:t>
   </x:si>
   <x:si>
     <x:t>C58L7AV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.07</x:t>
+    <x:t>415</x:t>
+  </x:si>
+  <x:si>
+    <x:t>416</x:t>
+  </x:si>
+  <x:si>
+    <x:t>417</x:t>
   </x:si>
   <x:si>
     <x:t>C58JYAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.08</x:t>
+    <x:t>418</x:t>
   </x:si>
   <x:si>
     <x:t>C58K9AV</x:t>
@@ -1962,19 +1962,19 @@
     <x:t>LCD 13.3WUXGAAGLED300UWVATPf5MPIRISP+60H</x:t>
   </x:si>
   <x:si>
-    <x:t>16.09</x:t>
+    <x:t>419</x:t>
   </x:si>
   <x:si>
     <x:t>C58LPAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.10</x:t>
+    <x:t>420</x:t>
   </x:si>
   <x:si>
     <x:t>C58KQAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.11</x:t>
+    <x:t>421</x:t>
   </x:si>
   <x:si>
     <x:t>C58M2AV</x:t>
@@ -1983,88 +1983,88 @@
     <x:t>WLAN I 2230 BE211 Wi-Fi 7 +BT 6.0 nvP WW</x:t>
   </x:si>
   <x:si>
-    <x:t>16.12</x:t>
+    <x:t>422</x:t>
   </x:si>
   <x:si>
     <x:t>C58KLAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.13</x:t>
+    <x:t>423</x:t>
   </x:si>
   <x:si>
     <x:t>C58KGAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.14</x:t>
+    <x:t>424</x:t>
   </x:si>
   <x:si>
     <x:t>C58KRAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.15</x:t>
+    <x:t>425</x:t>
   </x:si>
   <x:si>
     <x:t>C58JWAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.16</x:t>
+    <x:t>426</x:t>
   </x:si>
   <x:si>
     <x:t>C58JMAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.17</x:t>
+    <x:t>427</x:t>
   </x:si>
   <x:si>
     <x:t>C58B1AV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.18</x:t>
+    <x:t>428</x:t>
   </x:si>
   <x:si>
     <x:t>C58B1AV#ABG</x:t>
   </x:si>
   <x:si>
-    <x:t>16.19</x:t>
+    <x:t>429</x:t>
   </x:si>
   <x:si>
     <x:t>C57YNAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.20</x:t>
+    <x:t>430</x:t>
   </x:si>
   <x:si>
     <x:t>C57YNAV#ABG</x:t>
   </x:si>
   <x:si>
-    <x:t>16.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.23</x:t>
+    <x:t>431</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432</x:t>
+  </x:si>
+  <x:si>
+    <x:t>433</x:t>
   </x:si>
   <x:si>
     <x:t>C58C4AV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.24</x:t>
+    <x:t>434</x:t>
   </x:si>
   <x:si>
     <x:t>C58C4AV#UUF</x:t>
   </x:si>
   <x:si>
-    <x:t>16.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.26</x:t>
+    <x:t>435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>436</x:t>
   </x:si>
   <x:si>
     <x:t>4N735AV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.27</x:t>
+    <x:t>437</x:t>
   </x:si>
   <x:si>
     <x:t>X9H42AV</x:t>
@@ -2073,19 +2073,19 @@
     <x:t>No vPro AMT supported</x:t>
   </x:si>
   <x:si>
-    <x:t>16.28</x:t>
+    <x:t>438</x:t>
   </x:si>
   <x:si>
     <x:t>C58KPAV</x:t>
   </x:si>
   <x:si>
-    <x:t>16.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.31</x:t>
+    <x:t>439</x:t>
+  </x:si>
+  <x:si>
+    <x:t>440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>441</x:t>
   </x:si>
   <x:si>
     <x:t>C1GT0AV</x:t>
@@ -2094,16 +2094,16 @@
     <x:t>LBL Intel Core Ultra 5 sz3 G18</x:t>
   </x:si>
   <x:si>
-    <x:t>16.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
+    <x:t>442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>445</x:t>
   </x:si>
   <x:si>
     <x:t>55636510</x:t>
@@ -2112,7 +2112,7 @@
     <x:t>55636510-HP EliteBook 8 G2i 13 13in Touch, Intel Core Ultra 7, 32GB, 512GB</x:t>
   </x:si>
   <x:si>
-    <x:t>17.01</x:t>
+    <x:t>446</x:t>
   </x:si>
   <x:si>
     <x:t>C57XXAV</x:t>
@@ -2121,97 +2121,97 @@
     <x:t>BU IDS UMA U7355 32GB 8 13 G2i</x:t>
   </x:si>
   <x:si>
-    <x:t>17.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04</x:t>
+    <x:t>447</x:t>
+  </x:si>
+  <x:si>
+    <x:t>448</x:t>
+  </x:si>
+  <x:si>
+    <x:t>449</x:t>
   </x:si>
   <x:si>
     <x:t>C58L6AV</x:t>
   </x:si>
   <x:si>
-    <x:t>17.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.31</x:t>
+    <x:t>450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>451</x:t>
+  </x:si>
+  <x:si>
+    <x:t>452</x:t>
+  </x:si>
+  <x:si>
+    <x:t>453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>454</x:t>
+  </x:si>
+  <x:si>
+    <x:t>455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>458</x:t>
+  </x:si>
+  <x:si>
+    <x:t>459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>460</x:t>
+  </x:si>
+  <x:si>
+    <x:t>461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>462</x:t>
+  </x:si>
+  <x:si>
+    <x:t>463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>465</x:t>
+  </x:si>
+  <x:si>
+    <x:t>466</x:t>
+  </x:si>
+  <x:si>
+    <x:t>467</x:t>
+  </x:si>
+  <x:si>
+    <x:t>468</x:t>
+  </x:si>
+  <x:si>
+    <x:t>469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>470</x:t>
+  </x:si>
+  <x:si>
+    <x:t>471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>476</x:t>
   </x:si>
   <x:si>
     <x:t>C1GT2AV</x:t>
@@ -2220,13 +2220,13 @@
     <x:t>LBL Intel Core Ultra 7 sz3 G18</x:t>
   </x:si>
   <x:si>
-    <x:t>17.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.34</x:t>
+    <x:t>477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>479</x:t>
   </x:si>
   <x:si>
     <x:t>*</x:t>
